--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>605660</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>38.6800003051758</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>37.2799987792969</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>38.4000015258789</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>37.7299995422363</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>466080</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>37.2999992370605</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>37.7099990844727</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>38.0200004577637</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>384622</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>38.5400009155273</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>37.7299995422363</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>38.4799995422363</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>409978</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>38.7099990844727</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>38.060001373291</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>38.6100006103516</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>38.1300010681152</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>295525</v>
+        <v>157276</v>
       </c>
       <c r="C2715" t="n">
-        <v>40.5999984741211</v>
+        <v>41.0299987792969</v>
       </c>
       <c r="D2715" t="n">
-        <v>40</v>
+        <v>40.4700012207031</v>
       </c>
       <c r="E2715" t="n">
-        <v>40.5999984741211</v>
+        <v>40.7099990844727</v>
       </c>
       <c r="F2715" t="n">
-        <v>40.2999992370605</v>
+        <v>40.7999992370605</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>479672</v>
+        <v>295525</v>
       </c>
       <c r="C2716" t="n">
-        <v>40.6100006103516</v>
+        <v>40.5999984741211</v>
       </c>
       <c r="D2716" t="n">
-        <v>39.2900009155273</v>
+        <v>40</v>
       </c>
       <c r="E2716" t="n">
-        <v>39.9199981689453</v>
+        <v>40.5999984741211</v>
       </c>
       <c r="F2716" t="n">
-        <v>39.7799987792969</v>
+        <v>40.2999992370605</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>385460</v>
+        <v>479672</v>
       </c>
       <c r="C2717" t="n">
-        <v>39.7999992370605</v>
+        <v>40.6100006103516</v>
       </c>
       <c r="D2717" t="n">
-        <v>38.6300010681152</v>
+        <v>39.2900009155273</v>
       </c>
       <c r="E2717" t="n">
-        <v>39.5900001525879</v>
+        <v>39.9199981689453</v>
       </c>
       <c r="F2717" t="n">
-        <v>38.7000007629395</v>
+        <v>39.7799987792969</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>328343</v>
+        <v>385460</v>
       </c>
       <c r="C2718" t="n">
-        <v>39.3800010681152</v>
+        <v>39.7999992370605</v>
       </c>
       <c r="D2718" t="n">
-        <v>38.4099998474121</v>
+        <v>38.6300010681152</v>
       </c>
       <c r="E2718" t="n">
-        <v>38.9700012207031</v>
+        <v>39.5900001525879</v>
       </c>
       <c r="F2718" t="n">
-        <v>38.8800010681152</v>
+        <v>38.7000007629395</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>605660</v>
+        <v>328343</v>
       </c>
       <c r="C2719" t="n">
-        <v>38.6800003051758</v>
+        <v>39.3800010681152</v>
       </c>
       <c r="D2719" t="n">
-        <v>37.2799987792969</v>
+        <v>38.4099998474121</v>
       </c>
       <c r="E2719" t="n">
-        <v>38.4000015258789</v>
+        <v>38.9700012207031</v>
       </c>
       <c r="F2719" t="n">
-        <v>37.7299995422363</v>
+        <v>38.8800010681152</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>466080</v>
+        <v>605660</v>
       </c>
       <c r="C2720" t="n">
-        <v>38.25</v>
+        <v>38.6800003051758</v>
       </c>
       <c r="D2720" t="n">
-        <v>37.2999992370605</v>
+        <v>37.2799987792969</v>
       </c>
       <c r="E2720" t="n">
-        <v>37.7099990844727</v>
+        <v>38.4000015258789</v>
       </c>
       <c r="F2720" t="n">
-        <v>38.0200004577637</v>
+        <v>37.7299995422363</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>384622</v>
+        <v>466080</v>
       </c>
       <c r="C2721" t="n">
-        <v>38.5400009155273</v>
+        <v>38.25</v>
       </c>
       <c r="D2721" t="n">
-        <v>37.7299995422363</v>
+        <v>37.2999992370605</v>
       </c>
       <c r="E2721" t="n">
-        <v>38</v>
+        <v>37.7099990844727</v>
       </c>
       <c r="F2721" t="n">
-        <v>38.4799995422363</v>
+        <v>38.0200004577637</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>409978</v>
+        <v>384622</v>
       </c>
       <c r="C2722" t="n">
-        <v>38.7099990844727</v>
+        <v>38.5400009155273</v>
       </c>
       <c r="D2722" t="n">
-        <v>38.060001373291</v>
+        <v>37.7299995422363</v>
       </c>
       <c r="E2722" t="n">
-        <v>38.6100006103516</v>
+        <v>38</v>
       </c>
       <c r="F2722" t="n">
-        <v>38.1300010681152</v>
+        <v>38.4799995422363</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>902751</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>38.6199989318848</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>37.2000007629395</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>38.0999984741211</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>37.2999992370605</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>37.8600006103516</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>37.4900016784668</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>394079</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>38.2700004577637</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>37.5800018310547</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>37.7000007629395</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>37.7000007629395</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>37.7599983215332</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>489678</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>37.7599983215332</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>37.060001373291</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>37.189998626709</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>37.189998626709</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>37.060001373291</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>567011</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>36.8699989318848</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>36.7700004577637</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>36.7700004577637</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>36</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>388377</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>37.1599998474121</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>36.4799995422363</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>36.4799995422363</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>429490</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>37.2700004577637</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>36.6699981689453</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>37.1399993896484</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -421,7 +421,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2" t="n">
-        <v>13.7963047027588</v>
+        <v>13.7963056564331</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G4" t="n">
-        <v>13.7963047027588</v>
+        <v>13.7963056564331</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2207536697388</v>
+        <v>13.2207546234131</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G7" t="n">
-        <v>12.6028833389282</v>
+        <v>12.6028842926025</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G9" t="n">
-        <v>12.3320360183716</v>
+        <v>12.3320341110229</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>11.3840675354004</v>
+        <v>11.3840684890747</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G14" t="n">
-        <v>10.7746610641479</v>
+        <v>10.7746601104736</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G15" t="n">
-        <v>11.3332853317261</v>
+        <v>11.3332843780518</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G17" t="n">
-        <v>11.5872049331665</v>
+        <v>11.5872039794922</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G18" t="n">
-        <v>12.1289005279541</v>
+        <v>12.1288995742798</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>12.0188684463501</v>
+        <v>12.0188674926758</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G20" t="n">
-        <v>11.4602422714233</v>
+        <v>11.4602451324463</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G21" t="n">
-        <v>11.7734107971191</v>
+        <v>11.7734127044678</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9185485839844</v>
+        <v>10.918550491333</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G25" t="n">
-        <v>11.2655725479126</v>
+        <v>11.2655735015869</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G26" t="n">
-        <v>11.3925342559814</v>
+        <v>11.3925313949585</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G28" t="n">
-        <v>10.3937826156616</v>
+        <v>10.393780708313</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G29" t="n">
-        <v>11.1386127471924</v>
+        <v>11.1386137008667</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G30" t="n">
-        <v>10.3853178024292</v>
+        <v>10.3853168487549</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>10.2414302825928</v>
+        <v>10.2414293289185</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>10.6815595626831</v>
+        <v>10.6815586090088</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>10.6223096847534</v>
+        <v>10.6223077774048</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G35" t="n">
-        <v>11.3840675354004</v>
+        <v>11.3840684890747</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G37" t="n">
-        <v>11.7734107971191</v>
+        <v>11.7734127044678</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G38" t="n">
-        <v>11.3925342559814</v>
+        <v>11.3925313949585</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>11.8919067382812</v>
+        <v>11.8919076919556</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G42" t="n">
-        <v>11.9257621765137</v>
+        <v>11.9257640838623</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G44" t="n">
-        <v>12.1119709014893</v>
+        <v>12.1119718551636</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>12.1289005279541</v>
+        <v>12.1288995742798</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>12.171217918396</v>
+        <v>12.1712188720703</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G47" t="n">
-        <v>12.1119709014893</v>
+        <v>12.1119718551636</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G51" t="n">
-        <v>12.7044496536255</v>
+        <v>12.7044506072998</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>13.0853290557861</v>
+        <v>13.0853309631348</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G53" t="n">
-        <v>12.6198120117188</v>
+        <v>12.6198110580444</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>12.6790590286255</v>
+        <v>12.6790580749512</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G56" t="n">
-        <v>12.7044496536255</v>
+        <v>12.7044506072998</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G59" t="n">
-        <v>12.7467708587646</v>
+        <v>12.7467699050903</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G60" t="n">
-        <v>12.3320360183716</v>
+        <v>12.3320341110229</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G61" t="n">
-        <v>12.882194519043</v>
+        <v>12.8821954727173</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>13.0260829925537</v>
+        <v>13.0260820388794</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G63" t="n">
-        <v>12.8568019866943</v>
+        <v>12.8568029403687</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G64" t="n">
-        <v>12.9752979278564</v>
+        <v>12.9752998352051</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G65" t="n">
-        <v>12.7298421859741</v>
+        <v>12.7298431396484</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G66" t="n">
-        <v>12.8144845962524</v>
+        <v>12.8144836425781</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>15.25</v>
       </c>
       <c r="G67" t="n">
-        <v>12.9075860977173</v>
+        <v>12.9075870513916</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G68" t="n">
-        <v>12.6790590286255</v>
+        <v>12.6790580749512</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G69" t="n">
-        <v>13.1276502609253</v>
+        <v>13.1276512145996</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G70" t="n">
-        <v>13.212290763855</v>
+        <v>13.2122888565063</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G71" t="n">
-        <v>13.2207536697388</v>
+        <v>13.2207546234131</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>13.2715406417847</v>
+        <v>13.271538734436</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G74" t="n">
-        <v>13.5085296630859</v>
+        <v>13.5085287094116</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>16.75</v>
       </c>
       <c r="G76" t="n">
-        <v>14.1771850585938</v>
+        <v>14.1771831512451</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G77" t="n">
-        <v>14.3380002975464</v>
+        <v>14.3380012512207</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G78" t="n">
-        <v>14.4141788482666</v>
+        <v>14.4141798019409</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G79" t="n">
-        <v>14.1517934799194</v>
+        <v>14.1517925262451</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G80" t="n">
-        <v>13.9994421005249</v>
+        <v>13.9994440078735</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G81" t="n">
-        <v>13.9994421005249</v>
+        <v>13.9994440078735</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G83" t="n">
-        <v>14.1687211990356</v>
+        <v>14.16872215271</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G84" t="n">
-        <v>13.9994421005249</v>
+        <v>13.9994440078735</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>14.0079050064087</v>
+        <v>14.007905960083</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>13.8724822998047</v>
+        <v>13.8724803924561</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G87" t="n">
-        <v>13.9063396453857</v>
+        <v>13.9063386917114</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G90" t="n">
-        <v>13.7285928726196</v>
+        <v>13.7285919189453</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>14.2618265151978</v>
+        <v>14.2618255615234</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G92" t="n">
-        <v>14.2872161865234</v>
+        <v>14.2872180938721</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>14.0502262115479</v>
+        <v>14.0502243041992</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G95" t="n">
-        <v>14.4141788482666</v>
+        <v>14.4141798019409</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>14.5157432556152</v>
+        <v>14.5157442092896</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G98" t="n">
-        <v>14.5496025085449</v>
+        <v>14.5496015548706</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G99" t="n">
-        <v>14.6511688232422</v>
+        <v>14.6511697769165</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G100" t="n">
-        <v>14.6724233627319</v>
+        <v>14.672420501709</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G101" t="n">
-        <v>14.8679399490356</v>
+        <v>14.8679418563843</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G102" t="n">
-        <v>15.0974636077881</v>
+        <v>15.0974617004395</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G103" t="n">
-        <v>15.1739702224731</v>
+        <v>15.1739692687988</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G104" t="n">
-        <v>15.4884986877441</v>
+        <v>15.4885005950928</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G106" t="n">
-        <v>15.1824722290039</v>
+        <v>15.1824703216553</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G107" t="n">
-        <v>15.2334766387939</v>
+        <v>15.2334756851196</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G108" t="n">
-        <v>15.1824722290039</v>
+        <v>15.1824703216553</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G109" t="n">
-        <v>14.9699535369873</v>
+        <v>14.9699506759644</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G110" t="n">
-        <v>15.1824722290039</v>
+        <v>15.1824703216553</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>15.3439855575562</v>
+        <v>15.3439884185791</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G112" t="n">
-        <v>15.1994724273682</v>
+        <v>15.1994705200195</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G115" t="n">
-        <v>13.745831489563</v>
+        <v>13.7458324432373</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G117" t="n">
-        <v>13.4993076324463</v>
+        <v>13.499306678772</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>14.4173965454102</v>
+        <v>14.4173955917358</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G124" t="n">
-        <v>13.2442827224731</v>
+        <v>13.2442846298218</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G125" t="n">
-        <v>12.3091907501221</v>
+        <v>12.3091917037964</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>12.6662282943726</v>
+        <v>12.6662263870239</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G127" t="n">
-        <v>12.6832275390625</v>
+        <v>12.6832294464111</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3292932510376</v>
+        <v>13.329291343689</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G129" t="n">
-        <v>13.8478422164917</v>
+        <v>13.847843170166</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G131" t="n">
-        <v>13.3717947006226</v>
+        <v>13.3717956542969</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G132" t="n">
-        <v>12.9892578125</v>
+        <v>12.9892597198486</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G134" t="n">
-        <v>13.3972978591919</v>
+        <v>13.3972969055176</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G135" t="n">
-        <v>14.0178594589233</v>
+        <v>14.017858505249</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G136" t="n">
-        <v>14.1793737411499</v>
+        <v>14.1793746948242</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>14.6214170455933</v>
+        <v>14.6214179992676</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>14.5024032592773</v>
+        <v>14.5024042129517</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G140" t="n">
-        <v>14.6724233627319</v>
+        <v>14.672420501709</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>17.25</v>
       </c>
       <c r="G141" t="n">
-        <v>14.6639204025269</v>
+        <v>14.6639232635498</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>14.6724233627319</v>
+        <v>14.672420501709</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G143" t="n">
-        <v>14.8169326782227</v>
+        <v>14.8169374465942</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G144" t="n">
-        <v>14.9529466629028</v>
+        <v>14.9529495239258</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>15.0464601516724</v>
+        <v>15.0464582443237</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G147" t="n">
-        <v>15.2249765396118</v>
+        <v>15.2249746322632</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>17.75</v>
       </c>
       <c r="G148" t="n">
-        <v>15.0889625549316</v>
+        <v>15.088963508606</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G149" t="n">
-        <v>15.2334766387939</v>
+        <v>15.2334756851196</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>15.1739702224731</v>
+        <v>15.1739692687988</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G151" t="n">
-        <v>14.8594388961792</v>
+        <v>14.8594408035278</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>15.1484680175781</v>
+        <v>15.1484670639038</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G153" t="n">
-        <v>15.3524885177612</v>
+        <v>15.3524875640869</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G154" t="n">
-        <v>15.4629983901978</v>
+        <v>15.4629974365234</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G155" t="n">
-        <v>15.6925182342529</v>
+        <v>15.6925210952759</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G157" t="n">
-        <v>15.973048210144</v>
+        <v>15.9730472564697</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>16.6616134643555</v>
+        <v>16.6616153717041</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>16.4065914154053</v>
+        <v>16.406587600708</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G161" t="n">
-        <v>16.2450733184814</v>
+        <v>16.2450752258301</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G163" t="n">
-        <v>15.9985513687134</v>
+        <v>15.9985494613647</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G167" t="n">
-        <v>16.2450733184814</v>
+        <v>16.2450752258301</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G168" t="n">
-        <v>16.3300819396973</v>
+        <v>16.3300800323486</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>19.0900001525879</v>
       </c>
       <c r="G169" t="n">
-        <v>16.2280693054199</v>
+        <v>16.2280731201172</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G170" t="n">
-        <v>16.6021099090576</v>
+        <v>16.6021118164062</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>16.3045825958252</v>
+        <v>16.3045806884766</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G173" t="n">
-        <v>16.4490928649902</v>
+        <v>16.4490909576416</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G174" t="n">
-        <v>16.0920581817627</v>
+        <v>16.0920600891113</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G175" t="n">
-        <v>16.1345653533936</v>
+        <v>16.1345634460449</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G177" t="n">
-        <v>15.6755199432373</v>
+        <v>15.6755180358887</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>15.2589797973633</v>
+        <v>15.258978843689</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G180" t="n">
-        <v>14.7319297790527</v>
+        <v>14.7319259643555</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>15.2164735794067</v>
+        <v>15.2164764404297</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G182" t="n">
-        <v>15.4459934234619</v>
+        <v>15.4459981918335</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>15.2249765396118</v>
+        <v>15.2249746322632</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G184" t="n">
-        <v>15.3949928283691</v>
+        <v>15.3949890136719</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G185" t="n">
-        <v>15.3099842071533</v>
+        <v>15.3099870681763</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>15.0464601516724</v>
+        <v>15.0464582443237</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G187" t="n">
-        <v>15.3864898681641</v>
+        <v>15.386492729187</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>15.2929801940918</v>
+        <v>15.2929811477661</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>18</v>
       </c>
       <c r="G189" t="n">
-        <v>15.3014812469482</v>
+        <v>15.3014793395996</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G190" t="n">
-        <v>15.1229677200317</v>
+        <v>15.1229648590088</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G191" t="n">
-        <v>15.6160135269165</v>
+        <v>15.6160144805908</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G192" t="n">
-        <v>15.4629983901978</v>
+        <v>15.4629974365234</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>18.25</v>
       </c>
       <c r="G193" t="n">
-        <v>15.5140037536621</v>
+        <v>15.5140027999878</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G194" t="n">
-        <v>15.3779897689819</v>
+        <v>15.3779888153076</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>15.2164735794067</v>
+        <v>15.2164764404297</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>15.3864898681641</v>
+        <v>15.386492729187</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G197" t="n">
-        <v>15.5650100708008</v>
+        <v>15.5650110244751</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G198" t="n">
-        <v>15.3099842071533</v>
+        <v>15.3099870681763</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G199" t="n">
-        <v>15.4545001983643</v>
+        <v>15.4544973373413</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>15.3524885177612</v>
+        <v>15.3524875640869</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.75</v>
       </c>
       <c r="G201" t="n">
-        <v>15.0889625549316</v>
+        <v>15.088963508606</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G203" t="n">
-        <v>15.2844800949097</v>
+        <v>15.2844829559326</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>18</v>
       </c>
       <c r="G204" t="n">
-        <v>15.3014812469482</v>
+        <v>15.3014793395996</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G205" t="n">
-        <v>15.4459934234619</v>
+        <v>15.4459981918335</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>15.3269882202148</v>
+        <v>15.3269872665405</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>15.3099842071533</v>
+        <v>15.3099870681763</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G208" t="n">
-        <v>15.5055027008057</v>
+        <v>15.5054998397827</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G209" t="n">
-        <v>15.5055027008057</v>
+        <v>15.5054998397827</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G210" t="n">
-        <v>15.3184823989868</v>
+        <v>15.3184843063354</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G211" t="n">
-        <v>15.1569671630859</v>
+        <v>15.1569690704346</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G212" t="n">
-        <v>14.9699535369873</v>
+        <v>14.9699506759644</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G214" t="n">
-        <v>15.0634574890137</v>
+        <v>15.0634565353394</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G215" t="n">
-        <v>14.7999353408813</v>
+        <v>14.7999334335327</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G217" t="n">
-        <v>15.0209550857544</v>
+        <v>15.0209522247314</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G218" t="n">
-        <v>15.0549573898315</v>
+        <v>15.0549602508545</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G220" t="n">
-        <v>15.3184823989868</v>
+        <v>15.3184843063354</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G221" t="n">
-        <v>16.5426006317139</v>
+        <v>16.5426025390625</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G222" t="n">
-        <v>16.7636241912842</v>
+        <v>16.7636222839355</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G223" t="n">
-        <v>16.3215808868408</v>
+        <v>16.3215827941895</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G225" t="n">
-        <v>17.137659072876</v>
+        <v>17.1376609802246</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>20.5</v>
       </c>
       <c r="G227" t="n">
-        <v>17.4266910552979</v>
+        <v>17.426685333252</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>20.25</v>
       </c>
       <c r="G228" t="n">
-        <v>17.2141666412354</v>
+        <v>17.214168548584</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G230" t="n">
-        <v>17.0356502532959</v>
+        <v>17.0356483459473</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G232" t="n">
-        <v>17.3331775665283</v>
+        <v>17.333179473877</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>17.1716632843018</v>
+        <v>17.171667098999</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G235" t="n">
-        <v>16.7466220855713</v>
+        <v>16.7466239929199</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>17.0441493988037</v>
+        <v>17.0441513061523</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G237" t="n">
-        <v>16.9251384735107</v>
+        <v>16.9251403808594</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G238" t="n">
-        <v>16.9251384735107</v>
+        <v>16.9251403808594</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G239" t="n">
-        <v>17.673210144043</v>
+        <v>17.6732120513916</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G240" t="n">
-        <v>18.2597675323486</v>
+        <v>18.2597694396973</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G241" t="n">
-        <v>18.8463287353516</v>
+        <v>18.8463268280029</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G242" t="n">
-        <v>18.9398365020752</v>
+        <v>18.9398326873779</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>22</v>
       </c>
       <c r="G244" t="n">
-        <v>18.7018165588379</v>
+        <v>18.701810836792</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>18.531795501709</v>
+        <v>18.5317935943604</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>18.2342681884766</v>
+        <v>18.2342643737793</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>22.3899993896484</v>
       </c>
       <c r="G247" t="n">
-        <v>19.0333442687988</v>
+        <v>19.0333423614502</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G248" t="n">
-        <v>18.7188110351562</v>
+        <v>18.7188148498535</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G249" t="n">
-        <v>18.9653396606445</v>
+        <v>18.9653377532959</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G251" t="n">
-        <v>19.2883701324463</v>
+        <v>19.2883682250977</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>22.5</v>
       </c>
       <c r="G253" t="n">
-        <v>19.1268520355225</v>
+        <v>19.1268539428711</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>22.6700000762939</v>
       </c>
       <c r="G255" t="n">
-        <v>19.2713642120361</v>
+        <v>19.2713661193848</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G257" t="n">
-        <v>19.1353569030762</v>
+        <v>19.1353511810303</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9939346313477</v>
+        <v>19.9939365386963</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G260" t="n">
-        <v>19.4328842163086</v>
+        <v>19.43288230896</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>22.9099998474121</v>
       </c>
       <c r="G261" t="n">
-        <v>19.4753856658936</v>
+        <v>19.4753875732422</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G262" t="n">
-        <v>19.7389144897461</v>
+        <v>19.7389106750488</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>23</v>
       </c>
       <c r="G263" t="n">
-        <v>19.5518989562988</v>
+        <v>19.5518951416016</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>19.806921005249</v>
+        <v>19.8069171905518</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>23.7900009155273</v>
       </c>
       <c r="G265" t="n">
-        <v>20.223461151123</v>
+        <v>20.2234592437744</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>24.0900001525879</v>
       </c>
       <c r="G267" t="n">
-        <v>20.4784851074219</v>
+        <v>20.4784870147705</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>23.6100006103516</v>
       </c>
       <c r="G269" t="n">
-        <v>20.0704441070557</v>
+        <v>20.0704460144043</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>19.4668846130371</v>
+        <v>19.4668865203857</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>19.8919258117676</v>
+        <v>19.8919277191162</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>19.8919258117676</v>
+        <v>19.8919277191162</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>23.75</v>
       </c>
       <c r="G274" t="n">
-        <v>20.189453125</v>
+        <v>20.1894569396973</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>24.0900001525879</v>
       </c>
       <c r="G275" t="n">
-        <v>20.4784851074219</v>
+        <v>20.4784870147705</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>19.3818759918213</v>
+        <v>19.3818740844727</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G280" t="n">
-        <v>19.7899188995361</v>
+        <v>19.7899169921875</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G281" t="n">
-        <v>19.9429302215576</v>
+        <v>19.9429321289062</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>23.2299995422363</v>
       </c>
       <c r="G282" t="n">
-        <v>19.7474136352539</v>
+        <v>19.7474117279053</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>19.4668846130371</v>
+        <v>19.4668865203857</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G286" t="n">
-        <v>19.3478736877441</v>
+        <v>19.3478755950928</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>19.8749237060547</v>
+        <v>19.874927520752</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G290" t="n">
-        <v>20.4274768829346</v>
+        <v>20.4274806976318</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>19.8919258117676</v>
+        <v>19.8919277191162</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G293" t="n">
-        <v>20.1299533843994</v>
+        <v>20.1299514770508</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G296" t="n">
-        <v>19.7899188995361</v>
+        <v>19.7899169921875</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G297" t="n">
-        <v>19.3308753967285</v>
+        <v>19.3308715820312</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G298" t="n">
-        <v>19.9429302215576</v>
+        <v>19.9429321289062</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>19.8749237060547</v>
+        <v>19.874927520752</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G300" t="n">
-        <v>20.4699840545654</v>
+        <v>20.4699802398682</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G301" t="n">
-        <v>20.6059989929199</v>
+        <v>20.6059970855713</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>20.6059989929199</v>
+        <v>20.6059970855713</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>20.1044445037842</v>
+        <v>20.1044502258301</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>23.5300006866455</v>
       </c>
       <c r="G304" t="n">
-        <v>20.0024356842041</v>
+        <v>20.00244140625</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G305" t="n">
-        <v>20.1129493713379</v>
+        <v>20.1129455566406</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>23.3600006103516</v>
       </c>
       <c r="G307" t="n">
-        <v>19.8579254150391</v>
+        <v>19.8579216003418</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.806921005249</v>
+        <v>19.8069171905518</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7219104766846</v>
+        <v>19.7219142913818</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G311" t="n">
-        <v>20.2489643096924</v>
+        <v>20.2489624023438</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9089317321777</v>
+        <v>19.9089298248291</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>23.3600006103516</v>
       </c>
       <c r="G315" t="n">
-        <v>19.8579254150391</v>
+        <v>19.8579216003418</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>20.3169689178467</v>
+        <v>20.3169708251953</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G317" t="n">
-        <v>19.9939346313477</v>
+        <v>19.9939365386963</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>22.75</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3393726348877</v>
+        <v>19.3393745422363</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>18.9993381500244</v>
+        <v>18.999340057373</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G320" t="n">
-        <v>19.1523513793945</v>
+        <v>19.1523551940918</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7899188995361</v>
+        <v>19.7899169921875</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>20.2319583892822</v>
+        <v>20.2319564819336</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G324" t="n">
-        <v>20.1299533843994</v>
+        <v>20.1299514770508</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>23.0699996948242</v>
       </c>
       <c r="G326" t="n">
-        <v>19.6113986968994</v>
+        <v>19.611400604248</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G327" t="n">
-        <v>19.6624050140381</v>
+        <v>19.6624031066895</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>19.4073791503906</v>
+        <v>19.4073829650879</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G331" t="n">
-        <v>18.8038196563721</v>
+        <v>18.8038215637207</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G333" t="n">
-        <v>18.6678066253662</v>
+        <v>18.6678085327148</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>19.2968673706055</v>
+        <v>19.296875</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>23.5300006866455</v>
       </c>
       <c r="G336" t="n">
-        <v>20.0024356842041</v>
+        <v>20.00244140625</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>23.7299995422363</v>
       </c>
       <c r="G337" t="n">
-        <v>20.1724586486816</v>
+        <v>20.1724548339844</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G338" t="n">
-        <v>20.1469497680664</v>
+        <v>20.1469554901123</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>23.6299991607666</v>
       </c>
       <c r="G339" t="n">
-        <v>20.0874462127686</v>
+        <v>20.0874443054199</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>20.0619449615479</v>
+        <v>20.0619430541992</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>20.3169689178467</v>
+        <v>20.3169708251953</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>20.0619449615479</v>
+        <v>20.0619430541992</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G343" t="n">
-        <v>20.7675113677979</v>
+        <v>20.7675094604492</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G344" t="n">
-        <v>21.1415500640869</v>
+        <v>21.1415481567383</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G345" t="n">
-        <v>20.7760124206543</v>
+        <v>20.7760105133057</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G346" t="n">
-        <v>20.6654987335205</v>
+        <v>20.6655025482178</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G347" t="n">
-        <v>21.0225372314453</v>
+        <v>21.0225353240967</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G348" t="n">
-        <v>20.9205265045166</v>
+        <v>20.9205284118652</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>20.486988067627</v>
+        <v>20.4869842529297</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>23.6900005340576</v>
       </c>
       <c r="G351" t="n">
-        <v>20.1384525299072</v>
+        <v>20.1384506225586</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G353" t="n">
-        <v>19.0503425598145</v>
+        <v>19.0503482818604</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G354" t="n">
-        <v>19.7219104766846</v>
+        <v>19.7219142913818</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>23</v>
       </c>
       <c r="G355" t="n">
-        <v>19.6365356445312</v>
+        <v>19.6365337371826</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G357" t="n">
-        <v>19.6279964447021</v>
+        <v>19.6279983520508</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>23</v>
       </c>
       <c r="G359" t="n">
-        <v>19.6365356445312</v>
+        <v>19.6365337371826</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G361" t="n">
-        <v>19.7133750915527</v>
+        <v>19.7133731842041</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G362" t="n">
-        <v>19.7304496765137</v>
+        <v>19.730447769165</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G363" t="n">
-        <v>19.8841285705566</v>
+        <v>19.884126663208</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>23</v>
       </c>
       <c r="G365" t="n">
-        <v>19.6365356445312</v>
+        <v>19.6365337371826</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G368" t="n">
-        <v>19.6279964447021</v>
+        <v>19.6279983520508</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>19.8585147857666</v>
+        <v>19.858512878418</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>19.7645988464355</v>
+        <v>19.7646007537842</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G371" t="n">
-        <v>20.234167098999</v>
+        <v>20.2341690063477</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G373" t="n">
-        <v>19.1925792694092</v>
+        <v>19.1925811767578</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G374" t="n">
-        <v>19.3291797637939</v>
+        <v>19.3291778564453</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G375" t="n">
-        <v>19.4487075805664</v>
+        <v>19.448709487915</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G377" t="n">
-        <v>19.4401702880859</v>
+        <v>19.4401683807373</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G378" t="n">
-        <v>19.175500869751</v>
+        <v>19.1755027770996</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G379" t="n">
-        <v>18.9449882507324</v>
+        <v>18.9449901580811</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G381" t="n">
-        <v>18.8766860961914</v>
+        <v>18.87668800354</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G384" t="n">
-        <v>18.6034851074219</v>
+        <v>18.6034832000732</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G386" t="n">
-        <v>19.2181949615479</v>
+        <v>19.2181911468506</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>19.1669673919678</v>
+        <v>19.1669654846191</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>22.5</v>
       </c>
       <c r="G389" t="n">
-        <v>19.2096538543701</v>
+        <v>19.2096557617188</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G391" t="n">
-        <v>19.2608814239502</v>
+        <v>19.2608795166016</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G393" t="n">
-        <v>19.4487075805664</v>
+        <v>19.448709487915</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>22.6100006103516</v>
       </c>
       <c r="G394" t="n">
-        <v>19.3035678863525</v>
+        <v>19.3035697937012</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>19.1669673919678</v>
+        <v>19.1669654846191</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G397" t="n">
-        <v>18.7230110168457</v>
+        <v>18.7230072021484</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G398" t="n">
-        <v>19.0303630828857</v>
+        <v>19.0303649902344</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G399" t="n">
-        <v>18.5522537231445</v>
+        <v>18.5522575378418</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>18.8681468963623</v>
+        <v>18.8681488037109</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G402" t="n">
-        <v>18.671781539917</v>
+        <v>18.6717834472656</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G404" t="n">
-        <v>18.1680641174316</v>
+        <v>18.168062210083</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>18.2705173492432</v>
+        <v>18.2705135345459</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G410" t="n">
-        <v>18.210750579834</v>
+        <v>18.2107486724854</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G413" t="n">
-        <v>17.3313770294189</v>
+        <v>17.3313751220703</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>17.1179332733154</v>
+        <v>17.1179351806641</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G415" t="n">
-        <v>17.3826007843018</v>
+        <v>17.3826026916504</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>17.5448207855225</v>
+        <v>17.5448169708252</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>17.3313770294189</v>
+        <v>17.3313751220703</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G422" t="n">
-        <v>17.1862354278564</v>
+        <v>17.1862373352051</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G423" t="n">
-        <v>16.827657699585</v>
+        <v>16.8276557922363</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G428" t="n">
-        <v>17.5960426330566</v>
+        <v>17.5960464477539</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G429" t="n">
-        <v>17.6216526031494</v>
+        <v>17.621654510498</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G430" t="n">
-        <v>17.68141746521</v>
+        <v>17.6814155578613</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G431" t="n">
-        <v>17.68141746521</v>
+        <v>17.6814155578613</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G432" t="n">
-        <v>17.860710144043</v>
+        <v>17.8607120513916</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G433" t="n">
-        <v>17.8265590667725</v>
+        <v>17.8265571594238</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G435" t="n">
-        <v>18.1339111328125</v>
+        <v>18.1339130401611</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>21.5300006866455</v>
       </c>
       <c r="G436" t="n">
-        <v>18.3815002441406</v>
+        <v>18.3815040588379</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G437" t="n">
-        <v>18.210750579834</v>
+        <v>18.2107486724854</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>18.3132057189941</v>
+        <v>18.3132038116455</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>18.2278289794922</v>
+        <v>18.2278308868408</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G442" t="n">
-        <v>19.7475242614746</v>
+        <v>19.7475204467773</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G443" t="n">
-        <v>19.4401702880859</v>
+        <v>19.4401683807373</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G444" t="n">
-        <v>19.0901260375977</v>
+        <v>19.0901279449463</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>19.3804054260254</v>
+        <v>19.3804092407227</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G447" t="n">
-        <v>19.3291797637939</v>
+        <v>19.3291778564453</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G448" t="n">
-        <v>19.4999332427979</v>
+        <v>19.4999313354492</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G449" t="n">
-        <v>19.7475242614746</v>
+        <v>19.7475204467773</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G450" t="n">
-        <v>19.5340843200684</v>
+        <v>19.5340805053711</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G453" t="n">
-        <v>19.2779541015625</v>
+        <v>19.2779521942139</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G454" t="n">
-        <v>19.397481918335</v>
+        <v>19.3974800109863</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G455" t="n">
-        <v>19.3889465332031</v>
+        <v>19.3889446258545</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G456" t="n">
-        <v>19.7133750915527</v>
+        <v>19.7133731842041</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G461" t="n">
-        <v>19.8670539855957</v>
+        <v>19.8670482635498</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G465" t="n">
-        <v>20.3536949157715</v>
+        <v>20.3536930084229</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G473" t="n">
-        <v>19.8841285705566</v>
+        <v>19.884126663208</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>23</v>
       </c>
       <c r="G474" t="n">
-        <v>19.6365356445312</v>
+        <v>19.6365337371826</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G475" t="n">
-        <v>19.4572448730469</v>
+        <v>19.4572467803955</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G477" t="n">
-        <v>19.7133750915527</v>
+        <v>19.7133731842041</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>23</v>
       </c>
       <c r="G478" t="n">
-        <v>19.6365356445312</v>
+        <v>19.6365337371826</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>22.75</v>
       </c>
       <c r="G479" t="n">
-        <v>19.4230918884277</v>
+        <v>19.423095703125</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G481" t="n">
-        <v>18.8169231414795</v>
+        <v>18.8169250488281</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G483" t="n">
-        <v>19.4743156433105</v>
+        <v>19.4743194580078</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>20.0207290649414</v>
+        <v>20.0207271575928</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G488" t="n">
-        <v>19.4401702880859</v>
+        <v>19.4401683807373</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G491" t="n">
-        <v>19.1925792694092</v>
+        <v>19.1925811767578</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>19.0815906524658</v>
+        <v>19.0815887451172</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G493" t="n">
-        <v>18.5522537231445</v>
+        <v>18.5522575378418</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G494" t="n">
-        <v>19.4572448730469</v>
+        <v>19.4572467803955</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G495" t="n">
-        <v>19.4401702880859</v>
+        <v>19.4401683807373</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G496" t="n">
-        <v>19.0815906524658</v>
+        <v>19.0815887451172</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>19.0815906524658</v>
+        <v>19.0815887451172</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>19.0559787750244</v>
+        <v>19.0559768676758</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>19.0559787750244</v>
+        <v>19.0559768676758</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>22</v>
       </c>
       <c r="G503" t="n">
-        <v>18.7827758789062</v>
+        <v>18.782772064209</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G505" t="n">
-        <v>19.0559787750244</v>
+        <v>19.0559768676758</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G506" t="n">
-        <v>18.7230110168457</v>
+        <v>18.7230072021484</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>19.6194591522217</v>
+        <v>19.6194610595703</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>22.9400005340576</v>
       </c>
       <c r="G510" t="n">
-        <v>19.5853080749512</v>
+        <v>19.5853099822998</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>22.5</v>
       </c>
       <c r="G511" t="n">
-        <v>19.2096538543701</v>
+        <v>19.2096557617188</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G513" t="n">
-        <v>19.7902088165283</v>
+        <v>19.7902126312256</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G517" t="n">
-        <v>20.7805767059326</v>
+        <v>20.7805786132812</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G518" t="n">
-        <v>20.712272644043</v>
+        <v>20.7122745513916</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G519" t="n">
-        <v>20.4732227325439</v>
+        <v>20.4732246398926</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>20.5756778717041</v>
+        <v>20.5756721496582</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G521" t="n">
-        <v>20.3366222381592</v>
+        <v>20.3366184234619</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G528" t="n">
-        <v>20.3195457458496</v>
+        <v>20.319543838501</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G529" t="n">
-        <v>20.4219932556152</v>
+        <v>20.4219989776611</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>20.8318042755127</v>
+        <v>20.8318023681641</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G531" t="n">
-        <v>20.8659534454346</v>
+        <v>20.8659515380859</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G532" t="n">
-        <v>20.5244464874268</v>
+        <v>20.5244483947754</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>20.191478729248</v>
+        <v>20.1914806365967</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G534" t="n">
-        <v>20.1146430969238</v>
+        <v>20.1146411895752</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>23.0100002288818</v>
       </c>
       <c r="G535" t="n">
-        <v>19.6450729370117</v>
+        <v>19.6450748443604</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>18.8681468963623</v>
+        <v>18.8681488037109</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G538" t="n">
-        <v>18.9022979736328</v>
+        <v>18.9022960662842</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G539" t="n">
-        <v>17.7326469421387</v>
+        <v>17.73264503479</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G542" t="n">
-        <v>17.6899528503418</v>
+        <v>17.6899585723877</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G543" t="n">
-        <v>17.8948574066162</v>
+        <v>17.8948593139648</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G545" t="n">
-        <v>18.2022132873535</v>
+        <v>18.2022151947021</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>17.971700668335</v>
+        <v>17.9716987609863</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G547" t="n">
-        <v>18.6290950775146</v>
+        <v>18.629093170166</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G548" t="n">
-        <v>18.5095691680908</v>
+        <v>18.5095710754395</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>18.0997657775879</v>
+        <v>18.0997638702393</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G551" t="n">
-        <v>17.7070331573486</v>
+        <v>17.7070293426514</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>17.6984901428223</v>
+        <v>17.6984958648682</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>17.3313770294189</v>
+        <v>17.3313751220703</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>19.8549995422363</v>
       </c>
       <c r="G555" t="n">
-        <v>16.9514541625977</v>
+        <v>16.9514503479004</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G556" t="n">
-        <v>17.1862354278564</v>
+        <v>17.1862373352051</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G557" t="n">
-        <v>17.9033966064453</v>
+        <v>17.9033985137939</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G558" t="n">
-        <v>17.775333404541</v>
+        <v>17.7753314971924</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G559" t="n">
-        <v>18.1509876251221</v>
+        <v>18.1509895324707</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G560" t="n">
-        <v>18.279052734375</v>
+        <v>18.2790508270264</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G561" t="n">
-        <v>18.0741500854492</v>
+        <v>18.0741481781006</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G562" t="n">
-        <v>17.860710144043</v>
+        <v>17.8607120513916</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G563" t="n">
-        <v>17.3996753692627</v>
+        <v>17.39967918396</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G565" t="n">
-        <v>17.5448207855225</v>
+        <v>17.5448169708252</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G569" t="n">
-        <v>16.8746109008789</v>
+        <v>16.8746128082275</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G570" t="n">
-        <v>17.0667095184326</v>
+        <v>17.0667114257812</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>19.3549995422363</v>
       </c>
       <c r="G571" t="n">
-        <v>16.5245704650879</v>
+        <v>16.5245742797852</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G574" t="n">
-        <v>16.2300243377686</v>
+        <v>16.2300224304199</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G576" t="n">
-        <v>16.311128616333</v>
+        <v>16.3111324310303</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G578" t="n">
-        <v>16.6953239440918</v>
+        <v>16.6953258514404</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G579" t="n">
-        <v>16.3068618774414</v>
+        <v>16.3068599700928</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G582" t="n">
-        <v>16.6312885284424</v>
+        <v>16.6312923431396</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>19.7250003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>16.8404655456543</v>
+        <v>16.8404636383057</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G588" t="n">
-        <v>17.0923233032227</v>
+        <v>17.092321395874</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G590" t="n">
-        <v>17.5362854003906</v>
+        <v>17.5362796783447</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G592" t="n">
-        <v>17.7070331573486</v>
+        <v>17.7070293426514</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G594" t="n">
-        <v>17.8948574066162</v>
+        <v>17.8948593139648</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>18.1851348876953</v>
+        <v>18.1851367950439</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>18.3985767364502</v>
+        <v>18.3985805511475</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G597" t="n">
-        <v>18.7059326171875</v>
+        <v>18.7059345245361</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>18.8254623413086</v>
+        <v>18.8254585266113</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G600" t="n">
-        <v>19.3291797637939</v>
+        <v>19.3291778564453</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G606" t="n">
-        <v>19.1413516998291</v>
+        <v>19.1413536071777</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G607" t="n">
-        <v>18.7998485565186</v>
+        <v>18.7998504638672</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G610" t="n">
-        <v>18.610990524292</v>
+        <v>18.6109924316406</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G611" t="n">
-        <v>18.610990524292</v>
+        <v>18.6109924316406</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G613" t="n">
-        <v>17.9585762023926</v>
+        <v>17.9585781097412</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G614" t="n">
-        <v>17.3319110870361</v>
+        <v>17.3319149017334</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>17.5808601379395</v>
+        <v>17.5808620452881</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G620" t="n">
-        <v>18.2161083221436</v>
+        <v>18.2161102294922</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G624" t="n">
-        <v>18.1216831207275</v>
+        <v>18.1216793060303</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>18.113094329834</v>
+        <v>18.1130962371826</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G627" t="n">
-        <v>18.2504463195801</v>
+        <v>18.2504482269287</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G630" t="n">
-        <v>18.181770324707</v>
+        <v>18.1817722320557</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G631" t="n">
-        <v>17.6924610137939</v>
+        <v>17.6924629211426</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>17.769718170166</v>
+        <v>17.7697162628174</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G637" t="n">
-        <v>18.0186653137207</v>
+        <v>18.0186672210693</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>17.8212261199951</v>
+        <v>17.8212280273438</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G640" t="n">
-        <v>17.6752891540527</v>
+        <v>17.6752910614014</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>17.8727321624756</v>
+        <v>17.872730255127</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G644" t="n">
-        <v>18.1560173034668</v>
+        <v>18.1560134887695</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G645" t="n">
-        <v>17.769718170166</v>
+        <v>17.7697162628174</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G646" t="n">
-        <v>17.8212261199951</v>
+        <v>17.8212280273438</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G647" t="n">
-        <v>17.7954711914062</v>
+        <v>17.7954730987549</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G648" t="n">
-        <v>17.6752891540527</v>
+        <v>17.6752910614014</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G649" t="n">
-        <v>17.5894470214844</v>
+        <v>17.5894451141357</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G650" t="n">
-        <v>17.7182121276855</v>
+        <v>17.7182102203369</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>19.9150009155273</v>
       </c>
       <c r="G651" t="n">
-        <v>17.0958461761475</v>
+        <v>17.0958423614502</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>19.2049999237061</v>
       </c>
       <c r="G652" t="n">
-        <v>16.4863510131836</v>
+        <v>16.486349105835</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>19.1550006866455</v>
       </c>
       <c r="G653" t="n">
-        <v>16.4434299468994</v>
+        <v>16.4434280395508</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G654" t="n">
-        <v>16.5593166351318</v>
+        <v>16.5593185424805</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>16.6108245849609</v>
+        <v>16.6108264923096</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G658" t="n">
-        <v>16.3790454864502</v>
+        <v>16.3790435791016</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G660" t="n">
-        <v>16.0871734619141</v>
+        <v>16.0871772766113</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>18</v>
       </c>
       <c r="G661" t="n">
-        <v>15.4519271850586</v>
+        <v>15.4519309997559</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G663" t="n">
-        <v>15.2459058761597</v>
+        <v>15.2459030151367</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G664" t="n">
-        <v>15.6407861709595</v>
+        <v>15.6407880783081</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G665" t="n">
-        <v>15.5206060409546</v>
+        <v>15.5206031799316</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G666" t="n">
-        <v>15.3746700286865</v>
+        <v>15.3746719360352</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G667" t="n">
-        <v>15.168643951416</v>
+        <v>15.1686458587646</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>15.1085538864136</v>
+        <v>15.1085548400879</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G669" t="n">
-        <v>14.8596048355103</v>
+        <v>14.8596067428589</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>17.8349990844727</v>
       </c>
       <c r="G670" t="n">
-        <v>15.3102884292603</v>
+        <v>15.3102874755859</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>17.6949996948242</v>
       </c>
       <c r="G671" t="n">
-        <v>15.1901073455811</v>
+        <v>15.1901063919067</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>15.3660869598389</v>
+        <v>15.3660850524902</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>17.8950004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>15.3617973327637</v>
+        <v>15.3617935180664</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6922941207886</v>
+        <v>15.6922931671143</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>18.2150001525879</v>
       </c>
       <c r="G677" t="n">
-        <v>15.63649559021</v>
+        <v>15.636492729187</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.3231658935547</v>
+        <v>15.3231649398804</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G679" t="n">
-        <v>15.5206060409546</v>
+        <v>15.5206031799316</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>17.6749992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>15.1729354858398</v>
+        <v>15.1729345321655</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G682" t="n">
-        <v>14.8853607177734</v>
+        <v>14.8853597640991</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G683" t="n">
-        <v>14.8638982772827</v>
+        <v>14.863899230957</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>17.625</v>
       </c>
       <c r="G684" t="n">
-        <v>15.1300134658813</v>
+        <v>15.13001537323</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G685" t="n">
-        <v>15.1171388626099</v>
+        <v>15.1171407699585</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G686" t="n">
-        <v>15.0184202194214</v>
+        <v>15.0184144973755</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G687" t="n">
-        <v>15.18581199646</v>
+        <v>15.1858129501343</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G688" t="n">
-        <v>15.0956773757935</v>
+        <v>15.0956745147705</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G689" t="n">
-        <v>15.357497215271</v>
+        <v>15.3575019836426</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>17.6949996948242</v>
       </c>
       <c r="G691" t="n">
-        <v>15.1901073455811</v>
+        <v>15.1901063919067</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>17.8150005340576</v>
       </c>
       <c r="G692" t="n">
-        <v>15.2931184768677</v>
+        <v>15.293116569519</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>18.5149993896484</v>
       </c>
       <c r="G693" t="n">
-        <v>15.894024848938</v>
+        <v>15.8940277099609</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G694" t="n">
-        <v>16.2416934967041</v>
+        <v>16.2416954040527</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G695" t="n">
-        <v>16.3189544677734</v>
+        <v>16.3189563751221</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>18.7849998474121</v>
       </c>
       <c r="G697" t="n">
-        <v>16.125804901123</v>
+        <v>16.1258029937744</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G699" t="n">
-        <v>15.9798707962036</v>
+        <v>15.9798679351807</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>18.5450000762939</v>
       </c>
       <c r="G700" t="n">
-        <v>15.9197788238525</v>
+        <v>15.9197778701782</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G701" t="n">
-        <v>15.348916053772</v>
+        <v>15.3489141464233</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G704" t="n">
-        <v>15.8639812469482</v>
+        <v>15.8639793395996</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G705" t="n">
-        <v>15.932653427124</v>
+        <v>15.9326553344727</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G708" t="n">
-        <v>15.4733905792236</v>
+        <v>15.4733877182007</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>15.2330284118652</v>
+        <v>15.2330293655396</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>17.8549995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>15.3274564743042</v>
+        <v>15.3274555206299</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>17.5750007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>15.0870923995972</v>
+        <v>15.0870933532715</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>16.2350006103516</v>
       </c>
       <c r="G715" t="n">
-        <v>13.9367828369141</v>
+        <v>13.9367837905884</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G716" t="n">
-        <v>13.6835432052612</v>
+        <v>13.6835422515869</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>16.0849990844727</v>
       </c>
       <c r="G717" t="n">
-        <v>13.8080158233643</v>
+        <v>13.8080148696899</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G719" t="n">
-        <v>13.4689321517944</v>
+        <v>13.4689311981201</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>15.9250001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>13.6706657409668</v>
+        <v>13.6706666946411</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>16.5</v>
       </c>
       <c r="G723" t="n">
-        <v>14.1642684936523</v>
+        <v>14.1642694473267</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>14.5720272064209</v>
+        <v>14.5720291137695</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G726" t="n">
-        <v>14.7737627029419</v>
+        <v>14.7737598419189</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G727" t="n">
-        <v>14.5119380950928</v>
+        <v>14.5119352340698</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>16.5949993133545</v>
       </c>
       <c r="G728" t="n">
-        <v>14.2458200454712</v>
+        <v>14.2458219528198</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G729" t="n">
-        <v>14.6836252212524</v>
+        <v>14.6836233139038</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G730" t="n">
-        <v>14.632119178772</v>
+        <v>14.6321182250977</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>17.0349998474121</v>
       </c>
       <c r="G731" t="n">
-        <v>14.62353515625</v>
+        <v>14.6235342025757</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G732" t="n">
-        <v>14.1299304962158</v>
+        <v>14.1299314498901</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>16.4249992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>14.0998849868774</v>
+        <v>14.0998868942261</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>16.875</v>
       </c>
       <c r="G734" t="n">
-        <v>14.4861850738525</v>
+        <v>14.4861841201782</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>13.992579460144</v>
+        <v>13.9925804138184</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>13.8380632400513</v>
+        <v>13.838062286377</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G737" t="n">
-        <v>13.7608041763306</v>
+        <v>13.7608032226562</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>16</v>
       </c>
       <c r="G738" t="n">
-        <v>13.7350473403931</v>
+        <v>13.7350482940674</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G739" t="n">
-        <v>14.0526742935181</v>
+        <v>14.0526733398438</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>16.0450000762939</v>
       </c>
       <c r="G740" t="n">
-        <v>13.7736787796021</v>
+        <v>13.7736778259277</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G741" t="n">
-        <v>14.0483798980713</v>
+        <v>14.0483808517456</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>17.0550003051758</v>
       </c>
       <c r="G742" t="n">
-        <v>14.6407032012939</v>
+        <v>14.6407041549683</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G743" t="n">
-        <v>14.4947690963745</v>
+        <v>14.4947700500488</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>14.4218006134033</v>
+        <v>14.4218015670776</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G748" t="n">
-        <v>14.4260940551758</v>
+        <v>14.4260950088501</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>12.9624538421631</v>
+        <v>12.9624528884888</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>13.2199831008911</v>
+        <v>13.2199850082397</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G754" t="n">
-        <v>13.2714900970459</v>
+        <v>13.2714910507202</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>15.1049995422363</v>
       </c>
       <c r="G755" t="n">
-        <v>12.9667444229126</v>
+        <v>12.966742515564</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G756" t="n">
-        <v>12.9710359573364</v>
+        <v>12.9710369110107</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>15.2849998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>13.1212644577026</v>
+        <v>13.1212635040283</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G761" t="n">
-        <v>12.9109449386597</v>
+        <v>12.910945892334</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>15.0249996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>12.8980693817139</v>
+        <v>12.8980684280396</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>15.1850004196167</v>
       </c>
       <c r="G764" t="n">
-        <v>13.0354194641113</v>
+        <v>13.0354204177856</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>15.2550001144409</v>
       </c>
       <c r="G766" t="n">
-        <v>13.0955114364624</v>
+        <v>13.0955095291138</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G768" t="n">
-        <v>13.4689321517944</v>
+        <v>13.4689311981201</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.2350006103516</v>
       </c>
       <c r="G769" t="n">
-        <v>13.9367828369141</v>
+        <v>13.9367837905884</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G770" t="n">
-        <v>13.8638153076172</v>
+        <v>13.8638134002686</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>13.6921262741089</v>
+        <v>13.6921253204346</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G772" t="n">
-        <v>13.6749572753906</v>
+        <v>13.6749591827393</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G774" t="n">
-        <v>14.1728544235229</v>
+        <v>14.1728534698486</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>16.3449993133545</v>
       </c>
       <c r="G775" t="n">
-        <v>14.0312099456787</v>
+        <v>14.031210899353</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G776" t="n">
-        <v>14.1728544235229</v>
+        <v>14.1728534698486</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>16.2849998474121</v>
       </c>
       <c r="G777" t="n">
-        <v>13.9797029495239</v>
+        <v>13.9797039031982</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G778" t="n">
-        <v>13.9153203964233</v>
+        <v>13.915319442749</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>16.0450000762939</v>
       </c>
       <c r="G779" t="n">
-        <v>13.7736787796021</v>
+        <v>13.7736778259277</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>16.7649993896484</v>
       </c>
       <c r="G782" t="n">
-        <v>14.3917551040649</v>
+        <v>14.3917560577393</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G785" t="n">
-        <v>14.3102045059204</v>
+        <v>14.3102035522461</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G787" t="n">
-        <v>14.4561367034912</v>
+        <v>14.4561386108398</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G788" t="n">
-        <v>14.4947690963745</v>
+        <v>14.4947700500488</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G789" t="n">
-        <v>14.4260940551758</v>
+        <v>14.4260950088501</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>14.0355043411255</v>
+        <v>14.0355033874512</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>16.5849990844727</v>
       </c>
       <c r="G793" t="n">
-        <v>14.2372369766235</v>
+        <v>14.2372360229492</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>14.2501134872437</v>
+        <v>14.250111579895</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G796" t="n">
-        <v>14.4303865432739</v>
+        <v>14.4303855895996</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G798" t="n">
-        <v>14.4990615844727</v>
+        <v>14.4990606307983</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>17.1149997711182</v>
       </c>
       <c r="G799" t="n">
-        <v>14.6922092437744</v>
+        <v>14.6922101974487</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>16.9850006103516</v>
       </c>
       <c r="G800" t="n">
-        <v>14.5806121826172</v>
+        <v>14.5806131362915</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G801" t="n">
-        <v>14.6836252212524</v>
+        <v>14.6836233139038</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G802" t="n">
-        <v>14.5677347183228</v>
+        <v>14.5677356719971</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>17.0349998474121</v>
       </c>
       <c r="G804" t="n">
-        <v>14.62353515625</v>
+        <v>14.6235342025757</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>14.7651777267456</v>
+        <v>14.7651767730713</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G807" t="n">
-        <v>14.9840784072876</v>
+        <v>14.9840822219849</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>17.4449996948242</v>
       </c>
       <c r="G808" t="n">
-        <v>14.9754934310913</v>
+        <v>14.9754953384399</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G811" t="n">
-        <v>14.3960475921631</v>
+        <v>14.3960485458374</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>17.1849994659424</v>
       </c>
       <c r="G813" t="n">
-        <v>14.7523021697998</v>
+        <v>14.7523002624512</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G815" t="n">
-        <v>14.9712028503418</v>
+        <v>14.9712018966675</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G817" t="n">
-        <v>15.1772289276123</v>
+        <v>15.1772298812866</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G819" t="n">
-        <v>15.4776830673218</v>
+        <v>15.4776821136475</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>15.1514759063721</v>
+        <v>15.1514739990234</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>15.0441722869873</v>
+        <v>15.0441703796387</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G823" t="n">
-        <v>14.9669103622437</v>
+        <v>14.9669075012207</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>17.5650005340576</v>
       </c>
       <c r="G824" t="n">
-        <v>15.0785102844238</v>
+        <v>15.0785093307495</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>18.2350006103516</v>
       </c>
       <c r="G826" t="n">
-        <v>15.6536674499512</v>
+        <v>15.6536655426025</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>16.4820575714111</v>
+        <v>16.4820594787598</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>16.3747520446777</v>
+        <v>16.3747539520264</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G831" t="n">
-        <v>16.3275394439697</v>
+        <v>16.3275413513184</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>16.336124420166</v>
+        <v>16.3361206054688</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>16.2245292663574</v>
+        <v>16.2245273590088</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G834" t="n">
-        <v>16.2159423828125</v>
+        <v>16.2159404754639</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G837" t="n">
-        <v>16.4133853912354</v>
+        <v>16.4133834838867</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G838" t="n">
-        <v>16.6194076538086</v>
+        <v>16.6194095611572</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.6108245849609</v>
+        <v>16.6108264923096</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>17.0400428771973</v>
+        <v>17.0400466918945</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>19.4150009155273</v>
       </c>
       <c r="G844" t="n">
-        <v>16.6666278839111</v>
+        <v>16.6666221618652</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>19.6350002288818</v>
       </c>
       <c r="G845" t="n">
-        <v>16.8554840087891</v>
+        <v>16.8554821014404</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>19.9150009155273</v>
       </c>
       <c r="G848" t="n">
-        <v>17.0958461761475</v>
+        <v>17.0958423614502</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>16.6966686248779</v>
+        <v>16.6966705322266</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.9249992370605</v>
       </c>
       <c r="G850" t="n">
-        <v>16.2459888458252</v>
+        <v>16.2459850311279</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G851" t="n">
-        <v>16.1472682952881</v>
+        <v>16.1472663879395</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G852" t="n">
-        <v>16.1644325256348</v>
+        <v>16.1644344329834</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>19.25</v>
       </c>
       <c r="G853" t="n">
-        <v>16.5249786376953</v>
+        <v>16.5249824523926</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G855" t="n">
-        <v>16.2588634490967</v>
+        <v>16.2588653564453</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>16.5035190582275</v>
+        <v>16.5035209655762</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>19.1350002288818</v>
       </c>
       <c r="G860" t="n">
-        <v>16.5331745147705</v>
+        <v>16.5331726074219</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>15.8981142044067</v>
+        <v>15.8981094360352</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>18.3150005340576</v>
       </c>
       <c r="G863" t="n">
-        <v>15.8246717453003</v>
+        <v>15.824667930603</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G865" t="n">
-        <v>15.6129865646362</v>
+        <v>15.6129837036133</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G867" t="n">
-        <v>15.6043434143066</v>
+        <v>15.6043424606323</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G869" t="n">
-        <v>15.0427265167236</v>
+        <v>15.042724609375</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>17.7549991607666</v>
       </c>
       <c r="G871" t="n">
-        <v>15.3408155441284</v>
+        <v>15.3408136367798</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G872" t="n">
-        <v>15.1809682846069</v>
+        <v>15.1809673309326</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G873" t="n">
-        <v>15.0859241485596</v>
+        <v>15.0859279632568</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>17.875</v>
       </c>
       <c r="G874" t="n">
-        <v>15.4444961547852</v>
+        <v>15.4444990158081</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G875" t="n">
-        <v>15.5093021392822</v>
+        <v>15.5093002319336</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>17.5</v>
       </c>
       <c r="G876" t="n">
-        <v>15.1204881668091</v>
+        <v>15.1204862594604</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>17.8950004577637</v>
       </c>
       <c r="G877" t="n">
-        <v>15.4617786407471</v>
+        <v>15.46178150177</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G878" t="n">
-        <v>15.4142599105835</v>
+        <v>15.4142580032349</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>17.8150005340576</v>
       </c>
       <c r="G879" t="n">
-        <v>15.3926582336426</v>
+        <v>15.3926572799683</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G880" t="n">
-        <v>15.479061126709</v>
+        <v>15.4790620803833</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G881" t="n">
-        <v>15.3451375961304</v>
+        <v>15.345139503479</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G882" t="n">
-        <v>15.4401798248291</v>
+        <v>15.4401760101318</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G883" t="n">
-        <v>15.1161689758301</v>
+        <v>15.1161670684814</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G884" t="n">
-        <v>15.0470476150513</v>
+        <v>15.0470457077026</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>17.6650009155273</v>
       </c>
       <c r="G885" t="n">
-        <v>15.2630548477173</v>
+        <v>15.2630529403687</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>18.0450000762939</v>
       </c>
       <c r="G886" t="n">
-        <v>15.5913848876953</v>
+        <v>15.5913820266724</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G887" t="n">
-        <v>15.5265789031982</v>
+        <v>15.5265808105469</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G888" t="n">
-        <v>15.4185791015625</v>
+        <v>15.4185771942139</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>15.4876985549927</v>
+        <v>15.4877014160156</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>15.6821088790894</v>
+        <v>15.6821069717407</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G892" t="n">
-        <v>16.148681640625</v>
+        <v>16.1486835479736</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G894" t="n">
-        <v>16.243724822998</v>
+        <v>16.2437229156494</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G896" t="n">
-        <v>16.2350826263428</v>
+        <v>16.23508644104</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>18.7150001525879</v>
       </c>
       <c r="G897" t="n">
-        <v>16.1702823638916</v>
+        <v>16.170280456543</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G899" t="n">
-        <v>16.4424476623535</v>
+        <v>16.4424514770508</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>16.5893383026123</v>
+        <v>16.5893363952637</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>19.2450008392334</v>
       </c>
       <c r="G901" t="n">
-        <v>16.6282196044922</v>
+        <v>16.6282176971436</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>19.0900001525879</v>
       </c>
       <c r="G903" t="n">
-        <v>16.4942932128906</v>
+        <v>16.494291305542</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>16.5461349487305</v>
+        <v>16.5461368560791</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G909" t="n">
-        <v>16.5115737915039</v>
+        <v>16.5115718841553</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>15.8981142044067</v>
+        <v>15.8981094360352</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G912" t="n">
-        <v>15.6043434143066</v>
+        <v>15.6043424606323</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>17.5650005340576</v>
       </c>
       <c r="G913" t="n">
-        <v>15.1766519546509</v>
+        <v>15.1766510009766</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G914" t="n">
-        <v>15.2328100204468</v>
+        <v>15.2328109741211</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>15.5741033554077</v>
+        <v>15.5741014480591</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>18.2950000762939</v>
       </c>
       <c r="G918" t="n">
-        <v>15.8073902130127</v>
+        <v>15.8073892593384</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>18.4150009155273</v>
       </c>
       <c r="G919" t="n">
-        <v>15.9110736846924</v>
+        <v>15.9110746383667</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G922" t="n">
-        <v>15.9067525863647</v>
+        <v>15.9067516326904</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G923" t="n">
-        <v>16.1573219299316</v>
+        <v>16.157320022583</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G924" t="n">
-        <v>15.6907472610474</v>
+        <v>15.6907482147217</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>18.6049995422363</v>
       </c>
       <c r="G926" t="n">
-        <v>16.0752410888672</v>
+        <v>16.0752391815186</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>18.4549999237061</v>
       </c>
       <c r="G927" t="n">
-        <v>15.9456348419189</v>
+        <v>15.9456377029419</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G929" t="n">
-        <v>16.4208488464355</v>
+        <v>16.4208469390869</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>18.4850006103516</v>
       </c>
       <c r="G930" t="n">
-        <v>15.9715538024902</v>
+        <v>15.9715576171875</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>18.8649997711182</v>
       </c>
       <c r="G931" t="n">
-        <v>16.2998867034912</v>
+        <v>16.2998847961426</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>19.0849990844727</v>
       </c>
       <c r="G932" t="n">
-        <v>16.48996925354</v>
+        <v>16.4899730682373</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G933" t="n">
-        <v>16.6238975524902</v>
+        <v>16.6238956451416</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>19.125</v>
       </c>
       <c r="G934" t="n">
-        <v>16.5245323181152</v>
+        <v>16.5245361328125</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>19.3549995422363</v>
       </c>
       <c r="G935" t="n">
-        <v>16.723258972168</v>
+        <v>16.7232627868652</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G936" t="n">
-        <v>16.6930198669434</v>
+        <v>16.6930179595947</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>19.6350002288818</v>
       </c>
       <c r="G938" t="n">
-        <v>16.9651889801025</v>
+        <v>16.9651870727539</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G939" t="n">
-        <v>17.14231300354</v>
+        <v>17.1423149108887</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>17.5397663116455</v>
+        <v>17.5397644042969</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G941" t="n">
-        <v>17.5916061401367</v>
+        <v>17.5916080474854</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G942" t="n">
-        <v>17.8076171875</v>
+        <v>17.8076152801514</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>20.75</v>
       </c>
       <c r="G946" t="n">
-        <v>17.9285774230957</v>
+        <v>17.9285793304443</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G948" t="n">
-        <v>17.3410415649414</v>
+        <v>17.3410377502441</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G949" t="n">
-        <v>17.1077537536621</v>
+        <v>17.1077499389648</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G950" t="n">
-        <v>17.2632789611816</v>
+        <v>17.263277053833</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G954" t="n">
-        <v>18.161865234375</v>
+        <v>18.1618671417236</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G955" t="n">
-        <v>17.267599105835</v>
+        <v>17.2675971984863</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G956" t="n">
-        <v>17.0904731750488</v>
+        <v>17.0904712677002</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>19.8299999237061</v>
       </c>
       <c r="G957" t="n">
-        <v>17.1336708068848</v>
+        <v>17.133674621582</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G959" t="n">
-        <v>17.1509532928467</v>
+        <v>17.1509552001953</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G960" t="n">
-        <v>17.4447231292725</v>
+        <v>17.4447250366211</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G961" t="n">
-        <v>17.9112968444824</v>
+        <v>17.9112987518311</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G965" t="n">
-        <v>18.7234840393066</v>
+        <v>18.723482131958</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>18.835807800293</v>
+        <v>18.8358058929443</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G967" t="n">
-        <v>18.9740505218506</v>
+        <v>18.9740524291992</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>18.835807800293</v>
+        <v>18.8358058929443</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G969" t="n">
-        <v>18.6457233428955</v>
+        <v>18.6457214355469</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G971" t="n">
-        <v>18.6802845001221</v>
+        <v>18.6802864074707</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G972" t="n">
-        <v>18.7753257751465</v>
+        <v>18.7753276824951</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>22</v>
       </c>
       <c r="G973" t="n">
-        <v>19.0086154937744</v>
+        <v>19.0086116790771</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G975" t="n">
-        <v>19.0690975189209</v>
+        <v>19.0690956115723</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G977" t="n">
-        <v>18.91357421875</v>
+        <v>18.9135723114014</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G978" t="n">
-        <v>19.1382179260254</v>
+        <v>19.1382160186768</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G979" t="n">
-        <v>18.9913349151611</v>
+        <v>18.9913330078125</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G980" t="n">
-        <v>18.8790092468262</v>
+        <v>18.8790111541748</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G981" t="n">
-        <v>19.172779083252</v>
+        <v>19.1727828979492</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>22.9099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>19.7948780059814</v>
+        <v>19.7948799133301</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>19.5702304840088</v>
+        <v>19.5702323913574</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G989" t="n">
-        <v>19.725757598877</v>
+        <v>19.7257556915283</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G990" t="n">
-        <v>20.0281677246094</v>
+        <v>20.0281658172607</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G992" t="n">
-        <v>19.613431930542</v>
+        <v>19.6134338378906</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G994" t="n">
-        <v>19.9849681854248</v>
+        <v>19.9849624633789</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G997" t="n">
-        <v>19.4233493804932</v>
+        <v>19.4233455657959</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G998" t="n">
-        <v>19.0258979797363</v>
+        <v>19.0258960723877</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G999" t="n">
-        <v>18.7666873931885</v>
+        <v>18.7666854858398</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G1000" t="n">
-        <v>19.4147090911865</v>
+        <v>19.4147071838379</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1001" t="n">
-        <v>19.1122970581055</v>
+        <v>19.1122989654541</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G1002" t="n">
-        <v>19.604793548584</v>
+        <v>19.6047916412354</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>22.2700004577637</v>
       </c>
       <c r="G1003" t="n">
-        <v>19.2419013977051</v>
+        <v>19.2418994903564</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.3283042907715</v>
+        <v>19.3283061981201</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G1007" t="n">
-        <v>19.4492683410645</v>
+        <v>19.4492664337158</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G1009" t="n">
-        <v>19.4492683410645</v>
+        <v>19.4492664337158</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G1011" t="n">
-        <v>19.0690975189209</v>
+        <v>19.0690956115723</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1012" t="n">
-        <v>19.0431747436523</v>
+        <v>19.043176651001</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G1013" t="n">
-        <v>19.3628616333008</v>
+        <v>19.362865447998</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1014" t="n">
-        <v>19.3023834228516</v>
+        <v>19.3023815155029</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1015" t="n">
-        <v>19.3974266052246</v>
+        <v>19.3974285125732</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>22</v>
       </c>
       <c r="G1017" t="n">
-        <v>19.0086154937744</v>
+        <v>19.0086116790771</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G1018" t="n">
-        <v>18.91357421875</v>
+        <v>18.9135723114014</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1019" t="n">
-        <v>19.0950145721436</v>
+        <v>19.0950183868408</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G1020" t="n">
-        <v>18.8703689575195</v>
+        <v>18.8703670501709</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1021" t="n">
-        <v>18.844446182251</v>
+        <v>18.8444480895996</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G1022" t="n">
-        <v>18.7753257751465</v>
+        <v>18.7753276824951</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G1023" t="n">
-        <v>18.8703689575195</v>
+        <v>18.8703670501709</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1024" t="n">
-        <v>18.7494049072266</v>
+        <v>18.7494068145752</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G1026" t="n">
-        <v>18.3346710205078</v>
+        <v>18.3346729278564</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1028" t="n">
-        <v>18.8530883789062</v>
+        <v>18.8530864715576</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G1029" t="n">
-        <v>18.6889247894287</v>
+        <v>18.6889228820801</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G1031" t="n">
-        <v>18.4297161102295</v>
+        <v>18.4297122955322</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G1032" t="n">
-        <v>18.9826908111572</v>
+        <v>18.9826927185059</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G1033" t="n">
-        <v>18.4124336242676</v>
+        <v>18.4124317169189</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G1034" t="n">
-        <v>18.7839679718018</v>
+        <v>18.7839660644531</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1035" t="n">
-        <v>18.8790092468262</v>
+        <v>18.8790111541748</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.4297161102295</v>
+        <v>18.4297122955322</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>21.3700008392334</v>
       </c>
       <c r="G1038" t="n">
-        <v>18.4642772674561</v>
+        <v>18.4642753601074</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G1040" t="n">
-        <v>19.5529499053955</v>
+        <v>19.5529479980469</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>19.7862358093262</v>
+        <v>19.7862377166748</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G1044" t="n">
-        <v>20.0627288818359</v>
+        <v>20.0627307891846</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1045" t="n">
-        <v>20.3478546142578</v>
+        <v>20.3478584289551</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G1046" t="n">
-        <v>19.9676876068115</v>
+        <v>19.9676837921143</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>23</v>
       </c>
       <c r="G1047" t="n">
-        <v>19.8726444244385</v>
+        <v>19.8726406097412</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>19.7862358093262</v>
+        <v>19.7862377166748</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G1051" t="n">
-        <v>19.5011100769043</v>
+        <v>19.501106262207</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G1053" t="n">
-        <v>17.7644119262695</v>
+        <v>17.7644100189209</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1054" t="n">
-        <v>17.14231300354</v>
+        <v>17.1423149108887</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G1055" t="n">
-        <v>17.4447231292725</v>
+        <v>17.4447250366211</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>19.9549999237061</v>
       </c>
       <c r="G1056" t="n">
-        <v>17.241678237915</v>
+        <v>17.2416763305664</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G1057" t="n">
-        <v>17.0775108337402</v>
+        <v>17.0775089263916</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1059" t="n">
-        <v>16.4813289642334</v>
+        <v>16.4813327789307</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>15.5438604354858</v>
+        <v>15.5438632965088</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G1064" t="n">
-        <v>13.7942056655884</v>
+        <v>13.7942047119141</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1066" t="n">
-        <v>12.1136713027954</v>
+        <v>12.1136722564697</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.8048934936523</v>
+        <v>12.8048944473267</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1069" t="n">
-        <v>12.8048934936523</v>
+        <v>12.8048944473267</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1070" t="n">
-        <v>12.7703313827515</v>
+        <v>12.7703323364258</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>14.5050001144409</v>
       </c>
       <c r="G1071" t="n">
-        <v>12.5327234268188</v>
+        <v>12.5327243804932</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1072" t="n">
-        <v>12.4938440322876</v>
+        <v>12.493842124939</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>13.5150003433228</v>
       </c>
       <c r="G1073" t="n">
-        <v>11.6773376464844</v>
+        <v>11.6773366928101</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1075" t="n">
-        <v>13.9972524642944</v>
+        <v>13.9972543716431</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>17.375</v>
       </c>
       <c r="G1076" t="n">
-        <v>15.0124835968018</v>
+        <v>15.0124855041504</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1077" t="n">
-        <v>13.70348072052</v>
+        <v>13.7034826278687</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1080" t="n">
-        <v>13.6343612670898</v>
+        <v>13.6343593597412</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.5502290725708</v>
+        <v>14.5502281188965</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1086" t="n">
-        <v>15.3451375961304</v>
+        <v>15.345139503479</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>15.1750001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>13.1116218566895</v>
+        <v>13.1116228103638</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1091" t="n">
-        <v>14.1873397827148</v>
+        <v>14.1873378753662</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1092" t="n">
-        <v>13.6602821350098</v>
+        <v>13.6602811813354</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1093" t="n">
-        <v>14.269419670105</v>
+        <v>14.2694206237793</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1094" t="n">
-        <v>14.5502290725708</v>
+        <v>14.5502281188965</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>16.7150001525879</v>
       </c>
       <c r="G1095" t="n">
-        <v>14.4422254562378</v>
+        <v>14.4422264099121</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1096" t="n">
-        <v>15.258731842041</v>
+        <v>15.2587327957153</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>18.4050006866455</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.9024343490601</v>
+        <v>15.9024333953857</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>17.8850002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.4531393051147</v>
+        <v>15.4531383514404</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1103" t="n">
-        <v>14.2046184539795</v>
+        <v>14.2046203613281</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.6884737014771</v>
+        <v>14.6884746551514</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>17.1149997711182</v>
       </c>
       <c r="G1105" t="n">
-        <v>14.7878370285034</v>
+        <v>14.7878389358521</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>16.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>14.2564601898193</v>
+        <v>14.2564611434937</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1108" t="n">
-        <v>13.6689214706421</v>
+        <v>13.6689224243164</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>14.677544593811</v>
+        <v>14.6775436401367</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G1113" t="n">
-        <v>14.6470127105713</v>
+        <v>14.6470136642456</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1114" t="n">
-        <v>14.777868270874</v>
+        <v>14.7778673171997</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1115" t="n">
-        <v>15.2140502929688</v>
+        <v>15.2140493392944</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>15.1137285232544</v>
+        <v>15.1137313842773</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>15.4408655166626</v>
+        <v>15.440863609314</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1118" t="n">
-        <v>15.6851282119751</v>
+        <v>15.6851272583008</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1124" t="n">
-        <v>17.6043281555176</v>
+        <v>17.6043319702148</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G1125" t="n">
-        <v>17.3687896728516</v>
+        <v>17.3687915802002</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>19.7749996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>17.2510242462158</v>
+        <v>17.2510223388672</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1128" t="n">
-        <v>15.7549171447754</v>
+        <v>15.7549161911011</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G1129" t="n">
-        <v>15.7112979888916</v>
+        <v>15.7113008499146</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>19.8649997711182</v>
       </c>
       <c r="G1132" t="n">
-        <v>17.3295364379883</v>
+        <v>17.3295345306396</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1134" t="n">
-        <v>17.0372943878174</v>
+        <v>17.0372924804688</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G1136" t="n">
-        <v>17.5694351196289</v>
+        <v>17.5694332122803</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>19.2849998474121</v>
       </c>
       <c r="G1137" t="n">
-        <v>16.8235607147217</v>
+        <v>16.8235645294189</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>19.125</v>
       </c>
       <c r="G1138" t="n">
-        <v>16.6839847564697</v>
+        <v>16.6839866638184</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>16.6185550689697</v>
+        <v>16.6185569763184</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>19.4449996948242</v>
       </c>
       <c r="G1140" t="n">
-        <v>16.9631423950195</v>
+        <v>16.9631404876709</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G1141" t="n">
-        <v>16.7232418060303</v>
+        <v>16.7232398986816</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1142" t="n">
-        <v>16.6796245574951</v>
+        <v>16.6796226501465</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1143" t="n">
-        <v>17.0372943878174</v>
+        <v>17.0372924804688</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>16.7712211608887</v>
+        <v>16.7712230682373</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>19.6550006866455</v>
       </c>
       <c r="G1145" t="n">
-        <v>17.1463356018066</v>
+        <v>17.1463375091553</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>19.2549991607666</v>
       </c>
       <c r="G1148" t="n">
-        <v>16.7973918914795</v>
+        <v>16.7973957061768</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G1149" t="n">
-        <v>17.159423828125</v>
+        <v>17.1594219207764</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>19.8850002288818</v>
       </c>
       <c r="G1150" t="n">
-        <v>17.3469848632812</v>
+        <v>17.3469829559326</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>21.2099990844727</v>
       </c>
       <c r="G1152" t="n">
-        <v>18.5028648376465</v>
+        <v>18.5028686523438</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>18.6686172485352</v>
+        <v>18.6686153411865</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>21.3700008392334</v>
       </c>
       <c r="G1155" t="n">
-        <v>18.6424465179443</v>
+        <v>18.6424446105957</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1156" t="n">
-        <v>18.3545665740967</v>
+        <v>18.354564666748</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1158" t="n">
-        <v>18.6337223052979</v>
+        <v>18.6337203979492</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G1159" t="n">
-        <v>18.0754051208496</v>
+        <v>18.0754089355469</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G1161" t="n">
-        <v>17.918384552002</v>
+        <v>17.9183864593506</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G1162" t="n">
-        <v>17.6130523681641</v>
+        <v>17.6130542755127</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1166" t="n">
-        <v>17.0809116363525</v>
+        <v>17.0809135437012</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G1167" t="n">
-        <v>17.9620018005371</v>
+        <v>17.9620037078857</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G1169" t="n">
-        <v>17.7700824737549</v>
+        <v>17.7700805664062</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>20.8299999237061</v>
       </c>
       <c r="G1170" t="n">
-        <v>18.1713676452637</v>
+        <v>18.1713695526123</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1172" t="n">
-        <v>18.7122364044189</v>
+        <v>18.7122344970703</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>21.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>18.5377597808838</v>
+        <v>18.5377616882324</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G1176" t="n">
-        <v>18.6511688232422</v>
+        <v>18.6511650085449</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1177" t="n">
-        <v>18.5464839935303</v>
+        <v>18.5464859008789</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>20.75</v>
       </c>
       <c r="G1178" t="n">
-        <v>18.1015777587891</v>
+        <v>18.1015815734863</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1179" t="n">
-        <v>18.1626453399658</v>
+        <v>18.1626434326172</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>21.25</v>
       </c>
       <c r="G1180" t="n">
-        <v>18.5377597808838</v>
+        <v>18.5377616882324</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>21.2099990844727</v>
       </c>
       <c r="G1181" t="n">
-        <v>18.5028648376465</v>
+        <v>18.5028686523438</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G1182" t="n">
-        <v>18.4679737091064</v>
+        <v>18.4679718017578</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G1183" t="n">
-        <v>18.2934989929199</v>
+        <v>18.2934970855713</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G1184" t="n">
-        <v>18.1364727020264</v>
+        <v>18.136474609375</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G1185" t="n">
-        <v>17.900936126709</v>
+        <v>17.9009380340576</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1188" t="n">
-        <v>17.2204875946045</v>
+        <v>17.2204895019531</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>19.9699993133545</v>
       </c>
       <c r="G1189" t="n">
-        <v>17.4211349487305</v>
+        <v>17.4211311340332</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G1190" t="n">
-        <v>17.5258197784424</v>
+        <v>17.5258178710938</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1191" t="n">
-        <v>17.2117652893066</v>
+        <v>17.211763381958</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G1195" t="n">
-        <v>18.0754051208496</v>
+        <v>18.0754089355469</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1196" t="n">
-        <v>18.2324333190918</v>
+        <v>18.2324352264404</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1201" t="n">
-        <v>17.2379360198975</v>
+        <v>17.2379379272461</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>16.8366470336914</v>
+        <v>16.83664894104</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>19.2749996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>16.8148403167725</v>
+        <v>16.8148422241211</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G1205" t="n">
-        <v>17.5694351196289</v>
+        <v>17.5694332122803</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>19.8850002288818</v>
       </c>
       <c r="G1207" t="n">
-        <v>17.3469848632812</v>
+        <v>17.3469829559326</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>19.7950000762939</v>
       </c>
       <c r="G1209" t="n">
-        <v>17.2684707641602</v>
+        <v>17.2684688568115</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1210" t="n">
-        <v>17.4996490478516</v>
+        <v>17.4996471405029</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G1212" t="n">
-        <v>17.9096622467041</v>
+        <v>17.9096603393555</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>18.3632869720459</v>
+        <v>18.3632888793945</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1214" t="n">
-        <v>18.1103000640869</v>
+        <v>18.1103019714355</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>18.2324333190918</v>
+        <v>18.2324352264404</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G1218" t="n">
-        <v>17.6392230987549</v>
+        <v>17.6392250061035</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>18.1451988220215</v>
+        <v>18.1451969146729</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1220" t="n">
-        <v>17.9271087646484</v>
+        <v>17.9271068572998</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G1221" t="n">
-        <v>18.0928535461426</v>
+        <v>18.0928554534912</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.0841293334961</v>
+        <v>18.0841312408447</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1224" t="n">
-        <v>18.0230655670166</v>
+        <v>18.023063659668</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>18</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.7025747299194</v>
+        <v>15.7025766372681</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>17.9650001525879</v>
       </c>
       <c r="G1228" t="n">
-        <v>15.6720409393311</v>
+        <v>15.6720428466797</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.2041835784912</v>
+        <v>16.2041854858398</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1230" t="n">
-        <v>17.0460166931152</v>
+        <v>17.0460186004639</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1233" t="n">
-        <v>17.2553863525391</v>
+        <v>17.2553844451904</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.2728328704834</v>
+        <v>17.2728309631348</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1236" t="n">
-        <v>18.1451988220215</v>
+        <v>18.1451969146729</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G1237" t="n">
-        <v>18.0841293334961</v>
+        <v>18.0841312408447</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.7700824737549</v>
+        <v>17.7700805664062</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G1239" t="n">
-        <v>18.0754051208496</v>
+        <v>18.0754089355469</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>21</v>
       </c>
       <c r="G1242" t="n">
-        <v>18.3196716308594</v>
+        <v>18.3196678161621</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G1243" t="n">
-        <v>18.2411594390869</v>
+        <v>18.2411575317383</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1244" t="n">
-        <v>18.1103000640869</v>
+        <v>18.1103019714355</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1245" t="n">
-        <v>18.1103000640869</v>
+        <v>18.1103019714355</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>20.0100002288818</v>
       </c>
       <c r="G1252" t="n">
-        <v>17.4560298919678</v>
+        <v>17.4560279846191</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1253" t="n">
-        <v>17.3077278137207</v>
+        <v>17.3077259063721</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>17.0983581542969</v>
+        <v>17.0983600616455</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>17.0460166931152</v>
+        <v>17.0460186004639</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>19.6350002288818</v>
       </c>
       <c r="G1257" t="n">
-        <v>17.1288909912109</v>
+        <v>17.1288928985596</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>19.3050003051758</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.8410110473633</v>
+        <v>16.8410129547119</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>16.6621761322021</v>
+        <v>16.6621742248535</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>19.2849998474121</v>
       </c>
       <c r="G1261" t="n">
-        <v>16.8235607147217</v>
+        <v>16.8235645294189</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>19.3850002288818</v>
       </c>
       <c r="G1262" t="n">
-        <v>16.9107990264893</v>
+        <v>16.9108009338379</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>19.7749996185303</v>
       </c>
       <c r="G1264" t="n">
-        <v>17.2510242462158</v>
+        <v>17.2510223388672</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>19</v>
       </c>
       <c r="G1265" t="n">
-        <v>16.5749397277832</v>
+        <v>16.5749359130859</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>19.3150005340576</v>
       </c>
       <c r="G1267" t="n">
-        <v>16.8497371673584</v>
+        <v>16.8497352600098</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G1269" t="n">
-        <v>16.9326114654541</v>
+        <v>16.9326095581055</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G1271" t="n">
-        <v>17.6304988861084</v>
+        <v>17.630500793457</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G1274" t="n">
-        <v>19.3577861785889</v>
+        <v>19.3577899932861</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.9913902282715</v>
+        <v>18.9913921356201</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>18.6686172485352</v>
+        <v>18.6686153411865</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G1277" t="n">
-        <v>18.9913902282715</v>
+        <v>18.9913921356201</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>21.5699996948242</v>
       </c>
       <c r="G1278" t="n">
-        <v>18.8169174194336</v>
+        <v>18.8169193267822</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1279" t="n">
-        <v>18.5464839935303</v>
+        <v>18.5464859008789</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1280" t="n">
-        <v>18.5813751220703</v>
+        <v>18.5813770294189</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G1282" t="n">
-        <v>18.8518123626709</v>
+        <v>18.8518104553223</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G1284" t="n">
-        <v>18.5290355682373</v>
+        <v>18.5290374755859</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1285" t="n">
-        <v>18.1626453399658</v>
+        <v>18.1626434326172</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>20.5100002288818</v>
       </c>
       <c r="G1286" t="n">
-        <v>17.8922157287598</v>
+        <v>17.8922119140625</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G1287" t="n">
-        <v>18.0841293334961</v>
+        <v>18.0841312408447</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G1289" t="n">
-        <v>17.900936126709</v>
+        <v>17.9009380340576</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G1290" t="n">
-        <v>17.7351856231689</v>
+        <v>17.7351818084717</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1291" t="n">
-        <v>18.0974979400635</v>
+        <v>18.0974960327148</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1293" t="n">
-        <v>18.4779262542725</v>
+        <v>18.4779243469238</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G1300" t="n">
-        <v>19.2297248840332</v>
+        <v>19.2297210693359</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G1301" t="n">
-        <v>19.7097854614258</v>
+        <v>19.7097873687744</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G1302" t="n">
-        <v>19.4923992156982</v>
+        <v>19.4924011230469</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1303" t="n">
-        <v>19.3474788665771</v>
+        <v>19.3474731445312</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1304" t="n">
-        <v>19.0395107269287</v>
+        <v>19.0395088195801</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>21.3700008392334</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.3565330505371</v>
+        <v>19.3565311431885</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1310" t="n">
-        <v>18.9761066436768</v>
+        <v>18.9761047363281</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.2931270599365</v>
+        <v>19.2931251525879</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G1314" t="n">
-        <v>19.7369613647461</v>
+        <v>19.7369632720947</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>21.3700008392334</v>
       </c>
       <c r="G1315" t="n">
-        <v>19.3565330505371</v>
+        <v>19.3565311431885</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>22</v>
       </c>
       <c r="G1316" t="n">
-        <v>19.9271755218506</v>
+        <v>19.927173614502</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G1317" t="n">
-        <v>19.8184795379639</v>
+        <v>19.8184833526611</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G1318" t="n">
-        <v>19.9000015258789</v>
+        <v>19.8999996185303</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>20.2894878387451</v>
+        <v>20.2894859313965</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.3347759246826</v>
+        <v>20.3347778320312</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G1327" t="n">
-        <v>19.9362316131592</v>
+        <v>19.9362335205078</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.1264457702637</v>
+        <v>20.1264476776123</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1331" t="n">
-        <v>19.5286312103271</v>
+        <v>19.5286293029785</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G1332" t="n">
-        <v>19.7097854614258</v>
+        <v>19.7097873687744</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G1333" t="n">
-        <v>20.0811557769775</v>
+        <v>20.0811576843262</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1334" t="n">
-        <v>20.1083278656006</v>
+        <v>20.1083316802979</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>20.3347759246826</v>
+        <v>20.3347778320312</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G1337" t="n">
-        <v>20.0992736816406</v>
+        <v>20.0992774963379</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>20.1355018615723</v>
+        <v>20.1355037689209</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G1340" t="n">
-        <v>20.0811557769775</v>
+        <v>20.0811576843262</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1342" t="n">
-        <v>20.2532558441162</v>
+        <v>20.2532539367676</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G1344" t="n">
-        <v>20.7152061462402</v>
+        <v>20.7152042388916</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G1346" t="n">
-        <v>20.1173858642578</v>
+        <v>20.1173877716064</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1347" t="n">
-        <v>20.1626777648926</v>
+        <v>20.1626758575439</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G1349" t="n">
-        <v>20.3166618347168</v>
+        <v>20.3166599273682</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G1353" t="n">
-        <v>20.1173858642578</v>
+        <v>20.1173877716064</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G1356" t="n">
-        <v>20.5793361663818</v>
+        <v>20.5793342590332</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G1358" t="n">
-        <v>20.6336841583252</v>
+        <v>20.6336860656738</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G1360" t="n">
-        <v>20.8238964080811</v>
+        <v>20.8238983154297</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G1361" t="n">
-        <v>20.9325904846191</v>
+        <v>20.9325923919678</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>23.9400005340576</v>
       </c>
       <c r="G1364" t="n">
-        <v>21.6843910217285</v>
+        <v>21.6843891143799</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G1365" t="n">
-        <v>21.6753330230713</v>
+        <v>21.675329208374</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G1368" t="n">
-        <v>20.9325904846191</v>
+        <v>20.9325923919678</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>21.1981410980225</v>
+        <v>21.1981391906738</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G1371" t="n">
-        <v>21.1431980133057</v>
+        <v>21.143196105957</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G1373" t="n">
-        <v>21.3080234527588</v>
+        <v>21.3080215454102</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>23.4300003051758</v>
       </c>
       <c r="G1375" t="n">
-        <v>21.454532623291</v>
+        <v>21.4545345306396</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>23.5100002288818</v>
       </c>
       <c r="G1378" t="n">
-        <v>21.5277862548828</v>
+        <v>21.5277881622314</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G1386" t="n">
-        <v>21.2622375488281</v>
+        <v>21.2622394561768</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1392" t="n">
-        <v>20.5296859741211</v>
+        <v>20.5296878814697</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>22.75</v>
       </c>
       <c r="G1395" t="n">
-        <v>20.8318653106689</v>
+        <v>20.8318672180176</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>21.75</v>
       </c>
       <c r="G1398" t="n">
-        <v>19.9161796569824</v>
+        <v>19.9161777496338</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G1401" t="n">
-        <v>20.6121006011963</v>
+        <v>20.6120986938477</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>20.4655895233154</v>
+        <v>20.4655914306641</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G1408" t="n">
-        <v>19.9528064727783</v>
+        <v>19.952808380127</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1409" t="n">
-        <v>19.137845993042</v>
+        <v>19.1378479003906</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G1412" t="n">
-        <v>19.888708114624</v>
+        <v>19.8887100219727</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>20.0535316467285</v>
+        <v>20.0535297393799</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G1416" t="n">
-        <v>20.1267852783203</v>
+        <v>20.1267871856689</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1419" t="n">
-        <v>20.4564342498779</v>
+        <v>20.4564361572266</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1420" t="n">
-        <v>19.9436492919922</v>
+        <v>19.9436511993408</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G1422" t="n">
-        <v>19.57737159729</v>
+        <v>19.5773735046387</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1423" t="n">
-        <v>19.7330417633057</v>
+        <v>19.733039855957</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G1424" t="n">
-        <v>19.9344940185547</v>
+        <v>19.9344921112061</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G1426" t="n">
-        <v>20.7494525909424</v>
+        <v>20.749454498291</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1427" t="n">
-        <v>20.6487274169922</v>
+        <v>20.6487293243408</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1428" t="n">
-        <v>20.7402973175049</v>
+        <v>20.7402954101562</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>22</v>
       </c>
       <c r="G1431" t="n">
-        <v>20.1451015472412</v>
+        <v>20.1450996398926</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G1432" t="n">
-        <v>19.9344940185547</v>
+        <v>19.9344921112061</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1433" t="n">
-        <v>20.0077457427979</v>
+        <v>20.0077476501465</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>22</v>
       </c>
       <c r="G1435" t="n">
-        <v>20.1451015472412</v>
+        <v>20.1450996398926</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>22.6100006103516</v>
       </c>
       <c r="G1439" t="n">
-        <v>20.703670501709</v>
+        <v>20.7036724090576</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G1440" t="n">
-        <v>20.5846290588379</v>
+        <v>20.5846309661865</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>22.2700004577637</v>
       </c>
       <c r="G1441" t="n">
-        <v>20.3923358917236</v>
+        <v>20.392333984375</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1442" t="n">
-        <v>20.5663166046143</v>
+        <v>20.566312789917</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>22</v>
       </c>
       <c r="G1445" t="n">
-        <v>20.1451015472412</v>
+        <v>20.1450996398926</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1448" t="n">
-        <v>19.137845993042</v>
+        <v>19.1378479003906</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G1449" t="n">
-        <v>19.1653175354004</v>
+        <v>19.1653156280518</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1461" t="n">
-        <v>18.0207080841064</v>
+        <v>18.0207099914551</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>19.4750003814697</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.8329925537109</v>
+        <v>17.8329906463623</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.0664901733398</v>
+        <v>18.0664920806885</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>19.6650009155273</v>
       </c>
       <c r="G1469" t="n">
-        <v>18.0069732666016</v>
+        <v>18.0069713592529</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>19.6650009155273</v>
       </c>
       <c r="G1470" t="n">
-        <v>18.0069732666016</v>
+        <v>18.0069713592529</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1473" t="n">
-        <v>18.6342163085938</v>
+        <v>18.6342182159424</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G1481" t="n">
-        <v>18.3411960601807</v>
+        <v>18.3411979675293</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G1485" t="n">
-        <v>18.5792770385742</v>
+        <v>18.5792789459229</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.9089241027832</v>
+        <v>18.9089260101318</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.9455509185791</v>
+        <v>18.9455528259277</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G1497" t="n">
-        <v>18.2999935150146</v>
+        <v>18.299991607666</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>19.6450004577637</v>
       </c>
       <c r="G1501" t="n">
-        <v>17.9886589050293</v>
+        <v>17.9886608123779</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1502" t="n">
-        <v>18.0939636230469</v>
+        <v>18.0939617156982</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1504" t="n">
-        <v>17.1233367919922</v>
+        <v>17.1233348846436</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>18.5249996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>16.9630928039551</v>
+        <v>16.9630908966064</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G1508" t="n">
-        <v>16.9493560791016</v>
+        <v>16.9493541717529</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>19.3850002288818</v>
       </c>
       <c r="G1510" t="n">
-        <v>17.7505798339844</v>
+        <v>17.750581741333</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G1513" t="n">
-        <v>17.2790031433105</v>
+        <v>17.2790012359619</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1514" t="n">
-        <v>17.288158416748</v>
+        <v>17.2881565093994</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1515" t="n">
-        <v>17.1965885162354</v>
+        <v>17.196590423584</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1516" t="n">
-        <v>17.2149028778076</v>
+        <v>17.2149047851562</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G1517" t="n">
-        <v>17.1004409790039</v>
+        <v>17.1004447937012</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1518" t="n">
-        <v>17.1233367919922</v>
+        <v>17.1233348846436</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>18.6749992370605</v>
       </c>
       <c r="G1520" t="n">
-        <v>17.1004409790039</v>
+        <v>17.1004447937012</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1522" t="n">
-        <v>17.2149028778076</v>
+        <v>17.2149047851562</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>18.9050006866455</v>
       </c>
       <c r="G1523" t="n">
-        <v>17.3110523223877</v>
+        <v>17.3110504150391</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>19.5450000762939</v>
       </c>
       <c r="G1529" t="n">
-        <v>17.8970909118652</v>
+        <v>17.8970890045166</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1533" t="n">
-        <v>17.7185306549072</v>
+        <v>17.7185325622559</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1534" t="n">
-        <v>17.8192558288574</v>
+        <v>17.8192577362061</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1540" t="n">
-        <v>17.8375701904297</v>
+        <v>17.8375720977783</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1541" t="n">
-        <v>17.3934650421143</v>
+        <v>17.3934631347656</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>18.2649993896484</v>
       </c>
       <c r="G1543" t="n">
-        <v>16.7250099182129</v>
+        <v>16.7250118255615</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>18.5</v>
       </c>
       <c r="G1544" t="n">
-        <v>16.9401969909668</v>
+        <v>16.9401988983154</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>18.1749992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>16.6426010131836</v>
+        <v>16.642599105835</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G1546" t="n">
-        <v>16.5098247528076</v>
+        <v>16.5098285675049</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1550" t="n">
-        <v>17.3614139556885</v>
+        <v>17.3614158630371</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1552" t="n">
-        <v>17.2149028778076</v>
+        <v>17.2149047851562</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1553" t="n">
-        <v>17.086706161499</v>
+        <v>17.0867080688477</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G1555" t="n">
-        <v>18.3961391448975</v>
+        <v>18.3961410522461</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G1556" t="n">
-        <v>18.2450504302979</v>
+        <v>18.2450485229492</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1563" t="n">
-        <v>17.1782779693604</v>
+        <v>17.1782760620117</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G1567" t="n">
-        <v>15.6628150939941</v>
+        <v>15.6628160476685</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G1568" t="n">
-        <v>14.8432750701904</v>
+        <v>14.8432741165161</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>16.5550003051758</v>
       </c>
       <c r="G1569" t="n">
-        <v>15.1591882705688</v>
+        <v>15.1591873168945</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>16.3050003051758</v>
       </c>
       <c r="G1570" t="n">
-        <v>14.9302673339844</v>
+        <v>14.9302663803101</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>15.6049995422363</v>
       </c>
       <c r="G1571" t="n">
-        <v>14.2892866134644</v>
+        <v>14.28928565979</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>17.0550003051758</v>
       </c>
       <c r="G1574" t="n">
-        <v>15.6170320510864</v>
+        <v>15.6170310974121</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.6490793228149</v>
+        <v>15.6490802764893</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>17.4850006103516</v>
       </c>
       <c r="G1582" t="n">
-        <v>16.010778427124</v>
+        <v>16.0107803344727</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1584" t="n">
-        <v>15.676549911499</v>
+        <v>15.6765508651733</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1586" t="n">
-        <v>14.6326684951782</v>
+        <v>14.6326675415039</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.9146289825439</v>
+        <v>15.9146280288696</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.4338932037354</v>
+        <v>15.433892250061</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.6032991409302</v>
+        <v>15.6032981872559</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>16.5849990844727</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.1866598129272</v>
+        <v>15.1866588592529</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.4567852020264</v>
+        <v>15.4567861557007</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.6673965454102</v>
+        <v>15.6673955917358</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1606" t="n">
-        <v>16.5281391143799</v>
+        <v>16.5281372070312</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1608" t="n">
-        <v>16.1343936920166</v>
+        <v>16.1343955993652</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1611" t="n">
-        <v>16.116081237793</v>
+        <v>16.1160793304443</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1612" t="n">
-        <v>16.1710224151611</v>
+        <v>16.1710205078125</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1614" t="n">
-        <v>15.5758256912231</v>
+        <v>15.5758266448975</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1615" t="n">
-        <v>15.6948652267456</v>
+        <v>15.6948661804199</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1618" t="n">
-        <v>15.9146289825439</v>
+        <v>15.9146280288696</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1619" t="n">
-        <v>16.3907852172852</v>
+        <v>16.3907871246338</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1620" t="n">
-        <v>16.1893348693848</v>
+        <v>16.1893367767334</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>36.5999984741211</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>604853</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>37.0999984741211</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>36.4700012207031</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>36.5200004577637</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>36.6300010681152</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>36.6300010681152</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BZU.MI.xlsx
+++ b/data/BZU.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2" t="n">
-        <v>13.7963047027588</v>
+        <v>13.7963066101074</v>
       </c>
       <c r="H2" t="n">
         <v>867037</v>
@@ -456,7 +456,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G3" t="n">
-        <v>14.033299446106</v>
+        <v>14.0332984924316</v>
       </c>
       <c r="H3" t="n">
         <v>635398</v>
@@ -485,7 +485,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G4" t="n">
-        <v>13.7963047027588</v>
+        <v>13.7963066101074</v>
       </c>
       <c r="H4" t="n">
         <v>761752</v>
@@ -572,7 +572,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G7" t="n">
-        <v>12.6028842926025</v>
+        <v>12.6028833389282</v>
       </c>
       <c r="H7" t="n">
         <v>1014683</v>
@@ -601,7 +601,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G8" t="n">
-        <v>12.28125</v>
+        <v>12.2812509536743</v>
       </c>
       <c r="H8" t="n">
         <v>1390588</v>
@@ -659,7 +659,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>11.9596195220947</v>
+        <v>11.959620475769</v>
       </c>
       <c r="H10" t="n">
         <v>947205</v>
@@ -688,7 +688,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G11" t="n">
-        <v>11.570276260376</v>
+        <v>11.5702772140503</v>
       </c>
       <c r="H11" t="n">
         <v>1231193</v>
@@ -746,7 +746,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G13" t="n">
-        <v>11.6125974655151</v>
+        <v>11.6125965118408</v>
       </c>
       <c r="H13" t="n">
         <v>661953</v>
@@ -804,7 +804,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G15" t="n">
-        <v>11.3332843780518</v>
+        <v>11.3332853317261</v>
       </c>
       <c r="H15" t="n">
         <v>1359899</v>
@@ -862,7 +862,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G17" t="n">
-        <v>11.5872049331665</v>
+        <v>11.5872020721436</v>
       </c>
       <c r="H17" t="n">
         <v>936025</v>
@@ -891,7 +891,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G18" t="n">
-        <v>12.1289005279541</v>
+        <v>12.1288995742798</v>
       </c>
       <c r="H18" t="n">
         <v>1442046</v>
@@ -920,7 +920,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>12.0188665390015</v>
+        <v>12.0188674926758</v>
       </c>
       <c r="H19" t="n">
         <v>952360</v>
@@ -949,7 +949,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G20" t="n">
-        <v>11.460244178772</v>
+        <v>11.4602451324463</v>
       </c>
       <c r="H20" t="n">
         <v>991147</v>
@@ -978,7 +978,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G21" t="n">
-        <v>11.7734117507935</v>
+        <v>11.7734127044678</v>
       </c>
       <c r="H21" t="n">
         <v>589272</v>
@@ -1036,7 +1036,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G23" t="n">
-        <v>11.4940996170044</v>
+        <v>11.4941005706787</v>
       </c>
       <c r="H23" t="n">
         <v>1146346</v>
@@ -1065,7 +1065,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9185485839844</v>
+        <v>10.9185476303101</v>
       </c>
       <c r="H24" t="n">
         <v>1308044</v>
@@ -1152,7 +1152,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>10.5376682281494</v>
+        <v>10.5376710891724</v>
       </c>
       <c r="H27" t="n">
         <v>1362206</v>
@@ -1210,7 +1210,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G29" t="n">
-        <v>11.1386127471924</v>
+        <v>11.1386117935181</v>
       </c>
       <c r="H29" t="n">
         <v>1437721</v>
@@ -1239,7 +1239,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G30" t="n">
-        <v>10.3853168487549</v>
+        <v>10.3853178024292</v>
       </c>
       <c r="H30" t="n">
         <v>1654433</v>
@@ -1326,7 +1326,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>10.6223106384277</v>
+        <v>10.6223096847534</v>
       </c>
       <c r="H33" t="n">
         <v>1070244</v>
@@ -1413,7 +1413,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G36" t="n">
-        <v>11.4009971618652</v>
+        <v>11.4009981155396</v>
       </c>
       <c r="H36" t="n">
         <v>817066</v>
@@ -1442,7 +1442,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G37" t="n">
-        <v>11.7734117507935</v>
+        <v>11.7734127044678</v>
       </c>
       <c r="H37" t="n">
         <v>820874</v>
@@ -1500,7 +1500,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G39" t="n">
-        <v>11.1470775604248</v>
+        <v>11.1470766067505</v>
       </c>
       <c r="H39" t="n">
         <v>921174</v>
@@ -1529,7 +1529,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>11.4940996170044</v>
+        <v>11.4941005706787</v>
       </c>
       <c r="H40" t="n">
         <v>637167</v>
@@ -1587,7 +1587,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G42" t="n">
-        <v>11.9257640838623</v>
+        <v>11.925763130188</v>
       </c>
       <c r="H42" t="n">
         <v>703622</v>
@@ -1616,7 +1616,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G43" t="n">
-        <v>12.2473974227905</v>
+        <v>12.2473964691162</v>
       </c>
       <c r="H43" t="n">
         <v>497703</v>
@@ -1674,7 +1674,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G45" t="n">
-        <v>12.1289005279541</v>
+        <v>12.1288995742798</v>
       </c>
       <c r="H45" t="n">
         <v>584157</v>
@@ -1761,7 +1761,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G48" t="n">
-        <v>12.4928522109985</v>
+        <v>12.4928512573242</v>
       </c>
       <c r="H48" t="n">
         <v>1677316</v>
@@ -1790,7 +1790,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>12.3151073455811</v>
+        <v>12.3151082992554</v>
       </c>
       <c r="H49" t="n">
         <v>901441</v>
@@ -1819,7 +1819,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G50" t="n">
-        <v>12.28125</v>
+        <v>12.2812509536743</v>
       </c>
       <c r="H50" t="n">
         <v>988356</v>
@@ -1877,7 +1877,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G52" t="n">
-        <v>13.0853300094604</v>
+        <v>13.0853309631348</v>
       </c>
       <c r="H52" t="n">
         <v>1000714</v>
@@ -2022,7 +2022,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>12.80601978302</v>
+        <v>12.8060207366943</v>
       </c>
       <c r="H57" t="n">
         <v>801579</v>
@@ -2051,7 +2051,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>12.7806262969971</v>
+        <v>12.7806282043457</v>
       </c>
       <c r="H58" t="n">
         <v>681284</v>
@@ -2138,7 +2138,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G61" t="n">
-        <v>12.8821964263916</v>
+        <v>12.882194519043</v>
       </c>
       <c r="H61" t="n">
         <v>837439</v>
@@ -2167,7 +2167,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>13.0260820388794</v>
+        <v>13.0260829925537</v>
       </c>
       <c r="H62" t="n">
         <v>645429</v>
@@ -2225,7 +2225,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G64" t="n">
-        <v>12.9752979278564</v>
+        <v>12.9752988815308</v>
       </c>
       <c r="H64" t="n">
         <v>638411</v>
@@ -2254,7 +2254,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G65" t="n">
-        <v>12.7298440933228</v>
+        <v>12.7298431396484</v>
       </c>
       <c r="H65" t="n">
         <v>604959</v>
@@ -2283,7 +2283,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G66" t="n">
-        <v>12.8144836425781</v>
+        <v>12.8144826889038</v>
       </c>
       <c r="H66" t="n">
         <v>696467</v>
@@ -2399,7 +2399,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G70" t="n">
-        <v>13.2122898101807</v>
+        <v>13.2122917175293</v>
       </c>
       <c r="H70" t="n">
         <v>544381</v>
@@ -2457,7 +2457,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>13.2715396881104</v>
+        <v>13.271538734436</v>
       </c>
       <c r="H72" t="n">
         <v>1044777</v>
@@ -2486,7 +2486,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G73" t="n">
-        <v>13.6439552307129</v>
+        <v>13.6439571380615</v>
       </c>
       <c r="H73" t="n">
         <v>1029245</v>
@@ -2515,7 +2515,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G74" t="n">
-        <v>13.5085296630859</v>
+        <v>13.5085315704346</v>
       </c>
       <c r="H74" t="n">
         <v>865430</v>
@@ -2602,7 +2602,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G77" t="n">
-        <v>14.338002204895</v>
+        <v>14.3380031585693</v>
       </c>
       <c r="H77" t="n">
         <v>1114853</v>
@@ -2660,7 +2660,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G79" t="n">
-        <v>14.1517944335938</v>
+        <v>14.1517925262451</v>
       </c>
       <c r="H79" t="n">
         <v>836951</v>
@@ -2689,7 +2689,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G80" t="n">
-        <v>13.9994430541992</v>
+        <v>13.9994421005249</v>
       </c>
       <c r="H80" t="n">
         <v>691638</v>
@@ -2718,7 +2718,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G81" t="n">
-        <v>13.9994430541992</v>
+        <v>13.9994421005249</v>
       </c>
       <c r="H81" t="n">
         <v>1055098</v>
@@ -2747,7 +2747,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>14.0925464630127</v>
+        <v>14.0925436019897</v>
       </c>
       <c r="H82" t="n">
         <v>357435</v>
@@ -2776,7 +2776,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G83" t="n">
-        <v>14.1687202453613</v>
+        <v>14.1687211990356</v>
       </c>
       <c r="H83" t="n">
         <v>515268</v>
@@ -2805,7 +2805,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G84" t="n">
-        <v>13.9994430541992</v>
+        <v>13.9994421005249</v>
       </c>
       <c r="H84" t="n">
         <v>659612</v>
@@ -2863,7 +2863,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G86" t="n">
-        <v>13.8724803924561</v>
+        <v>13.872483253479</v>
       </c>
       <c r="H86" t="n">
         <v>576220</v>
@@ -2921,7 +2921,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G88" t="n">
-        <v>13.8047676086426</v>
+        <v>13.8047666549683</v>
       </c>
       <c r="H88" t="n">
         <v>510888</v>
@@ -2950,7 +2950,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>13.6947383880615</v>
+        <v>13.6947393417358</v>
       </c>
       <c r="H89" t="n">
         <v>1062381</v>
@@ -2979,7 +2979,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G90" t="n">
-        <v>13.7285938262939</v>
+        <v>13.7285928726196</v>
       </c>
       <c r="H90" t="n">
         <v>654443</v>
@@ -3008,7 +3008,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>14.2618265151978</v>
+        <v>14.2618274688721</v>
       </c>
       <c r="H91" t="n">
         <v>936443</v>
@@ -3037,7 +3037,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G92" t="n">
-        <v>14.2872171401978</v>
+        <v>14.2872161865234</v>
       </c>
       <c r="H92" t="n">
         <v>758244</v>
@@ -3095,7 +3095,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G94" t="n">
-        <v>14.0840835571289</v>
+        <v>14.0840826034546</v>
       </c>
       <c r="H94" t="n">
         <v>660067</v>
@@ -3153,7 +3153,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G96" t="n">
-        <v>14.3718566894531</v>
+        <v>14.3718595504761</v>
       </c>
       <c r="H96" t="n">
         <v>709757</v>
@@ -3211,7 +3211,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G98" t="n">
-        <v>14.5496025085449</v>
+        <v>14.5496015548706</v>
       </c>
       <c r="H98" t="n">
         <v>761871</v>
@@ -3240,7 +3240,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G99" t="n">
-        <v>14.6511688232422</v>
+        <v>14.6511707305908</v>
       </c>
       <c r="H99" t="n">
         <v>692736</v>
@@ -3269,7 +3269,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G100" t="n">
-        <v>14.6724233627319</v>
+        <v>14.672420501709</v>
       </c>
       <c r="H100" t="n">
         <v>689062</v>
@@ -3298,7 +3298,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G101" t="n">
-        <v>14.8679399490356</v>
+        <v>14.8679389953613</v>
       </c>
       <c r="H101" t="n">
         <v>613024</v>
@@ -3385,7 +3385,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G104" t="n">
-        <v>15.4885005950928</v>
+        <v>15.4884986877441</v>
       </c>
       <c r="H104" t="n">
         <v>710282</v>
@@ -3414,7 +3414,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G105" t="n">
-        <v>15.4715013504028</v>
+        <v>15.4714984893799</v>
       </c>
       <c r="H105" t="n">
         <v>636326</v>
@@ -3443,7 +3443,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G106" t="n">
-        <v>15.1824712753296</v>
+        <v>15.1824741363525</v>
       </c>
       <c r="H106" t="n">
         <v>535710</v>
@@ -3501,7 +3501,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G108" t="n">
-        <v>15.1824712753296</v>
+        <v>15.1824741363525</v>
       </c>
       <c r="H108" t="n">
         <v>358371</v>
@@ -3559,7 +3559,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G110" t="n">
-        <v>15.1824712753296</v>
+        <v>15.1824741363525</v>
       </c>
       <c r="H110" t="n">
         <v>384628</v>
@@ -3588,7 +3588,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>15.3439855575562</v>
+        <v>15.3439884185791</v>
       </c>
       <c r="H111" t="n">
         <v>493121</v>
@@ -3617,7 +3617,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G112" t="n">
-        <v>15.1994695663452</v>
+        <v>15.1994743347168</v>
       </c>
       <c r="H112" t="n">
         <v>336859</v>
@@ -3675,7 +3675,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G114" t="n">
-        <v>13.9923553466797</v>
+        <v>13.992356300354</v>
       </c>
       <c r="H114" t="n">
         <v>845497</v>
@@ -3762,7 +3762,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G117" t="n">
-        <v>13.4993076324463</v>
+        <v>13.499306678772</v>
       </c>
       <c r="H117" t="n">
         <v>852269</v>
@@ -3791,7 +3791,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>13.2782859802246</v>
+        <v>13.2782850265503</v>
       </c>
       <c r="H118" t="n">
         <v>796452</v>
@@ -3849,7 +3849,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G120" t="n">
-        <v>13.8988456726074</v>
+        <v>13.8988466262817</v>
       </c>
       <c r="H120" t="n">
         <v>1135084</v>
@@ -3878,7 +3878,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>13.8988456726074</v>
+        <v>13.8988466262817</v>
       </c>
       <c r="H121" t="n">
         <v>912159</v>
@@ -3936,7 +3936,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G123" t="n">
-        <v>14.4173965454102</v>
+        <v>14.4173974990845</v>
       </c>
       <c r="H123" t="n">
         <v>733201</v>
@@ -3965,7 +3965,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G124" t="n">
-        <v>13.2442817687988</v>
+        <v>13.2442836761475</v>
       </c>
       <c r="H124" t="n">
         <v>1394398</v>
@@ -3994,7 +3994,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G125" t="n">
-        <v>12.3091926574707</v>
+        <v>12.3091917037964</v>
       </c>
       <c r="H125" t="n">
         <v>1113602</v>
@@ -4023,7 +4023,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>12.6662263870239</v>
+        <v>12.6662282943726</v>
       </c>
       <c r="H126" t="n">
         <v>1314444</v>
@@ -4052,7 +4052,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G127" t="n">
-        <v>12.6832304000854</v>
+        <v>12.6832294464111</v>
       </c>
       <c r="H127" t="n">
         <v>1034494</v>
@@ -4081,7 +4081,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3292932510376</v>
+        <v>13.3292922973633</v>
       </c>
       <c r="H128" t="n">
         <v>1202215</v>
@@ -4110,7 +4110,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G129" t="n">
-        <v>13.8478412628174</v>
+        <v>13.847843170166</v>
       </c>
       <c r="H129" t="n">
         <v>1207033</v>
@@ -4139,7 +4139,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G130" t="n">
-        <v>13.62682056427</v>
+        <v>13.6268215179443</v>
       </c>
       <c r="H130" t="n">
         <v>557339</v>
@@ -4168,7 +4168,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G131" t="n">
-        <v>13.3717956542969</v>
+        <v>13.3717947006226</v>
       </c>
       <c r="H131" t="n">
         <v>468489</v>
@@ -4226,7 +4226,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G133" t="n">
-        <v>12.9127511978149</v>
+        <v>12.9127502441406</v>
       </c>
       <c r="H133" t="n">
         <v>900355</v>
@@ -4342,7 +4342,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G137" t="n">
-        <v>14.187876701355</v>
+        <v>14.1878757476807</v>
       </c>
       <c r="H137" t="n">
         <v>762151</v>
@@ -4371,7 +4371,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>14.6214170455933</v>
+        <v>14.6214179992676</v>
       </c>
       <c r="H138" t="n">
         <v>1081292</v>
@@ -4400,7 +4400,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>14.5024042129517</v>
+        <v>14.5024061203003</v>
       </c>
       <c r="H139" t="n">
         <v>548707</v>
@@ -4429,7 +4429,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G140" t="n">
-        <v>14.6724233627319</v>
+        <v>14.672420501709</v>
       </c>
       <c r="H140" t="n">
         <v>414949</v>
@@ -4458,7 +4458,7 @@
         <v>17.25</v>
       </c>
       <c r="G141" t="n">
-        <v>14.6639184951782</v>
+        <v>14.6639204025269</v>
       </c>
       <c r="H141" t="n">
         <v>804192</v>
@@ -4487,7 +4487,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>14.6724233627319</v>
+        <v>14.672420501709</v>
       </c>
       <c r="H142" t="n">
         <v>284088</v>
@@ -4516,7 +4516,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G143" t="n">
-        <v>14.8169345855713</v>
+        <v>14.8169355392456</v>
       </c>
       <c r="H143" t="n">
         <v>398834</v>
@@ -4545,7 +4545,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G144" t="n">
-        <v>14.9529495239258</v>
+        <v>14.9529504776001</v>
       </c>
       <c r="H144" t="n">
         <v>518284</v>
@@ -4574,7 +4574,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>14.7914333343506</v>
+        <v>14.7914342880249</v>
       </c>
       <c r="H145" t="n">
         <v>291864</v>
@@ -4603,7 +4603,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>15.0464601516724</v>
+        <v>15.0464582443237</v>
       </c>
       <c r="H146" t="n">
         <v>422888</v>
@@ -4632,7 +4632,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G147" t="n">
-        <v>15.2249736785889</v>
+        <v>15.2249774932861</v>
       </c>
       <c r="H147" t="n">
         <v>465538</v>
@@ -4661,7 +4661,7 @@
         <v>17.75</v>
       </c>
       <c r="G148" t="n">
-        <v>15.0889625549316</v>
+        <v>15.0889616012573</v>
       </c>
       <c r="H148" t="n">
         <v>341627</v>
@@ -4748,7 +4748,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G151" t="n">
-        <v>14.8594398498535</v>
+        <v>14.8594379425049</v>
       </c>
       <c r="H151" t="n">
         <v>565765</v>
@@ -4777,7 +4777,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>15.1484651565552</v>
+        <v>15.1484661102295</v>
       </c>
       <c r="H152" t="n">
         <v>989684</v>
@@ -4806,7 +4806,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G153" t="n">
-        <v>15.3524856567383</v>
+        <v>15.3524837493896</v>
       </c>
       <c r="H153" t="n">
         <v>1003828</v>
@@ -4835,7 +4835,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G154" t="n">
-        <v>15.4630002975464</v>
+        <v>15.4629983901978</v>
       </c>
       <c r="H154" t="n">
         <v>687884</v>
@@ -4893,7 +4893,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G156" t="n">
-        <v>15.9050407409668</v>
+        <v>15.9050388336182</v>
       </c>
       <c r="H156" t="n">
         <v>521873</v>
@@ -4922,7 +4922,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G157" t="n">
-        <v>15.9730491638184</v>
+        <v>15.973051071167</v>
       </c>
       <c r="H157" t="n">
         <v>413200</v>
@@ -4951,7 +4951,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G158" t="n">
-        <v>16.2875785827637</v>
+        <v>16.2875804901123</v>
       </c>
       <c r="H158" t="n">
         <v>850349</v>
@@ -5067,7 +5067,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G162" t="n">
-        <v>16.2025661468506</v>
+        <v>16.2025699615479</v>
       </c>
       <c r="H162" t="n">
         <v>619901</v>
@@ -5096,7 +5096,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G163" t="n">
-        <v>15.9985513687134</v>
+        <v>15.9985475540161</v>
       </c>
       <c r="H163" t="n">
         <v>391291</v>
@@ -5125,7 +5125,7 @@
         <v>18.75</v>
       </c>
       <c r="G164" t="n">
-        <v>15.9390449523926</v>
+        <v>15.9390468597412</v>
       </c>
       <c r="H164" t="n">
         <v>461976</v>
@@ -5154,7 +5154,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G165" t="n">
-        <v>16.3470840454102</v>
+        <v>16.3470859527588</v>
       </c>
       <c r="H165" t="n">
         <v>407634</v>
@@ -5270,7 +5270,7 @@
         <v>19.0900001525879</v>
       </c>
       <c r="G169" t="n">
-        <v>16.2280731201172</v>
+        <v>16.2280712127686</v>
       </c>
       <c r="H169" t="n">
         <v>322578</v>
@@ -5328,7 +5328,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G171" t="n">
-        <v>16.2025661468506</v>
+        <v>16.2025699615479</v>
       </c>
       <c r="H171" t="n">
         <v>382532</v>
@@ -5357,7 +5357,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>16.3045787811279</v>
+        <v>16.3045806884766</v>
       </c>
       <c r="H172" t="n">
         <v>584316</v>
@@ -5415,7 +5415,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G174" t="n">
-        <v>16.09206199646</v>
+        <v>16.0920600891113</v>
       </c>
       <c r="H174" t="n">
         <v>428131</v>
@@ -5473,7 +5473,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>16.3470840454102</v>
+        <v>16.3470859527588</v>
       </c>
       <c r="H176" t="n">
         <v>459476</v>
@@ -5531,7 +5531,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>15.2589797973633</v>
+        <v>15.2589769363403</v>
       </c>
       <c r="H178" t="n">
         <v>1817782</v>
@@ -5560,7 +5560,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>15.1314668655396</v>
+        <v>15.1314640045166</v>
       </c>
       <c r="H179" t="n">
         <v>932199</v>
@@ -5676,7 +5676,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>15.2249736785889</v>
+        <v>15.2249774932861</v>
       </c>
       <c r="H183" t="n">
         <v>504204</v>
@@ -5734,7 +5734,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G185" t="n">
-        <v>15.3099851608276</v>
+        <v>15.3099842071533</v>
       </c>
       <c r="H185" t="n">
         <v>311945</v>
@@ -5763,7 +5763,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>15.0464601516724</v>
+        <v>15.0464582443237</v>
       </c>
       <c r="H186" t="n">
         <v>897819</v>
@@ -5879,7 +5879,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G190" t="n">
-        <v>15.1229658126831</v>
+        <v>15.1229648590088</v>
       </c>
       <c r="H190" t="n">
         <v>560942</v>
@@ -5937,7 +5937,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G192" t="n">
-        <v>15.4630002975464</v>
+        <v>15.4629983901978</v>
       </c>
       <c r="H192" t="n">
         <v>699343</v>
@@ -5966,7 +5966,7 @@
         <v>18.25</v>
       </c>
       <c r="G193" t="n">
-        <v>15.5140056610107</v>
+        <v>15.5140018463135</v>
       </c>
       <c r="H193" t="n">
         <v>800668</v>
@@ -5995,7 +5995,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G194" t="n">
-        <v>15.3779926300049</v>
+        <v>15.3779888153076</v>
       </c>
       <c r="H194" t="n">
         <v>673744</v>
@@ -6111,7 +6111,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G198" t="n">
-        <v>15.3099851608276</v>
+        <v>15.3099842071533</v>
       </c>
       <c r="H198" t="n">
         <v>496588</v>
@@ -6169,7 +6169,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>15.3524856567383</v>
+        <v>15.3524837493896</v>
       </c>
       <c r="H200" t="n">
         <v>254813</v>
@@ -6198,7 +6198,7 @@
         <v>17.75</v>
       </c>
       <c r="G201" t="n">
-        <v>15.0889625549316</v>
+        <v>15.0889616012573</v>
       </c>
       <c r="H201" t="n">
         <v>564318</v>
@@ -6227,7 +6227,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>14.9189443588257</v>
+        <v>14.9189434051514</v>
       </c>
       <c r="H202" t="n">
         <v>309376</v>
@@ -6256,7 +6256,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G203" t="n">
-        <v>15.2844839096069</v>
+        <v>15.2844829559326</v>
       </c>
       <c r="H203" t="n">
         <v>372480</v>
@@ -6343,7 +6343,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>15.3269863128662</v>
+        <v>15.3269872665405</v>
       </c>
       <c r="H206" t="n">
         <v>235387</v>
@@ -6372,7 +6372,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>15.3099851608276</v>
+        <v>15.3099842071533</v>
       </c>
       <c r="H207" t="n">
         <v>201417</v>
@@ -6401,7 +6401,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G208" t="n">
-        <v>15.5054998397827</v>
+        <v>15.50550365448</v>
       </c>
       <c r="H208" t="n">
         <v>235924</v>
@@ -6430,7 +6430,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G209" t="n">
-        <v>15.5054998397827</v>
+        <v>15.50550365448</v>
       </c>
       <c r="H209" t="n">
         <v>828108</v>
@@ -6546,7 +6546,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>15.1314668655396</v>
+        <v>15.1314640045166</v>
       </c>
       <c r="H213" t="n">
         <v>391196</v>
@@ -6604,7 +6604,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G215" t="n">
-        <v>14.7999334335327</v>
+        <v>14.7999353408813</v>
       </c>
       <c r="H215" t="n">
         <v>390057</v>
@@ -6633,7 +6633,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G216" t="n">
-        <v>14.9784507751465</v>
+        <v>14.9784517288208</v>
       </c>
       <c r="H216" t="n">
         <v>654362</v>
@@ -6662,7 +6662,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G217" t="n">
-        <v>15.0209522247314</v>
+        <v>15.020956993103</v>
       </c>
       <c r="H217" t="n">
         <v>496464</v>
@@ -6691,7 +6691,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G218" t="n">
-        <v>15.0549554824829</v>
+        <v>15.0549583435059</v>
       </c>
       <c r="H218" t="n">
         <v>351198</v>
@@ -6720,7 +6720,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>15.1314668655396</v>
+        <v>15.1314640045166</v>
       </c>
       <c r="H219" t="n">
         <v>566936</v>
@@ -6778,7 +6778,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G221" t="n">
-        <v>16.5426063537598</v>
+        <v>16.5426025390625</v>
       </c>
       <c r="H221" t="n">
         <v>3250360</v>
@@ -6807,7 +6807,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G222" t="n">
-        <v>16.7636222839355</v>
+        <v>16.7636241912842</v>
       </c>
       <c r="H222" t="n">
         <v>2084529</v>
@@ -6836,7 +6836,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G223" t="n">
-        <v>16.3215827941895</v>
+        <v>16.3215808868408</v>
       </c>
       <c r="H223" t="n">
         <v>2233430</v>
@@ -6865,7 +6865,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G224" t="n">
-        <v>16.8316307067871</v>
+        <v>16.8316287994385</v>
       </c>
       <c r="H224" t="n">
         <v>966642</v>
@@ -6923,7 +6923,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>16.874137878418</v>
+        <v>16.8741359710693</v>
       </c>
       <c r="H226" t="n">
         <v>884597</v>
@@ -6952,7 +6952,7 @@
         <v>20.5</v>
       </c>
       <c r="G227" t="n">
-        <v>17.4266891479492</v>
+        <v>17.4266872406006</v>
       </c>
       <c r="H227" t="n">
         <v>1053882</v>
@@ -6981,7 +6981,7 @@
         <v>20.25</v>
       </c>
       <c r="G228" t="n">
-        <v>17.2141704559326</v>
+        <v>17.2141666412354</v>
       </c>
       <c r="H228" t="n">
         <v>1880282</v>
@@ -7039,7 +7039,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G230" t="n">
-        <v>17.0356483459473</v>
+        <v>17.0356502532959</v>
       </c>
       <c r="H230" t="n">
         <v>567307</v>
@@ -7097,7 +7097,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G232" t="n">
-        <v>17.3331775665283</v>
+        <v>17.333179473877</v>
       </c>
       <c r="H232" t="n">
         <v>738873</v>
@@ -7126,7 +7126,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>17.171667098999</v>
+        <v>17.1716651916504</v>
       </c>
       <c r="H233" t="n">
         <v>538504</v>
@@ -7155,7 +7155,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G234" t="n">
-        <v>16.7381210327148</v>
+        <v>16.7381248474121</v>
       </c>
       <c r="H234" t="n">
         <v>614560</v>
@@ -7184,7 +7184,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G235" t="n">
-        <v>16.7466239929199</v>
+        <v>16.7466220855713</v>
       </c>
       <c r="H235" t="n">
         <v>607586</v>
@@ -7213,7 +7213,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>17.0441493988037</v>
+        <v>17.0441513061523</v>
       </c>
       <c r="H236" t="n">
         <v>850377</v>
@@ -7242,7 +7242,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G237" t="n">
-        <v>16.9251403808594</v>
+        <v>16.9251384735107</v>
       </c>
       <c r="H237" t="n">
         <v>872092</v>
@@ -7271,7 +7271,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G238" t="n">
-        <v>16.9251403808594</v>
+        <v>16.9251384735107</v>
       </c>
       <c r="H238" t="n">
         <v>1108361</v>
@@ -7300,7 +7300,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G239" t="n">
-        <v>17.6732120513916</v>
+        <v>17.6732139587402</v>
       </c>
       <c r="H239" t="n">
         <v>924404</v>
@@ -7358,7 +7358,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G241" t="n">
-        <v>18.8463268280029</v>
+        <v>18.8463249206543</v>
       </c>
       <c r="H241" t="n">
         <v>1335115</v>
@@ -7445,7 +7445,7 @@
         <v>22</v>
       </c>
       <c r="G244" t="n">
-        <v>18.7018089294434</v>
+        <v>18.7018146514893</v>
       </c>
       <c r="H244" t="n">
         <v>881922</v>
@@ -7474,7 +7474,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>18.5317935943604</v>
+        <v>18.531795501709</v>
       </c>
       <c r="H245" t="n">
         <v>1378426</v>
@@ -7590,7 +7590,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G249" t="n">
-        <v>18.9653396606445</v>
+        <v>18.9653377532959</v>
       </c>
       <c r="H249" t="n">
         <v>594461</v>
@@ -7619,7 +7619,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G250" t="n">
-        <v>19.4158840179443</v>
+        <v>19.4158821105957</v>
       </c>
       <c r="H250" t="n">
         <v>888494</v>
@@ -7706,7 +7706,7 @@
         <v>22.5</v>
       </c>
       <c r="G253" t="n">
-        <v>19.1268501281738</v>
+        <v>19.1268539428711</v>
       </c>
       <c r="H253" t="n">
         <v>296318</v>
@@ -7735,7 +7735,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G254" t="n">
-        <v>19.2628650665283</v>
+        <v>19.2628631591797</v>
       </c>
       <c r="H254" t="n">
         <v>426455</v>
@@ -7764,7 +7764,7 @@
         <v>22.6700000762939</v>
       </c>
       <c r="G255" t="n">
-        <v>19.2713642120361</v>
+        <v>19.2713680267334</v>
       </c>
       <c r="H255" t="n">
         <v>481009</v>
@@ -7793,7 +7793,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4158840179443</v>
+        <v>19.4158821105957</v>
       </c>
       <c r="H256" t="n">
         <v>507615</v>
@@ -7851,7 +7851,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9939384460449</v>
+        <v>19.9939403533936</v>
       </c>
       <c r="H258" t="n">
         <v>773242</v>
@@ -7880,7 +7880,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G259" t="n">
-        <v>19.5688972473145</v>
+        <v>19.5688953399658</v>
       </c>
       <c r="H259" t="n">
         <v>1163965</v>
@@ -7909,7 +7909,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G260" t="n">
-        <v>19.4328842163086</v>
+        <v>19.43288230896</v>
       </c>
       <c r="H260" t="n">
         <v>871113</v>
@@ -7938,7 +7938,7 @@
         <v>22.9099998474121</v>
       </c>
       <c r="G261" t="n">
-        <v>19.4753875732422</v>
+        <v>19.4753856658936</v>
       </c>
       <c r="H261" t="n">
         <v>1241974</v>
@@ -7967,7 +7967,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G262" t="n">
-        <v>19.7389106750488</v>
+        <v>19.7389125823975</v>
       </c>
       <c r="H262" t="n">
         <v>628780</v>
@@ -7996,7 +7996,7 @@
         <v>23</v>
       </c>
       <c r="G263" t="n">
-        <v>19.5518951416016</v>
+        <v>19.5518932342529</v>
       </c>
       <c r="H263" t="n">
         <v>778597</v>
@@ -8054,7 +8054,7 @@
         <v>23.7900009155273</v>
       </c>
       <c r="G265" t="n">
-        <v>20.223461151123</v>
+        <v>20.2234592437744</v>
       </c>
       <c r="H265" t="n">
         <v>921307</v>
@@ -8083,7 +8083,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G266" t="n">
-        <v>19.8154201507568</v>
+        <v>19.8154220581055</v>
       </c>
       <c r="H266" t="n">
         <v>593415</v>
@@ -8112,7 +8112,7 @@
         <v>24.0900001525879</v>
       </c>
       <c r="G267" t="n">
-        <v>20.4784851074219</v>
+        <v>20.4784870147705</v>
       </c>
       <c r="H267" t="n">
         <v>711399</v>
@@ -8141,7 +8141,7 @@
         <v>24</v>
       </c>
       <c r="G268" t="n">
-        <v>20.4019737243652</v>
+        <v>20.4019756317139</v>
       </c>
       <c r="H268" t="n">
         <v>514717</v>
@@ -8257,7 +8257,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>19.8154201507568</v>
+        <v>19.8154220581055</v>
       </c>
       <c r="H272" t="n">
         <v>442156</v>
@@ -8344,7 +8344,7 @@
         <v>24.0900001525879</v>
       </c>
       <c r="G275" t="n">
-        <v>20.4784851074219</v>
+        <v>20.4784870147705</v>
       </c>
       <c r="H275" t="n">
         <v>873215</v>
@@ -8373,7 +8373,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G276" t="n">
-        <v>20.2064552307129</v>
+        <v>20.2064590454102</v>
       </c>
       <c r="H276" t="n">
         <v>392588</v>
@@ -8489,7 +8489,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G280" t="n">
-        <v>19.7899131774902</v>
+        <v>19.7899169921875</v>
       </c>
       <c r="H280" t="n">
         <v>941283</v>
@@ -8547,7 +8547,7 @@
         <v>23.2299995422363</v>
       </c>
       <c r="G282" t="n">
-        <v>19.7474136352539</v>
+        <v>19.7474098205566</v>
       </c>
       <c r="H282" t="n">
         <v>605006</v>
@@ -8605,7 +8605,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>19.4243812561035</v>
+        <v>19.4243850708008</v>
       </c>
       <c r="H284" t="n">
         <v>725073</v>
@@ -8634,7 +8634,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G285" t="n">
-        <v>19.1098518371582</v>
+        <v>19.1098480224609</v>
       </c>
       <c r="H285" t="n">
         <v>798657</v>
@@ -8663,7 +8663,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G286" t="n">
-        <v>19.3478755950928</v>
+        <v>19.3478736877441</v>
       </c>
       <c r="H286" t="n">
         <v>943427</v>
@@ -8692,7 +8692,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>19.8749217987061</v>
+        <v>19.8749237060547</v>
       </c>
       <c r="H287" t="n">
         <v>790971</v>
@@ -8721,7 +8721,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G288" t="n">
-        <v>19.8664245605469</v>
+        <v>19.8664226531982</v>
       </c>
       <c r="H288" t="n">
         <v>547163</v>
@@ -8750,7 +8750,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G289" t="n">
-        <v>20.2829685211182</v>
+        <v>20.2829647064209</v>
       </c>
       <c r="H289" t="n">
         <v>783178</v>
@@ -8808,7 +8808,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G291" t="n">
-        <v>20.2064552307129</v>
+        <v>20.2064590454102</v>
       </c>
       <c r="H291" t="n">
         <v>429672</v>
@@ -8924,7 +8924,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G295" t="n">
-        <v>20.4104766845703</v>
+        <v>20.4104804992676</v>
       </c>
       <c r="H295" t="n">
         <v>918579</v>
@@ -8953,7 +8953,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G296" t="n">
-        <v>19.7899131774902</v>
+        <v>19.7899169921875</v>
       </c>
       <c r="H296" t="n">
         <v>581863</v>
@@ -8982,7 +8982,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G297" t="n">
-        <v>19.3308734893799</v>
+        <v>19.3308773040771</v>
       </c>
       <c r="H297" t="n">
         <v>1537010</v>
@@ -9040,7 +9040,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>19.8749217987061</v>
+        <v>19.8749237060547</v>
       </c>
       <c r="H299" t="n">
         <v>1258162</v>
@@ -9069,7 +9069,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G300" t="n">
-        <v>20.4699821472168</v>
+        <v>20.4699840545654</v>
       </c>
       <c r="H300" t="n">
         <v>1074277</v>
@@ -9098,7 +9098,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G301" t="n">
-        <v>20.6059989929199</v>
+        <v>20.6059951782227</v>
       </c>
       <c r="H301" t="n">
         <v>911619</v>
@@ -9127,7 +9127,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G302" t="n">
-        <v>20.6059989929199</v>
+        <v>20.6059951782227</v>
       </c>
       <c r="H302" t="n">
         <v>314231</v>
@@ -9214,7 +9214,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G305" t="n">
-        <v>20.1129493713379</v>
+        <v>20.1129474639893</v>
       </c>
       <c r="H305" t="n">
         <v>393728</v>
@@ -9243,7 +9243,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G306" t="n">
-        <v>19.8154201507568</v>
+        <v>19.8154220581055</v>
       </c>
       <c r="H306" t="n">
         <v>704703</v>
@@ -9272,7 +9272,7 @@
         <v>23.3600006103516</v>
       </c>
       <c r="G307" t="n">
-        <v>19.8579254150391</v>
+        <v>19.8579273223877</v>
       </c>
       <c r="H307" t="n">
         <v>505529</v>
@@ -9388,7 +9388,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G311" t="n">
-        <v>20.2489624023438</v>
+        <v>20.2489604949951</v>
       </c>
       <c r="H311" t="n">
         <v>1041946</v>
@@ -9446,7 +9446,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G313" t="n">
-        <v>20.2404613494873</v>
+        <v>20.2404594421387</v>
       </c>
       <c r="H313" t="n">
         <v>435439</v>
@@ -9475,7 +9475,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9089260101318</v>
+        <v>19.9089298248291</v>
       </c>
       <c r="H314" t="n">
         <v>562091</v>
@@ -9504,7 +9504,7 @@
         <v>23.3600006103516</v>
       </c>
       <c r="G315" t="n">
-        <v>19.8579254150391</v>
+        <v>19.8579273223877</v>
       </c>
       <c r="H315" t="n">
         <v>1145871</v>
@@ -9533,7 +9533,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>20.316967010498</v>
+        <v>20.3169651031494</v>
       </c>
       <c r="H316" t="n">
         <v>793107</v>
@@ -9562,7 +9562,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G317" t="n">
-        <v>19.9939384460449</v>
+        <v>19.9939403533936</v>
       </c>
       <c r="H317" t="n">
         <v>480614</v>
@@ -9591,7 +9591,7 @@
         <v>22.75</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3393745422363</v>
+        <v>19.3393726348877</v>
       </c>
       <c r="H318" t="n">
         <v>1223519</v>
@@ -9620,7 +9620,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>18.999340057373</v>
+        <v>18.9993419647217</v>
       </c>
       <c r="H319" t="n">
         <v>905440</v>
@@ -9678,7 +9678,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7899131774902</v>
+        <v>19.7899169921875</v>
       </c>
       <c r="H321" t="n">
         <v>1177599</v>
@@ -9707,7 +9707,7 @@
         <v>24</v>
       </c>
       <c r="G322" t="n">
-        <v>20.4019737243652</v>
+        <v>20.4019756317139</v>
       </c>
       <c r="H322" t="n">
         <v>1835495</v>
@@ -9736,7 +9736,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>20.2319602966309</v>
+        <v>20.2319583892822</v>
       </c>
       <c r="H323" t="n">
         <v>1172906</v>
@@ -9794,7 +9794,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G325" t="n">
-        <v>19.8664245605469</v>
+        <v>19.8664226531982</v>
       </c>
       <c r="H325" t="n">
         <v>416664</v>
@@ -9823,7 +9823,7 @@
         <v>23.0699996948242</v>
       </c>
       <c r="G326" t="n">
-        <v>19.6113986968994</v>
+        <v>19.611400604248</v>
       </c>
       <c r="H326" t="n">
         <v>960327</v>
@@ -9852,7 +9852,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G327" t="n">
-        <v>19.6624050140381</v>
+        <v>19.6624031066895</v>
       </c>
       <c r="H327" t="n">
         <v>291695</v>
@@ -9910,7 +9910,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>19.4073791503906</v>
+        <v>19.4073810577393</v>
       </c>
       <c r="H329" t="n">
         <v>475737</v>
@@ -9939,7 +9939,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>19.0843486785889</v>
+        <v>19.0843467712402</v>
       </c>
       <c r="H330" t="n">
         <v>687272</v>
@@ -9968,7 +9968,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G331" t="n">
-        <v>18.8038234710693</v>
+        <v>18.803825378418</v>
       </c>
       <c r="H331" t="n">
         <v>498282</v>
@@ -9997,7 +9997,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G332" t="n">
-        <v>18.3872833251953</v>
+        <v>18.3872814178467</v>
       </c>
       <c r="H332" t="n">
         <v>726278</v>
@@ -10055,7 +10055,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>19.2968711853027</v>
+        <v>19.2968692779541</v>
       </c>
       <c r="H334" t="n">
         <v>890061</v>
@@ -10142,7 +10142,7 @@
         <v>23.7299995422363</v>
       </c>
       <c r="G337" t="n">
-        <v>20.1724510192871</v>
+        <v>20.1724529266357</v>
       </c>
       <c r="H337" t="n">
         <v>874360</v>
@@ -10171,7 +10171,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G338" t="n">
-        <v>20.1469554901123</v>
+        <v>20.1469535827637</v>
       </c>
       <c r="H338" t="n">
         <v>551421</v>
@@ -10200,7 +10200,7 @@
         <v>23.6299991607666</v>
       </c>
       <c r="G339" t="n">
-        <v>20.0874423980713</v>
+        <v>20.0874462127686</v>
       </c>
       <c r="H339" t="n">
         <v>587372</v>
@@ -10229,7 +10229,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>20.0619430541992</v>
+        <v>20.0619411468506</v>
       </c>
       <c r="H340" t="n">
         <v>668314</v>
@@ -10258,7 +10258,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>20.316967010498</v>
+        <v>20.3169651031494</v>
       </c>
       <c r="H341" t="n">
         <v>644233</v>
@@ -10287,7 +10287,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>20.0619430541992</v>
+        <v>20.0619411468506</v>
       </c>
       <c r="H342" t="n">
         <v>699221</v>
@@ -10316,7 +10316,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G343" t="n">
-        <v>20.7675094604492</v>
+        <v>20.7675113677979</v>
       </c>
       <c r="H343" t="n">
         <v>1793716</v>
@@ -10345,7 +10345,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G344" t="n">
-        <v>21.1415481567383</v>
+        <v>21.1415500640869</v>
       </c>
       <c r="H344" t="n">
         <v>1337374</v>
@@ -10403,7 +10403,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G346" t="n">
-        <v>20.6655044555664</v>
+        <v>20.6655006408691</v>
       </c>
       <c r="H346" t="n">
         <v>724204</v>
@@ -10432,7 +10432,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G347" t="n">
-        <v>21.022533416748</v>
+        <v>21.0225372314453</v>
       </c>
       <c r="H347" t="n">
         <v>775142</v>
@@ -10461,7 +10461,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G348" t="n">
-        <v>20.9205284118652</v>
+        <v>20.9205322265625</v>
       </c>
       <c r="H348" t="n">
         <v>1422415</v>
@@ -10548,7 +10548,7 @@
         <v>23.6900005340576</v>
       </c>
       <c r="G351" t="n">
-        <v>20.1384525299072</v>
+        <v>20.1384506225586</v>
       </c>
       <c r="H351" t="n">
         <v>1105919</v>
@@ -10577,7 +10577,7 @@
         <v>22.25</v>
       </c>
       <c r="G352" t="n">
-        <v>18.9143333435059</v>
+        <v>18.9143352508545</v>
       </c>
       <c r="H352" t="n">
         <v>2507165</v>
@@ -10606,7 +10606,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G353" t="n">
-        <v>19.0503463745117</v>
+        <v>19.0503425598145</v>
       </c>
       <c r="H353" t="n">
         <v>1483090</v>
@@ -10664,7 +10664,7 @@
         <v>23</v>
       </c>
       <c r="G355" t="n">
-        <v>19.6365375518799</v>
+        <v>19.6365356445312</v>
       </c>
       <c r="H355" t="n">
         <v>795664</v>
@@ -10722,7 +10722,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G357" t="n">
-        <v>19.6279964447021</v>
+        <v>19.6279983520508</v>
       </c>
       <c r="H357" t="n">
         <v>561258</v>
@@ -10780,7 +10780,7 @@
         <v>23</v>
       </c>
       <c r="G359" t="n">
-        <v>19.6365375518799</v>
+        <v>19.6365356445312</v>
       </c>
       <c r="H359" t="n">
         <v>403321</v>
@@ -10809,7 +10809,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>19.3377170562744</v>
+        <v>19.3377208709717</v>
       </c>
       <c r="H360" t="n">
         <v>178854</v>
@@ -10838,7 +10838,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G361" t="n">
-        <v>19.7133750915527</v>
+        <v>19.7133712768555</v>
       </c>
       <c r="H361" t="n">
         <v>958482</v>
@@ -10867,7 +10867,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G362" t="n">
-        <v>19.7304515838623</v>
+        <v>19.7304496765137</v>
       </c>
       <c r="H362" t="n">
         <v>597060</v>
@@ -10925,7 +10925,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>19.9780387878418</v>
+        <v>19.9780368804932</v>
       </c>
       <c r="H364" t="n">
         <v>498777</v>
@@ -10954,7 +10954,7 @@
         <v>23</v>
       </c>
       <c r="G365" t="n">
-        <v>19.6365375518799</v>
+        <v>19.6365356445312</v>
       </c>
       <c r="H365" t="n">
         <v>357460</v>
@@ -10983,7 +10983,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>19.6023864746094</v>
+        <v>19.6023826599121</v>
       </c>
       <c r="H366" t="n">
         <v>332393</v>
@@ -11041,7 +11041,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G368" t="n">
-        <v>19.6279964447021</v>
+        <v>19.6279983520508</v>
       </c>
       <c r="H368" t="n">
         <v>568772</v>
@@ -11099,7 +11099,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>19.7645988464355</v>
+        <v>19.7645969390869</v>
       </c>
       <c r="H370" t="n">
         <v>511060</v>
@@ -11157,7 +11157,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>19.5511589050293</v>
+        <v>19.5511608123779</v>
       </c>
       <c r="H372" t="n">
         <v>500340</v>
@@ -11215,7 +11215,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G374" t="n">
-        <v>19.3291778564453</v>
+        <v>19.3291816711426</v>
       </c>
       <c r="H374" t="n">
         <v>528731</v>
@@ -11360,7 +11360,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G379" t="n">
-        <v>18.9449882507324</v>
+        <v>18.9449901580811</v>
       </c>
       <c r="H379" t="n">
         <v>427581</v>
@@ -11389,7 +11389,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G380" t="n">
-        <v>19.1498908996582</v>
+        <v>19.1498928070068</v>
       </c>
       <c r="H380" t="n">
         <v>295661</v>
@@ -11418,7 +11418,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G381" t="n">
-        <v>18.87668800354</v>
+        <v>18.8766860961914</v>
       </c>
       <c r="H381" t="n">
         <v>858850</v>
@@ -11447,7 +11447,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>19.3633308410645</v>
+        <v>19.3633327484131</v>
       </c>
       <c r="H382" t="n">
         <v>1077882</v>
@@ -11505,7 +11505,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G384" t="n">
-        <v>18.6034832000732</v>
+        <v>18.6034851074219</v>
       </c>
       <c r="H384" t="n">
         <v>1537399</v>
@@ -11534,7 +11534,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G385" t="n">
-        <v>19.3377170562744</v>
+        <v>19.3377208709717</v>
       </c>
       <c r="H385" t="n">
         <v>806351</v>
@@ -11592,7 +11592,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G387" t="n">
-        <v>19.1498908996582</v>
+        <v>19.1498928070068</v>
       </c>
       <c r="H387" t="n">
         <v>907168</v>
@@ -11621,7 +11621,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>19.1669673919678</v>
+        <v>19.1669635772705</v>
       </c>
       <c r="H388" t="n">
         <v>475763</v>
@@ -11650,7 +11650,7 @@
         <v>22.5</v>
       </c>
       <c r="G389" t="n">
-        <v>19.2096538543701</v>
+        <v>19.2096557617188</v>
       </c>
       <c r="H389" t="n">
         <v>447100</v>
@@ -11708,7 +11708,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G391" t="n">
-        <v>19.2608757019043</v>
+        <v>19.2608814239502</v>
       </c>
       <c r="H391" t="n">
         <v>578421</v>
@@ -11737,7 +11737,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>19.5511589050293</v>
+        <v>19.5511608123779</v>
       </c>
       <c r="H392" t="n">
         <v>517577</v>
@@ -11795,7 +11795,7 @@
         <v>22.6100006103516</v>
       </c>
       <c r="G394" t="n">
-        <v>19.3035659790039</v>
+        <v>19.3035697937012</v>
       </c>
       <c r="H394" t="n">
         <v>351418</v>
@@ -11824,7 +11824,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>19.1669673919678</v>
+        <v>19.1669635772705</v>
       </c>
       <c r="H395" t="n">
         <v>372204</v>
@@ -11882,7 +11882,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G397" t="n">
-        <v>18.7230072021484</v>
+        <v>18.7230091094971</v>
       </c>
       <c r="H397" t="n">
         <v>495797</v>
@@ -11911,7 +11911,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G398" t="n">
-        <v>19.0303630828857</v>
+        <v>19.0303611755371</v>
       </c>
       <c r="H398" t="n">
         <v>1025833</v>
@@ -11940,7 +11940,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G399" t="n">
-        <v>18.5522594451904</v>
+        <v>18.5522556304932</v>
       </c>
       <c r="H399" t="n">
         <v>726007</v>
@@ -11969,7 +11969,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>18.8681507110596</v>
+        <v>18.8681468963623</v>
       </c>
       <c r="H400" t="n">
         <v>830912</v>
@@ -11998,7 +11998,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>18.5949440002441</v>
+        <v>18.5949420928955</v>
       </c>
       <c r="H401" t="n">
         <v>578837</v>
@@ -12114,7 +12114,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>18.2705135345459</v>
+        <v>18.2705173492432</v>
       </c>
       <c r="H405" t="n">
         <v>2722463</v>
@@ -12172,7 +12172,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>18.057071685791</v>
+        <v>18.0570697784424</v>
       </c>
       <c r="H407" t="n">
         <v>692565</v>
@@ -12288,7 +12288,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G411" t="n">
-        <v>17.9631614685059</v>
+        <v>17.9631595611572</v>
       </c>
       <c r="H411" t="n">
         <v>772668</v>
@@ -12346,7 +12346,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G413" t="n">
-        <v>17.3313770294189</v>
+        <v>17.3313732147217</v>
       </c>
       <c r="H413" t="n">
         <v>939866</v>
@@ -12375,7 +12375,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>17.1179332733154</v>
+        <v>17.1179351806641</v>
       </c>
       <c r="H414" t="n">
         <v>518090</v>
@@ -12433,7 +12433,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>17.5448150634766</v>
+        <v>17.5448169708252</v>
       </c>
       <c r="H416" t="n">
         <v>831785</v>
@@ -12491,7 +12491,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G418" t="n">
-        <v>17.2289257049561</v>
+        <v>17.2289237976074</v>
       </c>
       <c r="H418" t="n">
         <v>540865</v>
@@ -12520,7 +12520,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G419" t="n">
-        <v>17.2374649047852</v>
+        <v>17.2374610900879</v>
       </c>
       <c r="H419" t="n">
         <v>262848</v>
@@ -12549,7 +12549,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G420" t="n">
-        <v>17.3313770294189</v>
+        <v>17.3313732147217</v>
       </c>
       <c r="H420" t="n">
         <v>330139</v>
@@ -12607,7 +12607,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G422" t="n">
-        <v>17.1862354278564</v>
+        <v>17.1862373352051</v>
       </c>
       <c r="H422" t="n">
         <v>414774</v>
@@ -12694,7 +12694,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G425" t="n">
-        <v>16.4861507415771</v>
+        <v>16.4861526489258</v>
       </c>
       <c r="H425" t="n">
         <v>517543</v>
@@ -12723,7 +12723,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>17.2289257049561</v>
+        <v>17.2289237976074</v>
       </c>
       <c r="H426" t="n">
         <v>971454</v>
@@ -12781,7 +12781,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G428" t="n">
-        <v>17.5960445404053</v>
+        <v>17.5960426330566</v>
       </c>
       <c r="H428" t="n">
         <v>814045</v>
@@ -12839,7 +12839,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G430" t="n">
-        <v>17.6814193725586</v>
+        <v>17.6814212799072</v>
       </c>
       <c r="H430" t="n">
         <v>535402</v>
@@ -12868,7 +12868,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G431" t="n">
-        <v>17.6814193725586</v>
+        <v>17.6814212799072</v>
       </c>
       <c r="H431" t="n">
         <v>1015953</v>
@@ -12926,7 +12926,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G433" t="n">
-        <v>17.8265590667725</v>
+        <v>17.8265571594238</v>
       </c>
       <c r="H433" t="n">
         <v>229783</v>
@@ -12984,7 +12984,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G435" t="n">
-        <v>18.1339130401611</v>
+        <v>18.1339111328125</v>
       </c>
       <c r="H435" t="n">
         <v>942006</v>
@@ -13100,7 +13100,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>18.3132057189941</v>
+        <v>18.3132076263428</v>
       </c>
       <c r="H439" t="n">
         <v>368776</v>
@@ -13158,7 +13158,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G441" t="n">
-        <v>19.3377170562744</v>
+        <v>19.3377208709717</v>
       </c>
       <c r="H441" t="n">
         <v>3863835</v>
@@ -13187,7 +13187,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G442" t="n">
-        <v>19.7475242614746</v>
+        <v>19.747522354126</v>
       </c>
       <c r="H442" t="n">
         <v>2172637</v>
@@ -13245,7 +13245,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G444" t="n">
-        <v>19.0901260375977</v>
+        <v>19.0901279449463</v>
       </c>
       <c r="H444" t="n">
         <v>792978</v>
@@ -13274,7 +13274,7 @@
         <v>22.3299999237061</v>
       </c>
       <c r="G445" t="n">
-        <v>19.0645141601562</v>
+        <v>19.0645122528076</v>
       </c>
       <c r="H445" t="n">
         <v>894097</v>
@@ -13303,7 +13303,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>19.380407333374</v>
+        <v>19.3804035186768</v>
       </c>
       <c r="H446" t="n">
         <v>652030</v>
@@ -13332,7 +13332,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G447" t="n">
-        <v>19.3291778564453</v>
+        <v>19.3291816711426</v>
       </c>
       <c r="H447" t="n">
         <v>883283</v>
@@ -13390,7 +13390,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G449" t="n">
-        <v>19.7475242614746</v>
+        <v>19.747522354126</v>
       </c>
       <c r="H449" t="n">
         <v>887143</v>
@@ -13448,7 +13448,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G451" t="n">
-        <v>19.3462581634521</v>
+        <v>19.3462524414062</v>
       </c>
       <c r="H451" t="n">
         <v>1146594</v>
@@ -13477,7 +13477,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>19.5084705352783</v>
+        <v>19.508472442627</v>
       </c>
       <c r="H452" t="n">
         <v>514198</v>
@@ -13506,7 +13506,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G453" t="n">
-        <v>19.2779521942139</v>
+        <v>19.2779560089111</v>
       </c>
       <c r="H453" t="n">
         <v>409370</v>
@@ -13564,7 +13564,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G455" t="n">
-        <v>19.3889427185059</v>
+        <v>19.3889446258545</v>
       </c>
       <c r="H455" t="n">
         <v>515374</v>
@@ -13593,7 +13593,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G456" t="n">
-        <v>19.7133750915527</v>
+        <v>19.7133712768555</v>
       </c>
       <c r="H456" t="n">
         <v>705106</v>
@@ -13622,7 +13622,7 @@
         <v>23.2299995422363</v>
       </c>
       <c r="G457" t="n">
-        <v>19.8329029083252</v>
+        <v>19.8329010009766</v>
       </c>
       <c r="H457" t="n">
         <v>710035</v>
@@ -13651,7 +13651,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G458" t="n">
-        <v>19.9780387878418</v>
+        <v>19.9780368804932</v>
       </c>
       <c r="H458" t="n">
         <v>1011295</v>
@@ -13709,7 +13709,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>19.7731380462646</v>
+        <v>19.7731342315674</v>
       </c>
       <c r="H460" t="n">
         <v>585516</v>
@@ -13738,7 +13738,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G461" t="n">
-        <v>19.8670520782471</v>
+        <v>19.8670539855957</v>
       </c>
       <c r="H461" t="n">
         <v>542620</v>
@@ -13767,7 +13767,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G462" t="n">
-        <v>19.6109218597412</v>
+        <v>19.6109199523926</v>
       </c>
       <c r="H462" t="n">
         <v>340278</v>
@@ -13854,7 +13854,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G465" t="n">
-        <v>20.3536968231201</v>
+        <v>20.3536930084229</v>
       </c>
       <c r="H465" t="n">
         <v>783293</v>
@@ -13883,7 +13883,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G466" t="n">
-        <v>20.1061000823975</v>
+        <v>20.1061058044434</v>
       </c>
       <c r="H466" t="n">
         <v>639732</v>
@@ -13912,7 +13912,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G467" t="n">
-        <v>20.4049224853516</v>
+        <v>20.4049186706543</v>
       </c>
       <c r="H467" t="n">
         <v>647268</v>
@@ -13970,7 +13970,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G469" t="n">
-        <v>20.3280811309814</v>
+        <v>20.3280830383301</v>
       </c>
       <c r="H469" t="n">
         <v>469485</v>
@@ -13999,7 +13999,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G470" t="n">
-        <v>20.4305305480957</v>
+        <v>20.4305324554443</v>
       </c>
       <c r="H470" t="n">
         <v>641650</v>
@@ -14028,7 +14028,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G471" t="n">
-        <v>20.2853965759277</v>
+        <v>20.2853946685791</v>
       </c>
       <c r="H471" t="n">
         <v>573260</v>
@@ -14115,7 +14115,7 @@
         <v>23</v>
       </c>
       <c r="G474" t="n">
-        <v>19.6365375518799</v>
+        <v>19.6365356445312</v>
       </c>
       <c r="H474" t="n">
         <v>652301</v>
@@ -14144,7 +14144,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G475" t="n">
-        <v>19.4572448730469</v>
+        <v>19.4572467803955</v>
       </c>
       <c r="H475" t="n">
         <v>707003</v>
@@ -14202,7 +14202,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G477" t="n">
-        <v>19.7133750915527</v>
+        <v>19.7133712768555</v>
       </c>
       <c r="H477" t="n">
         <v>1269985</v>
@@ -14231,7 +14231,7 @@
         <v>23</v>
       </c>
       <c r="G478" t="n">
-        <v>19.6365375518799</v>
+        <v>19.6365356445312</v>
       </c>
       <c r="H478" t="n">
         <v>935317</v>
@@ -14260,7 +14260,7 @@
         <v>22.75</v>
       </c>
       <c r="G479" t="n">
-        <v>19.4230937957764</v>
+        <v>19.4230918884277</v>
       </c>
       <c r="H479" t="n">
         <v>343572</v>
@@ -14289,7 +14289,7 @@
         <v>22.6200008392334</v>
       </c>
       <c r="G480" t="n">
-        <v>19.3121070861816</v>
+        <v>19.3121089935303</v>
       </c>
       <c r="H480" t="n">
         <v>350797</v>
@@ -14318,7 +14318,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G481" t="n">
-        <v>18.8169250488281</v>
+        <v>18.8169231414795</v>
       </c>
       <c r="H481" t="n">
         <v>766693</v>
@@ -14405,7 +14405,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>20.02073097229</v>
+        <v>20.0207290649414</v>
       </c>
       <c r="H484" t="n">
         <v>644380</v>
@@ -14463,7 +14463,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G486" t="n">
-        <v>19.5767707824707</v>
+        <v>19.576774597168</v>
       </c>
       <c r="H486" t="n">
         <v>391370</v>
@@ -14492,7 +14492,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>19.5511589050293</v>
+        <v>19.5511608123779</v>
       </c>
       <c r="H487" t="n">
         <v>236896</v>
@@ -14550,7 +14550,7 @@
         <v>22.25</v>
       </c>
       <c r="G489" t="n">
-        <v>18.9962158203125</v>
+        <v>18.9962139129639</v>
       </c>
       <c r="H489" t="n">
         <v>418733</v>
@@ -14637,7 +14637,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>19.0815887451172</v>
+        <v>19.0815868377686</v>
       </c>
       <c r="H492" t="n">
         <v>366963</v>
@@ -14666,7 +14666,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G493" t="n">
-        <v>18.5522594451904</v>
+        <v>18.5522556304932</v>
       </c>
       <c r="H493" t="n">
         <v>589367</v>
@@ -14695,7 +14695,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G494" t="n">
-        <v>19.4572448730469</v>
+        <v>19.4572467803955</v>
       </c>
       <c r="H494" t="n">
         <v>1398654</v>
@@ -14753,7 +14753,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G496" t="n">
-        <v>19.0815887451172</v>
+        <v>19.0815868377686</v>
       </c>
       <c r="H496" t="n">
         <v>535254</v>
@@ -14782,7 +14782,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>18.8596115112305</v>
+        <v>18.8596134185791</v>
       </c>
       <c r="H497" t="n">
         <v>335764</v>
@@ -14811,7 +14811,7 @@
         <v>22.3299999237061</v>
       </c>
       <c r="G498" t="n">
-        <v>19.0645141601562</v>
+        <v>19.0645122528076</v>
       </c>
       <c r="H498" t="n">
         <v>667413</v>
@@ -14840,7 +14840,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>19.0815887451172</v>
+        <v>19.0815868377686</v>
       </c>
       <c r="H499" t="n">
         <v>331776</v>
@@ -14956,7 +14956,7 @@
         <v>22</v>
       </c>
       <c r="G503" t="n">
-        <v>18.782772064209</v>
+        <v>18.7827739715576</v>
       </c>
       <c r="H503" t="n">
         <v>558189</v>
@@ -15043,7 +15043,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G506" t="n">
-        <v>18.7230072021484</v>
+        <v>18.7230091094971</v>
       </c>
       <c r="H506" t="n">
         <v>433380</v>
@@ -15072,7 +15072,7 @@
         <v>22.25</v>
       </c>
       <c r="G507" t="n">
-        <v>18.9962158203125</v>
+        <v>18.9962139129639</v>
       </c>
       <c r="H507" t="n">
         <v>838196</v>
@@ -15101,7 +15101,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>19.3377170562744</v>
+        <v>19.3377208709717</v>
       </c>
       <c r="H508" t="n">
         <v>585297</v>
@@ -15130,7 +15130,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>19.6194591522217</v>
+        <v>19.619457244873</v>
       </c>
       <c r="H509" t="n">
         <v>455058</v>
@@ -15188,7 +15188,7 @@
         <v>22.5</v>
       </c>
       <c r="G511" t="n">
-        <v>19.2096538543701</v>
+        <v>19.2096557617188</v>
       </c>
       <c r="H511" t="n">
         <v>262056</v>
@@ -15217,7 +15217,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4913959503174</v>
+        <v>19.491397857666</v>
       </c>
       <c r="H512" t="n">
         <v>530848</v>
@@ -15246,7 +15246,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G513" t="n">
-        <v>19.7902088165283</v>
+        <v>19.7902126312256</v>
       </c>
       <c r="H513" t="n">
         <v>980905</v>
@@ -15304,7 +15304,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G515" t="n">
-        <v>20.3707733154297</v>
+        <v>20.3707695007324</v>
       </c>
       <c r="H515" t="n">
         <v>596326</v>
@@ -15333,7 +15333,7 @@
         <v>24</v>
       </c>
       <c r="G516" t="n">
-        <v>20.4902954101562</v>
+        <v>20.4902973175049</v>
       </c>
       <c r="H516" t="n">
         <v>589897</v>
@@ -15362,7 +15362,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G517" t="n">
-        <v>20.7805767059326</v>
+        <v>20.7805786132812</v>
       </c>
       <c r="H517" t="n">
         <v>661074</v>
@@ -15391,7 +15391,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G518" t="n">
-        <v>20.7122764587402</v>
+        <v>20.7122745513916</v>
       </c>
       <c r="H518" t="n">
         <v>690439</v>
@@ -15420,7 +15420,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G519" t="n">
-        <v>20.4732208251953</v>
+        <v>20.4732246398926</v>
       </c>
       <c r="H519" t="n">
         <v>864555</v>
@@ -15478,7 +15478,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G521" t="n">
-        <v>20.3366222381592</v>
+        <v>20.3366203308105</v>
       </c>
       <c r="H521" t="n">
         <v>611730</v>
@@ -15507,7 +15507,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>20.148796081543</v>
+        <v>20.1487941741943</v>
       </c>
       <c r="H522" t="n">
         <v>418116</v>
@@ -15565,7 +15565,7 @@
         <v>23.4799995422363</v>
       </c>
       <c r="G524" t="n">
-        <v>20.0463409423828</v>
+        <v>20.0463428497314</v>
       </c>
       <c r="H524" t="n">
         <v>497557</v>
@@ -15623,7 +15623,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G526" t="n">
-        <v>20.1658687591553</v>
+        <v>20.1658668518066</v>
       </c>
       <c r="H526" t="n">
         <v>636528</v>
@@ -15652,7 +15652,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G527" t="n">
-        <v>20.4561443328857</v>
+        <v>20.456148147583</v>
       </c>
       <c r="H527" t="n">
         <v>742200</v>
@@ -15710,7 +15710,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G529" t="n">
-        <v>20.4219951629639</v>
+        <v>20.4219970703125</v>
       </c>
       <c r="H529" t="n">
         <v>1294446</v>
@@ -15739,7 +15739,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>20.8318042755127</v>
+        <v>20.8318023681641</v>
       </c>
       <c r="H530" t="n">
         <v>598815</v>
@@ -15797,7 +15797,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G532" t="n">
-        <v>20.5244464874268</v>
+        <v>20.5244483947754</v>
       </c>
       <c r="H532" t="n">
         <v>662304</v>
@@ -15855,7 +15855,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G534" t="n">
-        <v>20.1146411895752</v>
+        <v>20.1146373748779</v>
       </c>
       <c r="H534" t="n">
         <v>634969</v>
@@ -15884,7 +15884,7 @@
         <v>23.0100002288818</v>
       </c>
       <c r="G535" t="n">
-        <v>19.6450710296631</v>
+        <v>19.6450729370117</v>
       </c>
       <c r="H535" t="n">
         <v>784173</v>
@@ -15913,7 +15913,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>19.3377170562744</v>
+        <v>19.3377208709717</v>
       </c>
       <c r="H536" t="n">
         <v>835419</v>
@@ -15942,7 +15942,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>18.8681507110596</v>
+        <v>18.8681468963623</v>
       </c>
       <c r="H537" t="n">
         <v>1121343</v>
@@ -15971,7 +15971,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G538" t="n">
-        <v>18.9022998809814</v>
+        <v>18.9022979736328</v>
       </c>
       <c r="H538" t="n">
         <v>1247092</v>
@@ -16029,7 +16029,7 @@
         <v>20.5100002288818</v>
       </c>
       <c r="G540" t="n">
-        <v>17.5106678009033</v>
+        <v>17.5106658935547</v>
       </c>
       <c r="H540" t="n">
         <v>1869657</v>
@@ -16058,7 +16058,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G541" t="n">
-        <v>17.8436336517334</v>
+        <v>17.8436298370361</v>
       </c>
       <c r="H541" t="n">
         <v>1228639</v>
@@ -16145,7 +16145,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>17.9204711914062</v>
+        <v>17.9204730987549</v>
       </c>
       <c r="H544" t="n">
         <v>533589</v>
@@ -16319,7 +16319,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G550" t="n">
-        <v>17.749719619751</v>
+        <v>17.7497215270996</v>
       </c>
       <c r="H550" t="n">
         <v>563752</v>
@@ -16406,7 +16406,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>17.3313770294189</v>
+        <v>17.3313732147217</v>
       </c>
       <c r="H553" t="n">
         <v>813238</v>
@@ -16464,7 +16464,7 @@
         <v>19.8549995422363</v>
       </c>
       <c r="G555" t="n">
-        <v>16.951452255249</v>
+        <v>16.9514541625977</v>
       </c>
       <c r="H555" t="n">
         <v>685015</v>
@@ -16493,7 +16493,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G556" t="n">
-        <v>17.1862354278564</v>
+        <v>17.1862373352051</v>
       </c>
       <c r="H556" t="n">
         <v>944539</v>
@@ -16522,7 +16522,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G557" t="n">
-        <v>17.9033966064453</v>
+        <v>17.9033946990967</v>
       </c>
       <c r="H557" t="n">
         <v>1295020</v>
@@ -16754,7 +16754,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G565" t="n">
-        <v>17.5448150634766</v>
+        <v>17.5448169708252</v>
       </c>
       <c r="H565" t="n">
         <v>760093</v>
@@ -16841,7 +16841,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G568" t="n">
-        <v>17.0581703186035</v>
+        <v>17.0581722259521</v>
       </c>
       <c r="H568" t="n">
         <v>894431</v>
@@ -16870,7 +16870,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G569" t="n">
-        <v>16.8746128082275</v>
+        <v>16.8746109008789</v>
       </c>
       <c r="H569" t="n">
         <v>1116818</v>
@@ -16928,7 +16928,7 @@
         <v>19.3549995422363</v>
       </c>
       <c r="G571" t="n">
-        <v>16.5245685577393</v>
+        <v>16.5245704650879</v>
       </c>
       <c r="H571" t="n">
         <v>1709664</v>
@@ -16986,7 +16986,7 @@
         <v>19.0849990844727</v>
       </c>
       <c r="G573" t="n">
-        <v>16.2940559387207</v>
+        <v>16.2940540313721</v>
       </c>
       <c r="H573" t="n">
         <v>1806358</v>
@@ -17102,7 +17102,7 @@
         <v>19.9650001525879</v>
       </c>
       <c r="G577" t="n">
-        <v>17.0453681945801</v>
+        <v>17.0453643798828</v>
       </c>
       <c r="H577" t="n">
         <v>1361863</v>
@@ -17131,7 +17131,7 @@
         <v>19.5550003051758</v>
       </c>
       <c r="G578" t="n">
-        <v>16.6953201293945</v>
+        <v>16.6953220367432</v>
       </c>
       <c r="H578" t="n">
         <v>557800</v>
@@ -17160,7 +17160,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G579" t="n">
-        <v>16.3068599700928</v>
+        <v>16.3068618774414</v>
       </c>
       <c r="H579" t="n">
         <v>1155007</v>
@@ -17218,7 +17218,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G581" t="n">
-        <v>16.4861507415771</v>
+        <v>16.4861526489258</v>
       </c>
       <c r="H581" t="n">
         <v>915783</v>
@@ -17334,7 +17334,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>16.8191204071045</v>
+        <v>16.8191223144531</v>
       </c>
       <c r="H585" t="n">
         <v>533746</v>
@@ -17392,7 +17392,7 @@
         <v>19.7250003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>16.8404674530029</v>
+        <v>16.8404636383057</v>
       </c>
       <c r="H587" t="n">
         <v>669242</v>
@@ -17421,7 +17421,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G588" t="n">
-        <v>17.0923233032227</v>
+        <v>17.092321395874</v>
       </c>
       <c r="H588" t="n">
         <v>998221</v>
@@ -17479,7 +17479,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G590" t="n">
-        <v>17.5362796783447</v>
+        <v>17.5362815856934</v>
       </c>
       <c r="H590" t="n">
         <v>664499</v>
@@ -17624,7 +17624,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>18.1851367950439</v>
+        <v>18.1851387023926</v>
       </c>
       <c r="H595" t="n">
         <v>874002</v>
@@ -17711,7 +17711,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>18.8254566192627</v>
+        <v>18.82546043396</v>
       </c>
       <c r="H598" t="n">
         <v>561311</v>
@@ -17769,7 +17769,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G600" t="n">
-        <v>19.3291778564453</v>
+        <v>19.3291816711426</v>
       </c>
       <c r="H600" t="n">
         <v>1494992</v>
@@ -17856,7 +17856,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G603" t="n">
-        <v>18.9791374206543</v>
+        <v>18.9791355133057</v>
       </c>
       <c r="H603" t="n">
         <v>556765</v>
@@ -18001,7 +18001,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G608" t="n">
-        <v>19.2033157348633</v>
+        <v>19.2033176422119</v>
       </c>
       <c r="H608" t="n">
         <v>627692</v>
@@ -18030,7 +18030,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G609" t="n">
-        <v>19.0487957000732</v>
+        <v>19.0487976074219</v>
       </c>
       <c r="H609" t="n">
         <v>671632</v>
@@ -18117,7 +18117,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G612" t="n">
-        <v>18.4650573730469</v>
+        <v>18.4650592803955</v>
       </c>
       <c r="H612" t="n">
         <v>1329240</v>
@@ -18175,7 +18175,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G614" t="n">
-        <v>17.3319187164307</v>
+        <v>17.3319149017334</v>
       </c>
       <c r="H614" t="n">
         <v>1421981</v>
@@ -18233,7 +18233,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G616" t="n">
-        <v>17.7353782653809</v>
+        <v>17.7353801727295</v>
       </c>
       <c r="H616" t="n">
         <v>656928</v>
@@ -18291,7 +18291,7 @@
         <v>21.25</v>
       </c>
       <c r="G618" t="n">
-        <v>18.2418594360352</v>
+        <v>18.2418632507324</v>
       </c>
       <c r="H618" t="n">
         <v>576382</v>
@@ -18320,7 +18320,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G619" t="n">
-        <v>18.1474304199219</v>
+        <v>18.1474342346191</v>
       </c>
       <c r="H619" t="n">
         <v>545184</v>
@@ -18378,7 +18378,7 @@
         <v>21.0900001525879</v>
       </c>
       <c r="G621" t="n">
-        <v>18.104513168335</v>
+        <v>18.1045112609863</v>
       </c>
       <c r="H621" t="n">
         <v>397015</v>
@@ -18407,7 +18407,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>17.9414081573486</v>
+        <v>17.9414043426514</v>
       </c>
       <c r="H622" t="n">
         <v>434949</v>
@@ -18436,7 +18436,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G623" t="n">
-        <v>18.3877964019775</v>
+        <v>18.3877983093262</v>
       </c>
       <c r="H623" t="n">
         <v>531769</v>
@@ -18523,7 +18523,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>18.1130981445312</v>
+        <v>18.1130962371826</v>
       </c>
       <c r="H626" t="n">
         <v>422227</v>
@@ -18610,7 +18610,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G629" t="n">
-        <v>17.9070701599121</v>
+        <v>17.9070720672607</v>
       </c>
       <c r="H629" t="n">
         <v>254334</v>
@@ -18726,7 +18726,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G633" t="n">
-        <v>17.3662509918213</v>
+        <v>17.3662490844727</v>
       </c>
       <c r="H633" t="n">
         <v>311023</v>
@@ -18755,7 +18755,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G634" t="n">
-        <v>17.7353782653809</v>
+        <v>17.7353801727295</v>
       </c>
       <c r="H634" t="n">
         <v>489396</v>
@@ -18813,7 +18813,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G636" t="n">
-        <v>17.8383941650391</v>
+        <v>17.8383960723877</v>
       </c>
       <c r="H636" t="n">
         <v>292527</v>
@@ -18842,7 +18842,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G637" t="n">
-        <v>18.018669128418</v>
+        <v>18.0186672210693</v>
       </c>
       <c r="H637" t="n">
         <v>364439</v>
@@ -18871,7 +18871,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>17.8212242126465</v>
+        <v>17.8212261199951</v>
       </c>
       <c r="H638" t="n">
         <v>367860</v>
@@ -18929,7 +18929,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G640" t="n">
-        <v>17.6752910614014</v>
+        <v>17.6752891540527</v>
       </c>
       <c r="H640" t="n">
         <v>264404</v>
@@ -19045,7 +19045,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G644" t="n">
-        <v>18.1560173034668</v>
+        <v>18.1560153961182</v>
       </c>
       <c r="H644" t="n">
         <v>414173</v>
@@ -19103,7 +19103,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G646" t="n">
-        <v>17.8212242126465</v>
+        <v>17.8212261199951</v>
       </c>
       <c r="H646" t="n">
         <v>206342</v>
@@ -19161,7 +19161,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G648" t="n">
-        <v>17.6752910614014</v>
+        <v>17.6752891540527</v>
       </c>
       <c r="H648" t="n">
         <v>312482</v>
@@ -19248,7 +19248,7 @@
         <v>19.9150009155273</v>
       </c>
       <c r="G651" t="n">
-        <v>17.0958480834961</v>
+        <v>17.0958461761475</v>
       </c>
       <c r="H651" t="n">
         <v>1464584</v>
@@ -19277,7 +19277,7 @@
         <v>19.2049999237061</v>
       </c>
       <c r="G652" t="n">
-        <v>16.4863529205322</v>
+        <v>16.4863510131836</v>
       </c>
       <c r="H652" t="n">
         <v>1783523</v>
@@ -19335,7 +19335,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G654" t="n">
-        <v>16.5593185424805</v>
+        <v>16.5593204498291</v>
       </c>
       <c r="H654" t="n">
         <v>669505</v>
@@ -19364,7 +19364,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G655" t="n">
-        <v>16.2931995391846</v>
+        <v>16.2932014465332</v>
       </c>
       <c r="H655" t="n">
         <v>349760</v>
@@ -19422,7 +19422,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>16.6108264923096</v>
+        <v>16.6108226776123</v>
       </c>
       <c r="H657" t="n">
         <v>573173</v>
@@ -19451,7 +19451,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G658" t="n">
-        <v>16.3790473937988</v>
+        <v>16.3790454864502</v>
       </c>
       <c r="H658" t="n">
         <v>324600</v>
@@ -19480,7 +19480,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>16.1816062927246</v>
+        <v>16.1816024780273</v>
       </c>
       <c r="H659" t="n">
         <v>729725</v>
@@ -19509,7 +19509,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G660" t="n">
-        <v>16.0871772766113</v>
+        <v>16.0871753692627</v>
       </c>
       <c r="H660" t="n">
         <v>486214</v>
@@ -19567,7 +19567,7 @@
         <v>17.75</v>
       </c>
       <c r="G662" t="n">
-        <v>15.2373189926147</v>
+        <v>15.2373180389404</v>
       </c>
       <c r="H662" t="n">
         <v>984539</v>
@@ -19596,7 +19596,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G663" t="n">
-        <v>15.245903968811</v>
+        <v>15.2459030151367</v>
       </c>
       <c r="H663" t="n">
         <v>931396</v>
@@ -19683,7 +19683,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G666" t="n">
-        <v>15.3746690750122</v>
+        <v>15.3746709823608</v>
       </c>
       <c r="H666" t="n">
         <v>401284</v>
@@ -19712,7 +19712,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G667" t="n">
-        <v>15.1686429977417</v>
+        <v>15.168643951416</v>
       </c>
       <c r="H667" t="n">
         <v>374627</v>
@@ -19741,7 +19741,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>15.1085548400879</v>
+        <v>15.1085529327393</v>
       </c>
       <c r="H668" t="n">
         <v>376567</v>
@@ -19799,7 +19799,7 @@
         <v>17.8349990844727</v>
       </c>
       <c r="G670" t="n">
-        <v>15.3102865219116</v>
+        <v>15.3102874755859</v>
       </c>
       <c r="H670" t="n">
         <v>758796</v>
@@ -19828,7 +19828,7 @@
         <v>17.6949996948242</v>
       </c>
       <c r="G671" t="n">
-        <v>15.1901063919067</v>
+        <v>15.1901054382324</v>
       </c>
       <c r="H671" t="n">
         <v>538324</v>
@@ -19857,7 +19857,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G672" t="n">
-        <v>15.1428909301758</v>
+        <v>15.1428928375244</v>
       </c>
       <c r="H672" t="n">
         <v>611295</v>
@@ -19915,7 +19915,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>15.3660831451416</v>
+        <v>15.3660869598389</v>
       </c>
       <c r="H674" t="n">
         <v>324849</v>
@@ -19944,7 +19944,7 @@
         <v>17.8950004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>15.3617916107178</v>
+        <v>15.3617935180664</v>
       </c>
       <c r="H675" t="n">
         <v>299237</v>
@@ -19973,7 +19973,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6922922134399</v>
+        <v>15.6922941207886</v>
       </c>
       <c r="H676" t="n">
         <v>758749</v>
@@ -20002,7 +20002,7 @@
         <v>18.2150001525879</v>
       </c>
       <c r="G677" t="n">
-        <v>15.63649559021</v>
+        <v>15.6364936828613</v>
       </c>
       <c r="H677" t="n">
         <v>433415</v>
@@ -20031,7 +20031,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.3231658935547</v>
+        <v>15.3231630325317</v>
       </c>
       <c r="H678" t="n">
         <v>730721</v>
@@ -20089,7 +20089,7 @@
         <v>17.6749992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>15.1729354858398</v>
+        <v>15.1729335784912</v>
       </c>
       <c r="H680" t="n">
         <v>889845</v>
@@ -20118,7 +20118,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G681" t="n">
-        <v>14.8681898117065</v>
+        <v>14.8681869506836</v>
       </c>
       <c r="H681" t="n">
         <v>880054</v>
@@ -20147,7 +20147,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G682" t="n">
-        <v>14.8853607177734</v>
+        <v>14.8853588104248</v>
       </c>
       <c r="H682" t="n">
         <v>681302</v>
@@ -20176,7 +20176,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G683" t="n">
-        <v>14.8639011383057</v>
+        <v>14.8638982772827</v>
       </c>
       <c r="H683" t="n">
         <v>836861</v>
@@ -20205,7 +20205,7 @@
         <v>17.625</v>
       </c>
       <c r="G684" t="n">
-        <v>15.1300134658813</v>
+        <v>15.13001537323</v>
       </c>
       <c r="H684" t="n">
         <v>895359</v>
@@ -20234,7 +20234,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G685" t="n">
-        <v>15.1171369552612</v>
+        <v>15.1171388626099</v>
       </c>
       <c r="H685" t="n">
         <v>664619</v>
@@ -20263,7 +20263,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G686" t="n">
-        <v>15.0184192657471</v>
+        <v>15.0184164047241</v>
       </c>
       <c r="H686" t="n">
         <v>792691</v>
@@ -20292,7 +20292,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G687" t="n">
-        <v>15.1858139038086</v>
+        <v>15.18581199646</v>
       </c>
       <c r="H687" t="n">
         <v>555458</v>
@@ -20321,7 +20321,7 @@
         <v>17.5849990844727</v>
       </c>
       <c r="G688" t="n">
-        <v>15.0956773757935</v>
+        <v>15.0956754684448</v>
       </c>
       <c r="H688" t="n">
         <v>307205</v>
@@ -20350,7 +20350,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G689" t="n">
-        <v>15.3575000762939</v>
+        <v>15.3575019836426</v>
       </c>
       <c r="H689" t="n">
         <v>900594</v>
@@ -20408,7 +20408,7 @@
         <v>17.6949996948242</v>
       </c>
       <c r="G691" t="n">
-        <v>15.1901063919067</v>
+        <v>15.1901054382324</v>
       </c>
       <c r="H691" t="n">
         <v>304710</v>
@@ -20466,7 +20466,7 @@
         <v>18.5149993896484</v>
       </c>
       <c r="G693" t="n">
-        <v>15.8940229415894</v>
+        <v>15.894024848938</v>
       </c>
       <c r="H693" t="n">
         <v>1194481</v>
@@ -20495,7 +20495,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G694" t="n">
-        <v>16.2416954040527</v>
+        <v>16.2416973114014</v>
       </c>
       <c r="H694" t="n">
         <v>767139</v>
@@ -20524,7 +20524,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G695" t="n">
-        <v>16.3189544677734</v>
+        <v>16.3189563751221</v>
       </c>
       <c r="H695" t="n">
         <v>1403018</v>
@@ -20582,7 +20582,7 @@
         <v>18.7849998474121</v>
       </c>
       <c r="G697" t="n">
-        <v>16.1258068084717</v>
+        <v>16.1258029937744</v>
       </c>
       <c r="H697" t="n">
         <v>371330</v>
@@ -20611,7 +20611,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G698" t="n">
-        <v>16.1086368560791</v>
+        <v>16.1086387634277</v>
       </c>
       <c r="H698" t="n">
         <v>358931</v>
@@ -20640,7 +20640,7 @@
         <v>18.6149997711182</v>
       </c>
       <c r="G699" t="n">
-        <v>15.9798679351807</v>
+        <v>15.9798698425293</v>
       </c>
       <c r="H699" t="n">
         <v>277462</v>
@@ -20727,7 +20727,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>15.9069023132324</v>
+        <v>15.9069042205811</v>
       </c>
       <c r="H702" t="n">
         <v>1725909</v>
@@ -20785,7 +20785,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G704" t="n">
-        <v>15.8639802932739</v>
+        <v>15.8639822006226</v>
       </c>
       <c r="H704" t="n">
         <v>471571</v>
@@ -20814,7 +20814,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G705" t="n">
-        <v>15.9326543807983</v>
+        <v>15.932656288147</v>
       </c>
       <c r="H705" t="n">
         <v>478868</v>
@@ -20843,7 +20843,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>15.7094612121582</v>
+        <v>15.7094631195068</v>
       </c>
       <c r="H706" t="n">
         <v>1214442</v>
@@ -20872,7 +20872,7 @@
         <v>17.875</v>
       </c>
       <c r="G707" t="n">
-        <v>15.3446264266968</v>
+        <v>15.3446245193481</v>
       </c>
       <c r="H707" t="n">
         <v>894970</v>
@@ -20930,7 +20930,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>15.2330293655396</v>
+        <v>15.2330265045166</v>
       </c>
       <c r="H709" t="n">
         <v>1657825</v>
@@ -20959,7 +20959,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G710" t="n">
-        <v>14.9282808303833</v>
+        <v>14.928279876709</v>
       </c>
       <c r="H710" t="n">
         <v>1131204</v>
@@ -21017,7 +21017,7 @@
         <v>17.5750007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>15.0870943069458</v>
+        <v>15.0870933532715</v>
       </c>
       <c r="H712" t="n">
         <v>627588</v>
@@ -21046,7 +21046,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>15.1385974884033</v>
+        <v>15.138599395752</v>
       </c>
       <c r="H713" t="n">
         <v>897158</v>
@@ -21075,7 +21075,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>14.8939447402954</v>
+        <v>14.8939437866211</v>
       </c>
       <c r="H714" t="n">
         <v>1644409</v>
@@ -21133,7 +21133,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G716" t="n">
-        <v>13.6835412979126</v>
+        <v>13.6835422515869</v>
       </c>
       <c r="H716" t="n">
         <v>1235607</v>
@@ -21162,7 +21162,7 @@
         <v>16.0849990844727</v>
       </c>
       <c r="G717" t="n">
-        <v>13.8080148696899</v>
+        <v>13.8080158233643</v>
       </c>
       <c r="H717" t="n">
         <v>1412991</v>
@@ -21191,7 +21191,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G718" t="n">
-        <v>13.6105756759644</v>
+        <v>13.61057472229</v>
       </c>
       <c r="H718" t="n">
         <v>705206</v>
@@ -21278,7 +21278,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G721" t="n">
-        <v>13.5976972579956</v>
+        <v>13.5976982116699</v>
       </c>
       <c r="H721" t="n">
         <v>481134</v>
@@ -21307,7 +21307,7 @@
         <v>16.2749996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>13.971118927002</v>
+        <v>13.9711198806763</v>
       </c>
       <c r="H722" t="n">
         <v>474719</v>
@@ -21365,7 +21365,7 @@
         <v>16.9750003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>14.5720291137695</v>
+        <v>14.5720281600952</v>
       </c>
       <c r="H724" t="n">
         <v>929718</v>
@@ -21423,7 +21423,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G726" t="n">
-        <v>14.7737617492676</v>
+        <v>14.7737627029419</v>
       </c>
       <c r="H726" t="n">
         <v>509787</v>
@@ -21452,7 +21452,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G727" t="n">
-        <v>14.5119390487671</v>
+        <v>14.5119380950928</v>
       </c>
       <c r="H727" t="n">
         <v>612493</v>
@@ -21481,7 +21481,7 @@
         <v>16.5949993133545</v>
       </c>
       <c r="G728" t="n">
-        <v>14.2458200454712</v>
+        <v>14.2458209991455</v>
       </c>
       <c r="H728" t="n">
         <v>837071</v>
@@ -21510,7 +21510,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G729" t="n">
-        <v>14.6836261749268</v>
+        <v>14.6836252212524</v>
       </c>
       <c r="H729" t="n">
         <v>1677998</v>
@@ -21539,7 +21539,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G730" t="n">
-        <v>14.632119178772</v>
+        <v>14.6321210861206</v>
       </c>
       <c r="H730" t="n">
         <v>893306</v>
@@ -21568,7 +21568,7 @@
         <v>17.0349998474121</v>
       </c>
       <c r="G731" t="n">
-        <v>14.62353515625</v>
+        <v>14.6235342025757</v>
       </c>
       <c r="H731" t="n">
         <v>377770</v>
@@ -21597,7 +21597,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G732" t="n">
-        <v>14.1299304962158</v>
+        <v>14.1299314498901</v>
       </c>
       <c r="H732" t="n">
         <v>764307</v>
@@ -21655,7 +21655,7 @@
         <v>16.875</v>
       </c>
       <c r="G734" t="n">
-        <v>14.4861850738525</v>
+        <v>14.4861841201782</v>
       </c>
       <c r="H734" t="n">
         <v>604648</v>
@@ -21713,7 +21713,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>13.838062286377</v>
+        <v>13.8380632400513</v>
       </c>
       <c r="H736" t="n">
         <v>729554</v>
@@ -21742,7 +21742,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G737" t="n">
-        <v>13.7608013153076</v>
+        <v>13.7608032226562</v>
       </c>
       <c r="H737" t="n">
         <v>605571</v>
@@ -21771,7 +21771,7 @@
         <v>16</v>
       </c>
       <c r="G738" t="n">
-        <v>13.7350473403931</v>
+        <v>13.7350492477417</v>
       </c>
       <c r="H738" t="n">
         <v>530208</v>
@@ -21800,7 +21800,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G739" t="n">
-        <v>14.0526733398438</v>
+        <v>14.0526723861694</v>
       </c>
       <c r="H739" t="n">
         <v>751544</v>
@@ -21829,7 +21829,7 @@
         <v>16.0450000762939</v>
       </c>
       <c r="G740" t="n">
-        <v>13.7736787796021</v>
+        <v>13.7736797332764</v>
       </c>
       <c r="H740" t="n">
         <v>382297</v>
@@ -21858,7 +21858,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G741" t="n">
-        <v>14.0483808517456</v>
+        <v>14.0483798980713</v>
       </c>
       <c r="H741" t="n">
         <v>772377</v>
@@ -21887,7 +21887,7 @@
         <v>17.0550003051758</v>
       </c>
       <c r="G742" t="n">
-        <v>14.6407022476196</v>
+        <v>14.6407051086426</v>
       </c>
       <c r="H742" t="n">
         <v>640080</v>
@@ -21945,7 +21945,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>14.4218006134033</v>
+        <v>14.4217987060547</v>
       </c>
       <c r="H744" t="n">
         <v>538212</v>
@@ -21974,7 +21974,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>14.2930355072021</v>
+        <v>14.2930345535278</v>
       </c>
       <c r="H745" t="n">
         <v>461340</v>
@@ -22032,7 +22032,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G747" t="n">
-        <v>14.7480087280273</v>
+        <v>14.7480096817017</v>
       </c>
       <c r="H747" t="n">
         <v>1263450</v>
@@ -22061,7 +22061,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G748" t="n">
-        <v>14.4260921478271</v>
+        <v>14.4260940551758</v>
       </c>
       <c r="H748" t="n">
         <v>550639</v>
@@ -22119,7 +22119,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G750" t="n">
-        <v>13.6148681640625</v>
+        <v>13.6148662567139</v>
       </c>
       <c r="H750" t="n">
         <v>993295</v>
@@ -22148,7 +22148,7 @@
         <v>15.625</v>
       </c>
       <c r="G751" t="n">
-        <v>13.4131326675415</v>
+        <v>13.4131345748901</v>
       </c>
       <c r="H751" t="n">
         <v>685551</v>
@@ -22177,7 +22177,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>12.9624519348145</v>
+        <v>12.9624509811401</v>
       </c>
       <c r="H752" t="n">
         <v>808165</v>
@@ -22206,7 +22206,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>13.2199850082397</v>
+        <v>13.2199840545654</v>
       </c>
       <c r="H753" t="n">
         <v>628778</v>
@@ -22235,7 +22235,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G754" t="n">
-        <v>13.2714900970459</v>
+        <v>13.2714910507202</v>
       </c>
       <c r="H754" t="n">
         <v>633668</v>
@@ -22264,7 +22264,7 @@
         <v>15.1049995422363</v>
       </c>
       <c r="G755" t="n">
-        <v>12.9667453765869</v>
+        <v>12.9667444229126</v>
       </c>
       <c r="H755" t="n">
         <v>638381</v>
@@ -22293,7 +22293,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G756" t="n">
-        <v>12.9710369110107</v>
+        <v>12.9710359573364</v>
       </c>
       <c r="H756" t="n">
         <v>537263</v>
@@ -22322,7 +22322,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>12.9195308685303</v>
+        <v>12.919529914856</v>
       </c>
       <c r="H757" t="n">
         <v>640368</v>
@@ -22380,7 +22380,7 @@
         <v>15.2849998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>13.121262550354</v>
+        <v>13.1212615966797</v>
       </c>
       <c r="H759" t="n">
         <v>486375</v>
@@ -22496,7 +22496,7 @@
         <v>15.0249996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>12.8980693817139</v>
+        <v>12.8980703353882</v>
       </c>
       <c r="H763" t="n">
         <v>433738</v>
@@ -22583,7 +22583,7 @@
         <v>15.2550001144409</v>
       </c>
       <c r="G766" t="n">
-        <v>13.0955104827881</v>
+        <v>13.0955114364624</v>
       </c>
       <c r="H766" t="n">
         <v>762096</v>
@@ -22612,7 +22612,7 @@
         <v>15.3950004577637</v>
       </c>
       <c r="G767" t="n">
-        <v>13.2156915664673</v>
+        <v>13.2156925201416</v>
       </c>
       <c r="H767" t="n">
         <v>476977</v>
@@ -22757,7 +22757,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G772" t="n">
-        <v>13.6749563217163</v>
+        <v>13.6749582290649</v>
       </c>
       <c r="H772" t="n">
         <v>335035</v>
@@ -22786,7 +22786,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G773" t="n">
-        <v>13.8037233352661</v>
+        <v>13.8037223815918</v>
       </c>
       <c r="H773" t="n">
         <v>827058</v>
@@ -22931,7 +22931,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G778" t="n">
-        <v>13.9153203964233</v>
+        <v>13.9153184890747</v>
       </c>
       <c r="H778" t="n">
         <v>322667</v>
@@ -22960,7 +22960,7 @@
         <v>16.0450000762939</v>
       </c>
       <c r="G779" t="n">
-        <v>13.7736787796021</v>
+        <v>13.7736797332764</v>
       </c>
       <c r="H779" t="n">
         <v>382568</v>
@@ -23018,7 +23018,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G781" t="n">
-        <v>14.1771450042725</v>
+        <v>14.1771459579468</v>
       </c>
       <c r="H781" t="n">
         <v>809129</v>
@@ -23047,7 +23047,7 @@
         <v>16.7649993896484</v>
       </c>
       <c r="G782" t="n">
-        <v>14.3917531967163</v>
+        <v>14.3917541503906</v>
       </c>
       <c r="H782" t="n">
         <v>1512114</v>
@@ -23076,7 +23076,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>14.2930355072021</v>
+        <v>14.2930345535278</v>
       </c>
       <c r="H783" t="n">
         <v>529339</v>
@@ -23134,7 +23134,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G785" t="n">
-        <v>14.3102045059204</v>
+        <v>14.3102025985718</v>
       </c>
       <c r="H785" t="n">
         <v>333488</v>
@@ -23163,7 +23163,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>14.2071895599365</v>
+        <v>14.2071905136108</v>
       </c>
       <c r="H786" t="n">
         <v>437564</v>
@@ -23192,7 +23192,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G787" t="n">
-        <v>14.4561386108398</v>
+        <v>14.4561395645142</v>
       </c>
       <c r="H787" t="n">
         <v>752563</v>
@@ -23250,7 +23250,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G789" t="n">
-        <v>14.4260921478271</v>
+        <v>14.4260940551758</v>
       </c>
       <c r="H789" t="n">
         <v>556882</v>
@@ -23308,7 +23308,7 @@
         <v>16.1949996948242</v>
       </c>
       <c r="G791" t="n">
-        <v>13.9024438858032</v>
+        <v>13.9024448394775</v>
       </c>
       <c r="H791" t="n">
         <v>529649</v>
@@ -23337,7 +23337,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G792" t="n">
-        <v>14.1943130493164</v>
+        <v>14.1943140029907</v>
       </c>
       <c r="H792" t="n">
         <v>581056</v>
@@ -23366,7 +23366,7 @@
         <v>16.5849990844727</v>
       </c>
       <c r="G793" t="n">
-        <v>14.2372350692749</v>
+        <v>14.2372360229492</v>
       </c>
       <c r="H793" t="n">
         <v>323073</v>
@@ -23395,7 +23395,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G794" t="n">
-        <v>14.3874645233154</v>
+        <v>14.3874635696411</v>
       </c>
       <c r="H794" t="n">
         <v>368697</v>
@@ -23424,7 +23424,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>14.250114440918</v>
+        <v>14.2501153945923</v>
       </c>
       <c r="H795" t="n">
         <v>450724</v>
@@ -23453,7 +23453,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G796" t="n">
-        <v>14.4303827285767</v>
+        <v>14.430383682251</v>
       </c>
       <c r="H796" t="n">
         <v>462068</v>
@@ -23540,7 +23540,7 @@
         <v>17.1149997711182</v>
       </c>
       <c r="G799" t="n">
-        <v>14.6922101974487</v>
+        <v>14.692211151123</v>
       </c>
       <c r="H799" t="n">
         <v>408496</v>
@@ -23569,7 +23569,7 @@
         <v>16.9850006103516</v>
       </c>
       <c r="G800" t="n">
-        <v>14.5806140899658</v>
+        <v>14.5806131362915</v>
       </c>
       <c r="H800" t="n">
         <v>321074</v>
@@ -23598,7 +23598,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G801" t="n">
-        <v>14.6836261749268</v>
+        <v>14.6836252212524</v>
       </c>
       <c r="H801" t="n">
         <v>584812</v>
@@ -23627,7 +23627,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G802" t="n">
-        <v>14.5677337646484</v>
+        <v>14.5677347183228</v>
       </c>
       <c r="H802" t="n">
         <v>342925</v>
@@ -23685,7 +23685,7 @@
         <v>17.0349998474121</v>
       </c>
       <c r="G804" t="n">
-        <v>14.62353515625</v>
+        <v>14.6235342025757</v>
       </c>
       <c r="H804" t="n">
         <v>376036</v>
@@ -23714,7 +23714,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>14.7651777267456</v>
+        <v>14.7651786804199</v>
       </c>
       <c r="H805" t="n">
         <v>570777</v>
@@ -23743,7 +23743,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G806" t="n">
-        <v>14.9454479217529</v>
+        <v>14.9454488754272</v>
       </c>
       <c r="H806" t="n">
         <v>534902</v>
@@ -23772,7 +23772,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G807" t="n">
-        <v>14.9840803146362</v>
+        <v>14.9840812683105</v>
       </c>
       <c r="H807" t="n">
         <v>250683</v>
@@ -23801,7 +23801,7 @@
         <v>17.4449996948242</v>
       </c>
       <c r="G808" t="n">
-        <v>14.9754962921143</v>
+        <v>14.9754953384399</v>
       </c>
       <c r="H808" t="n">
         <v>248771</v>
@@ -23830,7 +23830,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>14.872483253479</v>
+        <v>14.8724851608276</v>
       </c>
       <c r="H809" t="n">
         <v>407455</v>
@@ -23859,7 +23859,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>14.6149501800537</v>
+        <v>14.614951133728</v>
       </c>
       <c r="H810" t="n">
         <v>583004</v>
@@ -23888,7 +23888,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G811" t="n">
-        <v>14.3960494995117</v>
+        <v>14.3960485458374</v>
       </c>
       <c r="H811" t="n">
         <v>494881</v>
@@ -23946,7 +23946,7 @@
         <v>17.1849994659424</v>
       </c>
       <c r="G813" t="n">
-        <v>14.7522983551025</v>
+        <v>14.7523012161255</v>
       </c>
       <c r="H813" t="n">
         <v>526349</v>
@@ -23975,7 +23975,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G814" t="n">
-        <v>15.0055418014526</v>
+        <v>15.0055389404297</v>
       </c>
       <c r="H814" t="n">
         <v>519067</v>
@@ -24004,7 +24004,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G815" t="n">
-        <v>14.9712038040161</v>
+        <v>14.9712047576904</v>
       </c>
       <c r="H815" t="n">
         <v>375273</v>
@@ -24033,7 +24033,7 @@
         <v>17.6350002288818</v>
       </c>
       <c r="G816" t="n">
-        <v>15.1385974884033</v>
+        <v>15.138599395752</v>
       </c>
       <c r="H816" t="n">
         <v>497777</v>
@@ -24062,7 +24062,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G817" t="n">
-        <v>15.177227973938</v>
+        <v>15.1772308349609</v>
       </c>
       <c r="H817" t="n">
         <v>457095</v>
@@ -24091,7 +24091,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G818" t="n">
-        <v>15.2029781341553</v>
+        <v>15.2029809951782</v>
       </c>
       <c r="H818" t="n">
         <v>400053</v>
@@ -24120,7 +24120,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G819" t="n">
-        <v>15.4776840209961</v>
+        <v>15.4776821136475</v>
       </c>
       <c r="H819" t="n">
         <v>2021294</v>
@@ -24178,7 +24178,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>15.1514730453491</v>
+        <v>15.1514759063721</v>
       </c>
       <c r="H821" t="n">
         <v>2365125</v>
@@ -24207,7 +24207,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>15.0441694259644</v>
+        <v>15.0441675186157</v>
       </c>
       <c r="H822" t="n">
         <v>546006</v>
@@ -24236,7 +24236,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G823" t="n">
-        <v>14.9669103622437</v>
+        <v>14.966911315918</v>
       </c>
       <c r="H823" t="n">
         <v>913843</v>
@@ -24265,7 +24265,7 @@
         <v>17.5650005340576</v>
       </c>
       <c r="G824" t="n">
-        <v>15.0785083770752</v>
+        <v>15.0785074234009</v>
       </c>
       <c r="H824" t="n">
         <v>865751</v>
@@ -24294,7 +24294,7 @@
         <v>17.75</v>
       </c>
       <c r="G825" t="n">
-        <v>15.2373189926147</v>
+        <v>15.2373180389404</v>
       </c>
       <c r="H825" t="n">
         <v>2168126</v>
@@ -24323,7 +24323,7 @@
         <v>18.2350006103516</v>
       </c>
       <c r="G826" t="n">
-        <v>15.6536664962769</v>
+        <v>15.6536626815796</v>
       </c>
       <c r="H826" t="n">
         <v>1473738</v>
@@ -24352,7 +24352,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G827" t="n">
-        <v>16.1300983428955</v>
+        <v>16.1301002502441</v>
       </c>
       <c r="H827" t="n">
         <v>1447618</v>
@@ -24381,7 +24381,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G828" t="n">
-        <v>16.2931995391846</v>
+        <v>16.2932014465332</v>
       </c>
       <c r="H828" t="n">
         <v>1108106</v>
@@ -24410,7 +24410,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>16.4820594787598</v>
+        <v>16.4820575714111</v>
       </c>
       <c r="H829" t="n">
         <v>751173</v>
@@ -24468,7 +24468,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G831" t="n">
-        <v>16.3275375366211</v>
+        <v>16.3275394439697</v>
       </c>
       <c r="H831" t="n">
         <v>1245338</v>
@@ -24497,7 +24497,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>16.3361225128174</v>
+        <v>16.336124420166</v>
       </c>
       <c r="H832" t="n">
         <v>548988</v>
@@ -24642,7 +24642,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G837" t="n">
-        <v>16.4133834838867</v>
+        <v>16.4133815765381</v>
       </c>
       <c r="H837" t="n">
         <v>632164</v>
@@ -24700,7 +24700,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.6108264923096</v>
+        <v>16.6108226776123</v>
       </c>
       <c r="H839" t="n">
         <v>599292</v>
@@ -24729,7 +24729,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>17.0400428771973</v>
+        <v>17.0400447845459</v>
       </c>
       <c r="H840" t="n">
         <v>1773951</v>
@@ -24845,7 +24845,7 @@
         <v>19.4150009155273</v>
       </c>
       <c r="G844" t="n">
-        <v>16.6666221618652</v>
+        <v>16.6666259765625</v>
       </c>
       <c r="H844" t="n">
         <v>370896</v>
@@ -24903,7 +24903,7 @@
         <v>19.8299999237061</v>
       </c>
       <c r="G846" t="n">
-        <v>17.0228786468506</v>
+        <v>17.022876739502</v>
       </c>
       <c r="H846" t="n">
         <v>666949</v>
@@ -24961,7 +24961,7 @@
         <v>19.9150009155273</v>
       </c>
       <c r="G848" t="n">
-        <v>17.0958480834961</v>
+        <v>17.0958461761475</v>
       </c>
       <c r="H848" t="n">
         <v>668248</v>
@@ -24990,7 +24990,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>16.6966705322266</v>
+        <v>16.6966686248779</v>
       </c>
       <c r="H849" t="n">
         <v>1706852</v>
@@ -25077,7 +25077,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G852" t="n">
-        <v>16.164436340332</v>
+        <v>16.1644325256348</v>
       </c>
       <c r="H852" t="n">
         <v>1438428</v>
@@ -25106,7 +25106,7 @@
         <v>19.25</v>
       </c>
       <c r="G853" t="n">
-        <v>16.5249805450439</v>
+        <v>16.5249824523926</v>
       </c>
       <c r="H853" t="n">
         <v>721349</v>
@@ -25164,7 +25164,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G855" t="n">
-        <v>16.2588653564453</v>
+        <v>16.2588634490967</v>
       </c>
       <c r="H855" t="n">
         <v>714816</v>
@@ -25222,7 +25222,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>16.5035190582275</v>
+        <v>16.5035171508789</v>
       </c>
       <c r="H857" t="n">
         <v>600288</v>
@@ -25280,7 +25280,7 @@
         <v>18.8050003051758</v>
       </c>
       <c r="G859" t="n">
-        <v>16.2480430603027</v>
+        <v>16.248046875</v>
       </c>
       <c r="H859" t="n">
         <v>586460</v>
@@ -25338,7 +25338,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>16.5029315948486</v>
+        <v>16.5029335021973</v>
       </c>
       <c r="H861" t="n">
         <v>488256</v>
@@ -25425,7 +25425,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G864" t="n">
-        <v>15.7425889968872</v>
+        <v>15.7425870895386</v>
       </c>
       <c r="H864" t="n">
         <v>425102</v>
@@ -25483,7 +25483,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>15.1636877059937</v>
+        <v>15.163688659668</v>
       </c>
       <c r="H866" t="n">
         <v>939210</v>
@@ -25512,7 +25512,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G867" t="n">
-        <v>15.6043434143066</v>
+        <v>15.604341506958</v>
       </c>
       <c r="H867" t="n">
         <v>1057150</v>
@@ -25599,7 +25599,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>15.4660987854004</v>
+        <v>15.466100692749</v>
       </c>
       <c r="H870" t="n">
         <v>935013</v>
@@ -25628,7 +25628,7 @@
         <v>17.7549991607666</v>
       </c>
       <c r="G871" t="n">
-        <v>15.3408136367798</v>
+        <v>15.3408155441284</v>
       </c>
       <c r="H871" t="n">
         <v>759316</v>
@@ -25657,7 +25657,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G872" t="n">
-        <v>15.1809682846069</v>
+        <v>15.1809692382812</v>
       </c>
       <c r="H872" t="n">
         <v>620900</v>
@@ -25744,7 +25744,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G875" t="n">
-        <v>15.5093021392822</v>
+        <v>15.5093002319336</v>
       </c>
       <c r="H875" t="n">
         <v>908373</v>
@@ -25773,7 +25773,7 @@
         <v>17.5</v>
       </c>
       <c r="G876" t="n">
-        <v>15.1204891204834</v>
+        <v>15.1204872131348</v>
       </c>
       <c r="H876" t="n">
         <v>671741</v>
@@ -25802,7 +25802,7 @@
         <v>17.8950004577637</v>
       </c>
       <c r="G877" t="n">
-        <v>15.4617776870728</v>
+        <v>15.4617795944214</v>
       </c>
       <c r="H877" t="n">
         <v>686717</v>
@@ -25831,7 +25831,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G878" t="n">
-        <v>15.4142570495605</v>
+        <v>15.4142589569092</v>
       </c>
       <c r="H878" t="n">
         <v>706225</v>
@@ -25889,7 +25889,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G880" t="n">
-        <v>15.4790573120117</v>
+        <v>15.479061126709</v>
       </c>
       <c r="H880" t="n">
         <v>898349</v>
@@ -25918,7 +25918,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G881" t="n">
-        <v>15.3451366424561</v>
+        <v>15.3451347351074</v>
       </c>
       <c r="H881" t="n">
         <v>768994</v>
@@ -25976,7 +25976,7 @@
         <v>17.4950008392334</v>
       </c>
       <c r="G883" t="n">
-        <v>15.1161689758301</v>
+        <v>15.1161670684814</v>
       </c>
       <c r="H883" t="n">
         <v>1051210</v>
@@ -26005,7 +26005,7 @@
         <v>17.4150009155273</v>
       </c>
       <c r="G884" t="n">
-        <v>15.0470457077026</v>
+        <v>15.0470476150513</v>
       </c>
       <c r="H884" t="n">
         <v>412961</v>
@@ -26034,7 +26034,7 @@
         <v>17.6650009155273</v>
       </c>
       <c r="G885" t="n">
-        <v>15.263053894043</v>
+        <v>15.2630548477173</v>
       </c>
       <c r="H885" t="n">
         <v>1520269</v>
@@ -26092,7 +26092,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G887" t="n">
-        <v>15.5265798568726</v>
+        <v>15.5265779495239</v>
       </c>
       <c r="H887" t="n">
         <v>752868</v>
@@ -26150,7 +26150,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G889" t="n">
-        <v>15.4660987854004</v>
+        <v>15.466100692749</v>
       </c>
       <c r="H889" t="n">
         <v>878912</v>
@@ -26179,7 +26179,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>15.4877004623413</v>
+        <v>15.4876985549927</v>
       </c>
       <c r="H890" t="n">
         <v>690710</v>
@@ -26295,7 +26295,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G894" t="n">
-        <v>16.2437210083008</v>
+        <v>16.2437229156494</v>
       </c>
       <c r="H894" t="n">
         <v>440372</v>
@@ -26324,7 +26324,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>16.0709209442139</v>
+        <v>16.0709190368652</v>
       </c>
       <c r="H895" t="n">
         <v>438496</v>
@@ -26353,7 +26353,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G896" t="n">
-        <v>16.2350845336914</v>
+        <v>16.23508644104</v>
       </c>
       <c r="H896" t="n">
         <v>801662</v>
@@ -26382,7 +26382,7 @@
         <v>18.7150001525879</v>
       </c>
       <c r="G897" t="n">
-        <v>16.1702823638916</v>
+        <v>16.1702842712402</v>
       </c>
       <c r="H897" t="n">
         <v>521307</v>
@@ -26469,7 +26469,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>16.5893363952637</v>
+        <v>16.589334487915</v>
       </c>
       <c r="H900" t="n">
         <v>601137</v>
@@ -26527,7 +26527,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G902" t="n">
-        <v>16.5634136199951</v>
+        <v>16.5634117126465</v>
       </c>
       <c r="H902" t="n">
         <v>519014</v>
@@ -26556,7 +26556,7 @@
         <v>19.0900001525879</v>
       </c>
       <c r="G903" t="n">
-        <v>16.4942932128906</v>
+        <v>16.494291305542</v>
       </c>
       <c r="H903" t="n">
         <v>696029</v>
@@ -26614,7 +26614,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G905" t="n">
-        <v>16.5634136199951</v>
+        <v>16.5634117126465</v>
       </c>
       <c r="H905" t="n">
         <v>745758</v>
@@ -26643,7 +26643,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>16.5461311340332</v>
+        <v>16.5461330413818</v>
       </c>
       <c r="H906" t="n">
         <v>615121</v>
@@ -26672,7 +26672,7 @@
         <v>18.9449996948242</v>
       </c>
       <c r="G907" t="n">
-        <v>16.369010925293</v>
+        <v>16.3690071105957</v>
       </c>
       <c r="H907" t="n">
         <v>822657</v>
@@ -26701,7 +26701,7 @@
         <v>19.1749992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>16.5677356719971</v>
+        <v>16.5677375793457</v>
       </c>
       <c r="H908" t="n">
         <v>757808</v>
@@ -26730,7 +26730,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G909" t="n">
-        <v>16.5115756988525</v>
+        <v>16.5115737915039</v>
       </c>
       <c r="H909" t="n">
         <v>723810</v>
@@ -26817,7 +26817,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G912" t="n">
-        <v>15.6043434143066</v>
+        <v>15.604341506958</v>
       </c>
       <c r="H912" t="n">
         <v>1126172</v>
@@ -26846,7 +26846,7 @@
         <v>17.5650005340576</v>
       </c>
       <c r="G913" t="n">
-        <v>15.1766510009766</v>
+        <v>15.1766500473022</v>
       </c>
       <c r="H913" t="n">
         <v>1722483</v>
@@ -26904,7 +26904,7 @@
         <v>18.0249996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>15.5741033554077</v>
+        <v>15.5741014480591</v>
       </c>
       <c r="H915" t="n">
         <v>1562993</v>
@@ -26933,7 +26933,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>15.8117084503174</v>
+        <v>15.811710357666</v>
       </c>
       <c r="H916" t="n">
         <v>1359956</v>
@@ -27020,7 +27020,7 @@
         <v>18.4150009155273</v>
       </c>
       <c r="G919" t="n">
-        <v>15.9110727310181</v>
+        <v>15.9110708236694</v>
       </c>
       <c r="H919" t="n">
         <v>659371</v>
@@ -27078,7 +27078,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G921" t="n">
-        <v>15.8117084503174</v>
+        <v>15.811710357666</v>
       </c>
       <c r="H921" t="n">
         <v>761691</v>
@@ -27136,7 +27136,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G923" t="n">
-        <v>16.157320022583</v>
+        <v>16.1573219299316</v>
       </c>
       <c r="H923" t="n">
         <v>380914</v>
@@ -27165,7 +27165,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G924" t="n">
-        <v>15.690746307373</v>
+        <v>15.6907444000244</v>
       </c>
       <c r="H924" t="n">
         <v>446530</v>
@@ -27194,7 +27194,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G925" t="n">
-        <v>16.1227607727051</v>
+        <v>16.1227588653564</v>
       </c>
       <c r="H925" t="n">
         <v>306899</v>
@@ -27223,7 +27223,7 @@
         <v>18.6049995422363</v>
       </c>
       <c r="G926" t="n">
-        <v>16.0752372741699</v>
+        <v>16.0752353668213</v>
       </c>
       <c r="H926" t="n">
         <v>439417</v>
@@ -27252,7 +27252,7 @@
         <v>18.4549999237061</v>
       </c>
       <c r="G927" t="n">
-        <v>15.9456367492676</v>
+        <v>15.9456348419189</v>
       </c>
       <c r="H927" t="n">
         <v>314830</v>
@@ -27281,7 +27281,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G928" t="n">
-        <v>16.140043258667</v>
+        <v>16.1400375366211</v>
       </c>
       <c r="H928" t="n">
         <v>201567</v>
@@ -27310,7 +27310,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G929" t="n">
-        <v>16.4208469390869</v>
+        <v>16.4208488464355</v>
       </c>
       <c r="H929" t="n">
         <v>382728</v>
@@ -27339,7 +27339,7 @@
         <v>18.4850006103516</v>
       </c>
       <c r="G930" t="n">
-        <v>15.9715576171875</v>
+        <v>15.9715557098389</v>
       </c>
       <c r="H930" t="n">
         <v>1200050</v>
@@ -27397,7 +27397,7 @@
         <v>19.0849990844727</v>
       </c>
       <c r="G932" t="n">
-        <v>16.4899730682373</v>
+        <v>16.4899711608887</v>
       </c>
       <c r="H932" t="n">
         <v>450460</v>
@@ -27484,7 +27484,7 @@
         <v>19.3549995422363</v>
       </c>
       <c r="G935" t="n">
-        <v>16.723258972168</v>
+        <v>16.7232608795166</v>
       </c>
       <c r="H935" t="n">
         <v>451146</v>
@@ -27600,7 +27600,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G939" t="n">
-        <v>17.14231300354</v>
+        <v>17.1423110961914</v>
       </c>
       <c r="H939" t="n">
         <v>422740</v>
@@ -27658,7 +27658,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G941" t="n">
-        <v>17.591609954834</v>
+        <v>17.5916080474854</v>
       </c>
       <c r="H941" t="n">
         <v>639640</v>
@@ -27774,7 +27774,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G945" t="n">
-        <v>17.4274425506592</v>
+        <v>17.4274444580078</v>
       </c>
       <c r="H945" t="n">
         <v>536673</v>
@@ -27890,7 +27890,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G949" t="n">
-        <v>17.1077499389648</v>
+        <v>17.1077518463135</v>
       </c>
       <c r="H949" t="n">
         <v>398252</v>
@@ -27948,7 +27948,7 @@
         <v>19.9650001525879</v>
       </c>
       <c r="G951" t="n">
-        <v>17.2503185272217</v>
+        <v>17.2503147125244</v>
       </c>
       <c r="H951" t="n">
         <v>376838</v>
@@ -27977,7 +27977,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G952" t="n">
-        <v>17.7903347015381</v>
+        <v>17.7903327941895</v>
       </c>
       <c r="H952" t="n">
         <v>858042</v>
@@ -28006,7 +28006,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G953" t="n">
-        <v>18.1791496276855</v>
+        <v>18.1791477203369</v>
       </c>
       <c r="H953" t="n">
         <v>718953</v>
@@ -28064,7 +28064,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G955" t="n">
-        <v>17.2675971984863</v>
+        <v>17.267599105835</v>
       </c>
       <c r="H955" t="n">
         <v>914921</v>
@@ -28093,7 +28093,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G956" t="n">
-        <v>17.0904712677002</v>
+        <v>17.0904731750488</v>
       </c>
       <c r="H956" t="n">
         <v>470830</v>
@@ -28122,7 +28122,7 @@
         <v>19.8299999237061</v>
       </c>
       <c r="G957" t="n">
-        <v>17.133674621582</v>
+        <v>17.1336727142334</v>
       </c>
       <c r="H957" t="n">
         <v>637008</v>
@@ -28151,7 +28151,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G958" t="n">
-        <v>17.3756008148193</v>
+        <v>17.375602722168</v>
       </c>
       <c r="H958" t="n">
         <v>408567</v>
@@ -28180,7 +28180,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G959" t="n">
-        <v>17.150951385498</v>
+        <v>17.1509532928467</v>
       </c>
       <c r="H959" t="n">
         <v>532603</v>
@@ -28209,7 +28209,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G960" t="n">
-        <v>17.4447250366211</v>
+        <v>17.4447212219238</v>
       </c>
       <c r="H960" t="n">
         <v>1510362</v>
@@ -28267,7 +28267,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G962" t="n">
-        <v>18.5247611999512</v>
+        <v>18.5247592926025</v>
       </c>
       <c r="H962" t="n">
         <v>870453</v>
@@ -28296,7 +28296,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G963" t="n">
-        <v>18.5247611999512</v>
+        <v>18.5247592926025</v>
       </c>
       <c r="H963" t="n">
         <v>546026</v>
@@ -28354,7 +28354,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G965" t="n">
-        <v>18.7234859466553</v>
+        <v>18.7234840393066</v>
       </c>
       <c r="H965" t="n">
         <v>1068360</v>
@@ -28383,7 +28383,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>18.8358097076416</v>
+        <v>18.835807800293</v>
       </c>
       <c r="H966" t="n">
         <v>570110</v>
@@ -28412,7 +28412,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G967" t="n">
-        <v>18.9740543365479</v>
+        <v>18.9740524291992</v>
       </c>
       <c r="H967" t="n">
         <v>514208</v>
@@ -28441,7 +28441,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>18.8358097076416</v>
+        <v>18.835807800293</v>
       </c>
       <c r="H968" t="n">
         <v>387697</v>
@@ -28470,7 +28470,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G969" t="n">
-        <v>18.6457233428955</v>
+        <v>18.6457214355469</v>
       </c>
       <c r="H969" t="n">
         <v>969347</v>
@@ -28499,7 +28499,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G970" t="n">
-        <v>18.5852394104004</v>
+        <v>18.585241317749</v>
       </c>
       <c r="H970" t="n">
         <v>258799</v>
@@ -28528,7 +28528,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G971" t="n">
-        <v>18.6802825927734</v>
+        <v>18.6802806854248</v>
       </c>
       <c r="H971" t="n">
         <v>271314</v>
@@ -28557,7 +28557,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G972" t="n">
-        <v>18.7753276824951</v>
+        <v>18.7753238677979</v>
       </c>
       <c r="H972" t="n">
         <v>391924</v>
@@ -28673,7 +28673,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G976" t="n">
-        <v>18.6975631713867</v>
+        <v>18.6975612640381</v>
       </c>
       <c r="H976" t="n">
         <v>588566</v>
@@ -28702,7 +28702,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G977" t="n">
-        <v>18.9135665893555</v>
+        <v>18.9135684967041</v>
       </c>
       <c r="H977" t="n">
         <v>361006</v>
@@ -28731,7 +28731,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G978" t="n">
-        <v>19.1382160186768</v>
+        <v>19.1382179260254</v>
       </c>
       <c r="H978" t="n">
         <v>454073</v>
@@ -28760,7 +28760,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G979" t="n">
-        <v>18.9913330078125</v>
+        <v>18.9913311004639</v>
       </c>
       <c r="H979" t="n">
         <v>437367</v>
@@ -28789,7 +28789,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G980" t="n">
-        <v>18.8790073394775</v>
+        <v>18.8790092468262</v>
       </c>
       <c r="H980" t="n">
         <v>380597</v>
@@ -28847,7 +28847,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>18.9222106933594</v>
+        <v>18.9222087860107</v>
       </c>
       <c r="H982" t="n">
         <v>589510</v>
@@ -28963,7 +28963,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G986" t="n">
-        <v>19.6652755737305</v>
+        <v>19.6652736663818</v>
       </c>
       <c r="H986" t="n">
         <v>513358</v>
@@ -29021,7 +29021,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>19.5702304840088</v>
+        <v>19.5702342987061</v>
       </c>
       <c r="H988" t="n">
         <v>429192</v>
@@ -29050,7 +29050,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G989" t="n">
-        <v>19.7257556915283</v>
+        <v>19.725757598877</v>
       </c>
       <c r="H989" t="n">
         <v>693120</v>
@@ -29079,7 +29079,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G990" t="n">
-        <v>20.0281639099121</v>
+        <v>20.0281658172607</v>
       </c>
       <c r="H990" t="n">
         <v>525156</v>
@@ -29108,7 +29108,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G991" t="n">
-        <v>19.6825580596924</v>
+        <v>19.6825561523438</v>
       </c>
       <c r="H991" t="n">
         <v>600425</v>
@@ -29137,7 +29137,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G992" t="n">
-        <v>19.6134357452393</v>
+        <v>19.613431930542</v>
       </c>
       <c r="H992" t="n">
         <v>576218</v>
@@ -29195,7 +29195,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G994" t="n">
-        <v>19.9849662780762</v>
+        <v>19.9849643707275</v>
       </c>
       <c r="H994" t="n">
         <v>1013128</v>
@@ -29282,7 +29282,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G997" t="n">
-        <v>19.4233455657959</v>
+        <v>19.4233474731445</v>
       </c>
       <c r="H997" t="n">
         <v>1272052</v>
@@ -29311,7 +29311,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G998" t="n">
-        <v>19.0258922576904</v>
+        <v>19.0258941650391</v>
       </c>
       <c r="H998" t="n">
         <v>808774</v>
@@ -29369,7 +29369,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G1000" t="n">
-        <v>19.4147071838379</v>
+        <v>19.4147052764893</v>
       </c>
       <c r="H1000" t="n">
         <v>2245061</v>
@@ -29398,7 +29398,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1001" t="n">
-        <v>19.1122970581055</v>
+        <v>19.1122989654541</v>
       </c>
       <c r="H1001" t="n">
         <v>872139</v>
@@ -29456,7 +29456,7 @@
         <v>22.2700004577637</v>
       </c>
       <c r="G1003" t="n">
-        <v>19.2419013977051</v>
+        <v>19.2418994903564</v>
       </c>
       <c r="H1003" t="n">
         <v>570727</v>
@@ -29485,7 +29485,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G1004" t="n">
-        <v>18.8962898254395</v>
+        <v>18.8962917327881</v>
       </c>
       <c r="H1004" t="n">
         <v>1244469</v>
@@ -29514,7 +29514,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.3283042907715</v>
+        <v>19.3283061981201</v>
       </c>
       <c r="H1005" t="n">
         <v>613705</v>
@@ -29543,7 +29543,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.4060668945312</v>
+        <v>19.4060649871826</v>
       </c>
       <c r="H1006" t="n">
         <v>561671</v>
@@ -29717,7 +29717,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1012" t="n">
-        <v>19.0431747436523</v>
+        <v>19.0431728363037</v>
       </c>
       <c r="H1012" t="n">
         <v>764557</v>
@@ -29804,7 +29804,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1015" t="n">
-        <v>19.3974266052246</v>
+        <v>19.397424697876</v>
       </c>
       <c r="H1015" t="n">
         <v>338926</v>
@@ -29891,7 +29891,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G1018" t="n">
-        <v>18.9135665893555</v>
+        <v>18.9135684967041</v>
       </c>
       <c r="H1018" t="n">
         <v>273534</v>
@@ -29920,7 +29920,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1019" t="n">
-        <v>19.0950164794922</v>
+        <v>19.0950145721436</v>
       </c>
       <c r="H1019" t="n">
         <v>395836</v>
@@ -29949,7 +29949,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G1020" t="n">
-        <v>18.8703689575195</v>
+        <v>18.8703708648682</v>
       </c>
       <c r="H1020" t="n">
         <v>456762</v>
@@ -29978,7 +29978,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1021" t="n">
-        <v>18.8444480895996</v>
+        <v>18.8444499969482</v>
       </c>
       <c r="H1021" t="n">
         <v>402476</v>
@@ -30007,7 +30007,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G1022" t="n">
-        <v>18.7753276824951</v>
+        <v>18.7753238677979</v>
       </c>
       <c r="H1022" t="n">
         <v>407317</v>
@@ -30036,7 +30036,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G1023" t="n">
-        <v>18.8703689575195</v>
+        <v>18.8703708648682</v>
       </c>
       <c r="H1023" t="n">
         <v>335837</v>
@@ -30065,7 +30065,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1024" t="n">
-        <v>18.7494087219238</v>
+        <v>18.7494068145752</v>
       </c>
       <c r="H1024" t="n">
         <v>655913</v>
@@ -30094,7 +30094,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G1025" t="n">
-        <v>18.2655467987061</v>
+        <v>18.2655487060547</v>
       </c>
       <c r="H1025" t="n">
         <v>815019</v>
@@ -30181,7 +30181,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1028" t="n">
-        <v>18.8530902862549</v>
+        <v>18.8530883789062</v>
       </c>
       <c r="H1028" t="n">
         <v>882582</v>
@@ -30297,7 +30297,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G1032" t="n">
-        <v>18.9826908111572</v>
+        <v>18.9826927185059</v>
       </c>
       <c r="H1032" t="n">
         <v>472760</v>
@@ -30384,7 +30384,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1035" t="n">
-        <v>18.8790073394775</v>
+        <v>18.8790092468262</v>
       </c>
       <c r="H1035" t="n">
         <v>276554</v>
@@ -30471,7 +30471,7 @@
         <v>21.3700008392334</v>
       </c>
       <c r="G1038" t="n">
-        <v>18.4642772674561</v>
+        <v>18.4642753601074</v>
       </c>
       <c r="H1038" t="n">
         <v>364548</v>
@@ -30500,7 +30500,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G1039" t="n">
-        <v>19.1295776367188</v>
+        <v>19.1295757293701</v>
       </c>
       <c r="H1039" t="n">
         <v>670786</v>
@@ -30529,7 +30529,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G1040" t="n">
-        <v>19.5529479980469</v>
+        <v>19.5529499053955</v>
       </c>
       <c r="H1040" t="n">
         <v>619118</v>
@@ -30558,7 +30558,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>19.7862377166748</v>
+        <v>19.7862396240234</v>
       </c>
       <c r="H1041" t="n">
         <v>715877</v>
@@ -30645,7 +30645,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G1044" t="n">
-        <v>20.0627288818359</v>
+        <v>20.0627269744873</v>
       </c>
       <c r="H1044" t="n">
         <v>579468</v>
@@ -30674,7 +30674,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1045" t="n">
-        <v>20.3478527069092</v>
+        <v>20.3478565216064</v>
       </c>
       <c r="H1045" t="n">
         <v>594255</v>
@@ -30703,7 +30703,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G1046" t="n">
-        <v>19.9676876068115</v>
+        <v>19.9676856994629</v>
       </c>
       <c r="H1046" t="n">
         <v>720462</v>
@@ -30761,7 +30761,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>19.7862377166748</v>
+        <v>19.7862396240234</v>
       </c>
       <c r="H1048" t="n">
         <v>375090</v>
@@ -30819,7 +30819,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1050" t="n">
-        <v>19.7689590454102</v>
+        <v>19.7689571380615</v>
       </c>
       <c r="H1050" t="n">
         <v>265935</v>
@@ -30848,7 +30848,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G1051" t="n">
-        <v>19.5011100769043</v>
+        <v>19.5011081695557</v>
       </c>
       <c r="H1051" t="n">
         <v>595524</v>
@@ -30935,7 +30935,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1054" t="n">
-        <v>17.14231300354</v>
+        <v>17.1423110961914</v>
       </c>
       <c r="H1054" t="n">
         <v>1439523</v>
@@ -30964,7 +30964,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G1055" t="n">
-        <v>17.4447250366211</v>
+        <v>17.4447212219238</v>
       </c>
       <c r="H1055" t="n">
         <v>1272061</v>
@@ -31022,7 +31022,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G1057" t="n">
-        <v>17.0775108337402</v>
+        <v>17.0775089263916</v>
       </c>
       <c r="H1057" t="n">
         <v>1350261</v>
@@ -31051,7 +31051,7 @@
         <v>18.625</v>
       </c>
       <c r="G1058" t="n">
-        <v>16.0925197601318</v>
+        <v>16.0925178527832</v>
       </c>
       <c r="H1058" t="n">
         <v>1206197</v>
@@ -31080,7 +31080,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1059" t="n">
-        <v>16.4813346862793</v>
+        <v>16.4813327789307</v>
       </c>
       <c r="H1059" t="n">
         <v>1155232</v>
@@ -31109,7 +31109,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>16.1141204833984</v>
+        <v>16.1141185760498</v>
       </c>
       <c r="H1060" t="n">
         <v>453020</v>
@@ -31138,7 +31138,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>16.0709209442139</v>
+        <v>16.0709190368652</v>
       </c>
       <c r="H1061" t="n">
         <v>644724</v>
@@ -31167,7 +31167,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>15.5438632965088</v>
+        <v>15.5438613891602</v>
       </c>
       <c r="H1062" t="n">
         <v>1316298</v>
@@ -31225,7 +31225,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G1064" t="n">
-        <v>13.7942056655884</v>
+        <v>13.7942047119141</v>
       </c>
       <c r="H1064" t="n">
         <v>1653315</v>
@@ -31254,7 +31254,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G1065" t="n">
-        <v>13.7639627456665</v>
+        <v>13.7639646530151</v>
       </c>
       <c r="H1065" t="n">
         <v>903512</v>
@@ -31283,7 +31283,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1066" t="n">
-        <v>12.1136713027954</v>
+        <v>12.1136722564697</v>
       </c>
       <c r="H1066" t="n">
         <v>1519802</v>
@@ -31312,7 +31312,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1067" t="n">
-        <v>12.7184906005859</v>
+        <v>12.7184896469116</v>
       </c>
       <c r="H1067" t="n">
         <v>1322292</v>
@@ -31341,7 +31341,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.8048934936523</v>
+        <v>12.8048944473267</v>
       </c>
       <c r="H1068" t="n">
         <v>1639735</v>
@@ -31370,7 +31370,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1069" t="n">
-        <v>12.8048934936523</v>
+        <v>12.8048944473267</v>
       </c>
       <c r="H1069" t="n">
         <v>1807481</v>
@@ -31399,7 +31399,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1070" t="n">
-        <v>12.7703304290771</v>
+        <v>12.7703323364258</v>
       </c>
       <c r="H1070" t="n">
         <v>1332610</v>
@@ -31428,7 +31428,7 @@
         <v>14.5050001144409</v>
       </c>
       <c r="G1071" t="n">
-        <v>12.5327243804932</v>
+        <v>12.5327234268188</v>
       </c>
       <c r="H1071" t="n">
         <v>1577196</v>
@@ -31486,7 +31486,7 @@
         <v>13.5150003433228</v>
       </c>
       <c r="G1073" t="n">
-        <v>11.6773366928101</v>
+        <v>11.6773376464844</v>
       </c>
       <c r="H1073" t="n">
         <v>973048</v>
@@ -31602,7 +31602,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1077" t="n">
-        <v>13.7034826278687</v>
+        <v>13.7034816741943</v>
       </c>
       <c r="H1077" t="n">
         <v>1433172</v>
@@ -31660,7 +31660,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.4033451080322</v>
+        <v>14.4033432006836</v>
       </c>
       <c r="H1079" t="n">
         <v>1228953</v>
@@ -31776,7 +31776,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.5502300262451</v>
+        <v>14.5502309799194</v>
       </c>
       <c r="H1083" t="n">
         <v>382917</v>
@@ -31863,7 +31863,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1086" t="n">
-        <v>15.3451366424561</v>
+        <v>15.3451347351074</v>
       </c>
       <c r="H1086" t="n">
         <v>758752</v>
@@ -31950,7 +31950,7 @@
         <v>15.1750001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>13.1116237640381</v>
+        <v>13.1116228103638</v>
       </c>
       <c r="H1089" t="n">
         <v>733279</v>
@@ -31979,7 +31979,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>13.6862010955811</v>
+        <v>13.6862020492554</v>
       </c>
       <c r="H1090" t="n">
         <v>726636</v>
@@ -32037,7 +32037,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1092" t="n">
-        <v>13.6602811813354</v>
+        <v>13.6602802276611</v>
       </c>
       <c r="H1092" t="n">
         <v>418998</v>
@@ -32066,7 +32066,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1093" t="n">
-        <v>14.2694187164307</v>
+        <v>14.269419670105</v>
       </c>
       <c r="H1093" t="n">
         <v>581606</v>
@@ -32095,7 +32095,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1094" t="n">
-        <v>14.5502300262451</v>
+        <v>14.5502309799194</v>
       </c>
       <c r="H1094" t="n">
         <v>495905</v>
@@ -32153,7 +32153,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1096" t="n">
-        <v>15.2587327957153</v>
+        <v>15.2587337493896</v>
       </c>
       <c r="H1096" t="n">
         <v>634317</v>
@@ -32182,7 +32182,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G1097" t="n">
-        <v>14.9606447219849</v>
+        <v>14.9606428146362</v>
       </c>
       <c r="H1097" t="n">
         <v>615666</v>
@@ -32211,7 +32211,7 @@
         <v>18.4050006866455</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.9024343490601</v>
+        <v>15.9024362564087</v>
       </c>
       <c r="H1098" t="n">
         <v>703639</v>
@@ -32240,7 +32240,7 @@
         <v>17.8850002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.4531373977661</v>
+        <v>15.4531412124634</v>
       </c>
       <c r="H1099" t="n">
         <v>580040</v>
@@ -32269,7 +32269,7 @@
         <v>16.9249992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>14.6236705780029</v>
+        <v>14.6236715316772</v>
       </c>
       <c r="H1100" t="n">
         <v>704770</v>
@@ -32298,7 +32298,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G1101" t="n">
-        <v>14.4206275939941</v>
+        <v>14.4206266403198</v>
       </c>
       <c r="H1101" t="n">
         <v>771713</v>
@@ -32356,7 +32356,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1103" t="n">
-        <v>14.2046194076538</v>
+        <v>14.2046184539795</v>
       </c>
       <c r="H1103" t="n">
         <v>400906</v>
@@ -32385,7 +32385,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="n">
-        <v>14.6884746551514</v>
+        <v>14.6884756088257</v>
       </c>
       <c r="H1104" t="n">
         <v>509568</v>
@@ -32501,7 +32501,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1108" t="n">
-        <v>13.6689224243164</v>
+        <v>13.6689214706421</v>
       </c>
       <c r="H1108" t="n">
         <v>1071150</v>
@@ -32530,7 +32530,7 @@
         <v>15.6949996948242</v>
       </c>
       <c r="G1109" t="n">
-        <v>13.5609178543091</v>
+        <v>13.5609188079834</v>
       </c>
       <c r="H1109" t="n">
         <v>405513</v>
@@ -32588,7 +32588,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1111" t="n">
-        <v>14.524881362915</v>
+        <v>14.5248804092407</v>
       </c>
       <c r="H1111" t="n">
         <v>1060170</v>
@@ -32617,7 +32617,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>14.6775465011597</v>
+        <v>14.6775455474854</v>
       </c>
       <c r="H1112" t="n">
         <v>687654</v>
@@ -32733,7 +32733,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>15.1137285232544</v>
+        <v>15.1137294769287</v>
       </c>
       <c r="H1116" t="n">
         <v>598374</v>
@@ -32762,7 +32762,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>15.4408664703369</v>
+        <v>15.4408645629883</v>
       </c>
       <c r="H1117" t="n">
         <v>1129370</v>
@@ -32820,7 +32820,7 @@
         <v>17.8850002288818</v>
       </c>
       <c r="G1119" t="n">
-        <v>15.6022520065308</v>
+        <v>15.6022529602051</v>
       </c>
       <c r="H1119" t="n">
         <v>725808</v>
@@ -32849,7 +32849,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1120" t="n">
-        <v>15.7461929321289</v>
+        <v>15.7461948394775</v>
       </c>
       <c r="H1120" t="n">
         <v>316376</v>
@@ -32878,7 +32878,7 @@
         <v>18.8150005340576</v>
       </c>
       <c r="G1121" t="n">
-        <v>16.413553237915</v>
+        <v>16.4135513305664</v>
       </c>
       <c r="H1121" t="n">
         <v>683299</v>
@@ -32907,7 +32907,7 @@
         <v>19.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>17.0111236572266</v>
+        <v>17.0111217498779</v>
       </c>
       <c r="H1122" t="n">
         <v>807558</v>
@@ -32965,7 +32965,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1124" t="n">
-        <v>17.6043319702148</v>
+        <v>17.6043300628662</v>
       </c>
       <c r="H1124" t="n">
         <v>678311</v>
@@ -33081,7 +33081,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1128" t="n">
-        <v>15.7549171447754</v>
+        <v>15.7549152374268</v>
       </c>
       <c r="H1128" t="n">
         <v>862847</v>
@@ -33110,7 +33110,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G1129" t="n">
-        <v>15.7113008499146</v>
+        <v>15.7112970352173</v>
       </c>
       <c r="H1129" t="n">
         <v>798511</v>
@@ -33168,7 +33168,7 @@
         <v>19.5650005340576</v>
       </c>
       <c r="G1131" t="n">
-        <v>17.0678291320801</v>
+        <v>17.0678272247314</v>
       </c>
       <c r="H1131" t="n">
         <v>1989808</v>
@@ -33226,7 +33226,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1133" t="n">
-        <v>17.2902774810791</v>
+        <v>17.2902755737305</v>
       </c>
       <c r="H1133" t="n">
         <v>477700</v>
@@ -33255,7 +33255,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1134" t="n">
-        <v>17.0372943878174</v>
+        <v>17.037296295166</v>
       </c>
       <c r="H1134" t="n">
         <v>558615</v>
@@ -33284,7 +33284,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1135" t="n">
-        <v>17.0285701751709</v>
+        <v>17.0285682678223</v>
       </c>
       <c r="H1135" t="n">
         <v>526589</v>
@@ -33400,7 +33400,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>16.6185550689697</v>
+        <v>16.6185569763184</v>
       </c>
       <c r="H1139" t="n">
         <v>554140</v>
@@ -33516,7 +33516,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1143" t="n">
-        <v>17.0372943878174</v>
+        <v>17.037296295166</v>
       </c>
       <c r="H1143" t="n">
         <v>700678</v>
@@ -33545,7 +33545,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>16.7712230682373</v>
+        <v>16.7712211608887</v>
       </c>
       <c r="H1144" t="n">
         <v>273529</v>
@@ -33603,7 +33603,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G1146" t="n">
-        <v>17.019847869873</v>
+        <v>17.0198459625244</v>
       </c>
       <c r="H1146" t="n">
         <v>335108</v>
@@ -33632,7 +33632,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G1147" t="n">
-        <v>16.7581329345703</v>
+        <v>16.7581348419189</v>
       </c>
       <c r="H1147" t="n">
         <v>562703</v>
@@ -33661,7 +33661,7 @@
         <v>19.2549991607666</v>
       </c>
       <c r="G1148" t="n">
-        <v>16.7973937988281</v>
+        <v>16.7973918914795</v>
       </c>
       <c r="H1148" t="n">
         <v>506595</v>
@@ -33719,7 +33719,7 @@
         <v>19.8850002288818</v>
       </c>
       <c r="G1150" t="n">
-        <v>17.3469829559326</v>
+        <v>17.3469848632812</v>
       </c>
       <c r="H1150" t="n">
         <v>486401</v>
@@ -33806,7 +33806,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>18.6686153411865</v>
+        <v>18.6686172485352</v>
       </c>
       <c r="H1153" t="n">
         <v>470208</v>
@@ -33835,7 +33835,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G1154" t="n">
-        <v>18.5726547241211</v>
+        <v>18.5726566314697</v>
       </c>
       <c r="H1154" t="n">
         <v>303652</v>
@@ -33864,7 +33864,7 @@
         <v>21.3700008392334</v>
       </c>
       <c r="G1155" t="n">
-        <v>18.642448425293</v>
+        <v>18.6424465179443</v>
       </c>
       <c r="H1155" t="n">
         <v>311599</v>
@@ -33893,7 +33893,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1156" t="n">
-        <v>18.3545665740967</v>
+        <v>18.354564666748</v>
       </c>
       <c r="H1156" t="n">
         <v>527784</v>
@@ -33951,7 +33951,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1158" t="n">
-        <v>18.6337242126465</v>
+        <v>18.6337223052979</v>
       </c>
       <c r="H1158" t="n">
         <v>975728</v>
@@ -33980,7 +33980,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G1159" t="n">
-        <v>18.0754070281982</v>
+        <v>18.0754051208496</v>
       </c>
       <c r="H1159" t="n">
         <v>568338</v>
@@ -34009,7 +34009,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1160" t="n">
-        <v>18.2149848937988</v>
+        <v>18.2149829864502</v>
       </c>
       <c r="H1160" t="n">
         <v>688607</v>
@@ -34038,7 +34038,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G1161" t="n">
-        <v>17.9183807373047</v>
+        <v>17.9183826446533</v>
       </c>
       <c r="H1161" t="n">
         <v>414850</v>
@@ -34067,7 +34067,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G1162" t="n">
-        <v>17.6130542755127</v>
+        <v>17.6130523681641</v>
       </c>
       <c r="H1162" t="n">
         <v>354990</v>
@@ -34241,7 +34241,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G1168" t="n">
-        <v>17.8224201202393</v>
+        <v>17.8224220275879</v>
       </c>
       <c r="H1168" t="n">
         <v>811515</v>
@@ -34270,7 +34270,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G1169" t="n">
-        <v>17.7700805664062</v>
+        <v>17.7700824737549</v>
       </c>
       <c r="H1169" t="n">
         <v>421964</v>
@@ -34299,7 +34299,7 @@
         <v>20.8299999237061</v>
       </c>
       <c r="G1170" t="n">
-        <v>18.1713695526123</v>
+        <v>18.1713676452637</v>
       </c>
       <c r="H1170" t="n">
         <v>477775</v>
@@ -34328,7 +34328,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G1171" t="n">
-        <v>18.8256435394287</v>
+        <v>18.8256397247314</v>
       </c>
       <c r="H1171" t="n">
         <v>777023</v>
@@ -34444,7 +34444,7 @@
         <v>21.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>18.5377597808838</v>
+        <v>18.5377616882324</v>
       </c>
       <c r="H1175" t="n">
         <v>349463</v>
@@ -34473,7 +34473,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G1176" t="n">
-        <v>18.6511669158936</v>
+        <v>18.6511707305908</v>
       </c>
       <c r="H1176" t="n">
         <v>343268</v>
@@ -34531,7 +34531,7 @@
         <v>20.75</v>
       </c>
       <c r="G1178" t="n">
-        <v>18.1015815734863</v>
+        <v>18.1015796661377</v>
       </c>
       <c r="H1178" t="n">
         <v>460794</v>
@@ -34560,7 +34560,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1179" t="n">
-        <v>18.1626434326172</v>
+        <v>18.1626453399658</v>
       </c>
       <c r="H1179" t="n">
         <v>318276</v>
@@ -34589,7 +34589,7 @@
         <v>21.25</v>
       </c>
       <c r="G1180" t="n">
-        <v>18.5377597808838</v>
+        <v>18.5377616882324</v>
       </c>
       <c r="H1180" t="n">
         <v>419785</v>
@@ -34647,7 +34647,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G1182" t="n">
-        <v>18.4679698944092</v>
+        <v>18.4679718017578</v>
       </c>
       <c r="H1182" t="n">
         <v>384141</v>
@@ -34734,7 +34734,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G1185" t="n">
-        <v>17.9009323120117</v>
+        <v>17.900936126709</v>
       </c>
       <c r="H1185" t="n">
         <v>399381</v>
@@ -34763,7 +34763,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G1186" t="n">
-        <v>17.9358253479004</v>
+        <v>17.935827255249</v>
       </c>
       <c r="H1186" t="n">
         <v>499741</v>
@@ -34792,7 +34792,7 @@
         <v>20.5</v>
       </c>
       <c r="G1187" t="n">
-        <v>17.8834857940674</v>
+        <v>17.883487701416</v>
       </c>
       <c r="H1187" t="n">
         <v>432371</v>
@@ -34821,7 +34821,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1188" t="n">
-        <v>17.2204875946045</v>
+        <v>17.2204895019531</v>
       </c>
       <c r="H1188" t="n">
         <v>699067</v>
@@ -34850,7 +34850,7 @@
         <v>19.9699993133545</v>
       </c>
       <c r="G1189" t="n">
-        <v>17.4211349487305</v>
+        <v>17.4211330413818</v>
       </c>
       <c r="H1189" t="n">
         <v>605304</v>
@@ -34879,7 +34879,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G1190" t="n">
-        <v>17.5258159637451</v>
+        <v>17.5258178710938</v>
       </c>
       <c r="H1190" t="n">
         <v>337756</v>
@@ -34908,7 +34908,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1191" t="n">
-        <v>17.2117652893066</v>
+        <v>17.211763381958</v>
       </c>
       <c r="H1191" t="n">
         <v>612423</v>
@@ -34995,7 +34995,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G1194" t="n">
-        <v>18.0666828155518</v>
+        <v>18.0666847229004</v>
       </c>
       <c r="H1194" t="n">
         <v>301722</v>
@@ -35024,7 +35024,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G1195" t="n">
-        <v>18.0754070281982</v>
+        <v>18.0754051208496</v>
       </c>
       <c r="H1195" t="n">
         <v>291651</v>
@@ -35053,7 +35053,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1196" t="n">
-        <v>18.2324333190918</v>
+        <v>18.2324314117432</v>
       </c>
       <c r="H1196" t="n">
         <v>232755</v>
@@ -35082,7 +35082,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G1197" t="n">
-        <v>18.4417991638184</v>
+        <v>18.441801071167</v>
       </c>
       <c r="H1197" t="n">
         <v>329812</v>
@@ -35111,7 +35111,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G1198" t="n">
-        <v>18.389461517334</v>
+        <v>18.3894596099854</v>
       </c>
       <c r="H1198" t="n">
         <v>332560</v>
@@ -35227,7 +35227,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>16.83664894104</v>
+        <v>16.8366470336914</v>
       </c>
       <c r="H1202" t="n">
         <v>569331</v>
@@ -35285,7 +35285,7 @@
         <v>19.0949993133545</v>
       </c>
       <c r="G1204" t="n">
-        <v>16.6578159332275</v>
+        <v>16.6578121185303</v>
       </c>
       <c r="H1204" t="n">
         <v>560714</v>
@@ -35372,7 +35372,7 @@
         <v>19.8850002288818</v>
       </c>
       <c r="G1207" t="n">
-        <v>17.3469829559326</v>
+        <v>17.3469848632812</v>
       </c>
       <c r="H1207" t="n">
         <v>470255</v>
@@ -35430,7 +35430,7 @@
         <v>19.7950000762939</v>
       </c>
       <c r="G1209" t="n">
-        <v>17.2684688568115</v>
+        <v>17.2684707641602</v>
       </c>
       <c r="H1209" t="n">
         <v>229628</v>
@@ -35459,7 +35459,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1210" t="n">
-        <v>17.4996452331543</v>
+        <v>17.4996471405029</v>
       </c>
       <c r="H1210" t="n">
         <v>393981</v>
@@ -35546,7 +35546,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>18.3632888793945</v>
+        <v>18.3632907867432</v>
       </c>
       <c r="H1213" t="n">
         <v>492066</v>
@@ -35575,7 +35575,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1214" t="n">
-        <v>18.1103019714355</v>
+        <v>18.1103038787842</v>
       </c>
       <c r="H1214" t="n">
         <v>408956</v>
@@ -35633,7 +35633,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>18.2324333190918</v>
+        <v>18.2324314117432</v>
       </c>
       <c r="H1216" t="n">
         <v>776509</v>
@@ -35662,7 +35662,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1217" t="n">
-        <v>18.2673301696777</v>
+        <v>18.2673282623291</v>
       </c>
       <c r="H1217" t="n">
         <v>530844</v>
@@ -35691,7 +35691,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G1218" t="n">
-        <v>17.6392269134521</v>
+        <v>17.6392250061035</v>
       </c>
       <c r="H1218" t="n">
         <v>551153</v>
@@ -35720,7 +35720,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>18.1451969146729</v>
+        <v>18.1451988220215</v>
       </c>
       <c r="H1219" t="n">
         <v>714588</v>
@@ -35749,7 +35749,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1220" t="n">
-        <v>17.9271011352539</v>
+        <v>17.9271030426025</v>
       </c>
       <c r="H1220" t="n">
         <v>453748</v>
@@ -35865,7 +35865,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1224" t="n">
-        <v>18.023063659668</v>
+        <v>18.0230655670166</v>
       </c>
       <c r="H1224" t="n">
         <v>253636</v>
@@ -35981,7 +35981,7 @@
         <v>17.9650001525879</v>
       </c>
       <c r="G1228" t="n">
-        <v>15.6720428466797</v>
+        <v>15.6720409393311</v>
       </c>
       <c r="H1228" t="n">
         <v>1055704</v>
@@ -36039,7 +36039,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1230" t="n">
-        <v>17.0460205078125</v>
+        <v>17.0460166931152</v>
       </c>
       <c r="H1230" t="n">
         <v>962081</v>
@@ -36068,7 +36068,7 @@
         <v>19.8050003051758</v>
       </c>
       <c r="G1231" t="n">
-        <v>17.277193069458</v>
+        <v>17.2771911621094</v>
       </c>
       <c r="H1231" t="n">
         <v>700378</v>
@@ -36097,7 +36097,7 @@
         <v>19.2950000762939</v>
       </c>
       <c r="G1232" t="n">
-        <v>16.8322906494141</v>
+        <v>16.8322868347168</v>
       </c>
       <c r="H1232" t="n">
         <v>1345481</v>
@@ -36126,7 +36126,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1233" t="n">
-        <v>17.2553825378418</v>
+        <v>17.2553844451904</v>
       </c>
       <c r="H1233" t="n">
         <v>856020</v>
@@ -36155,7 +36155,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>17.2728271484375</v>
+        <v>17.2728290557861</v>
       </c>
       <c r="H1234" t="n">
         <v>1959644</v>
@@ -36213,7 +36213,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1236" t="n">
-        <v>18.1451969146729</v>
+        <v>18.1451988220215</v>
       </c>
       <c r="H1236" t="n">
         <v>1171228</v>
@@ -36271,7 +36271,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G1238" t="n">
-        <v>17.7700805664062</v>
+        <v>17.7700824737549</v>
       </c>
       <c r="H1238" t="n">
         <v>539003</v>
@@ -36300,7 +36300,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G1239" t="n">
-        <v>18.0754070281982</v>
+        <v>18.0754051208496</v>
       </c>
       <c r="H1239" t="n">
         <v>585199</v>
@@ -36387,7 +36387,7 @@
         <v>21</v>
       </c>
       <c r="G1242" t="n">
-        <v>18.3196716308594</v>
+        <v>18.3196697235107</v>
       </c>
       <c r="H1242" t="n">
         <v>553393</v>
@@ -36445,7 +36445,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1244" t="n">
-        <v>18.1103019714355</v>
+        <v>18.1103038787842</v>
       </c>
       <c r="H1244" t="n">
         <v>453297</v>
@@ -36474,7 +36474,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1245" t="n">
-        <v>18.1103019714355</v>
+        <v>18.1103038787842</v>
       </c>
       <c r="H1245" t="n">
         <v>439774</v>
@@ -36503,7 +36503,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1246" t="n">
-        <v>18.2673301696777</v>
+        <v>18.2673282623291</v>
       </c>
       <c r="H1246" t="n">
         <v>799395</v>
@@ -36648,7 +36648,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G1251" t="n">
-        <v>17.7439136505127</v>
+        <v>17.7439117431641</v>
       </c>
       <c r="H1251" t="n">
         <v>580126</v>
@@ -36735,7 +36735,7 @@
         <v>19.9650001525879</v>
       </c>
       <c r="G1254" t="n">
-        <v>17.4167728424072</v>
+        <v>17.41676902771</v>
       </c>
       <c r="H1254" t="n">
         <v>686845</v>
@@ -36793,7 +36793,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>17.0460205078125</v>
+        <v>17.0460166931152</v>
       </c>
       <c r="H1256" t="n">
         <v>337325</v>
@@ -36822,7 +36822,7 @@
         <v>19.6350002288818</v>
       </c>
       <c r="G1257" t="n">
-        <v>17.1288890838623</v>
+        <v>17.1288909912109</v>
       </c>
       <c r="H1257" t="n">
         <v>455206</v>
@@ -36851,7 +36851,7 @@
         <v>19.3050003051758</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.8410110473633</v>
+        <v>16.8410129547119</v>
       </c>
       <c r="H1258" t="n">
         <v>433788</v>
@@ -36967,7 +36967,7 @@
         <v>19.3850002288818</v>
       </c>
       <c r="G1262" t="n">
-        <v>16.9108009338379</v>
+        <v>16.9108028411865</v>
       </c>
       <c r="H1262" t="n">
         <v>502379</v>
@@ -36996,7 +36996,7 @@
         <v>19.5650005340576</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.0678291320801</v>
+        <v>17.0678272247314</v>
       </c>
       <c r="H1263" t="n">
         <v>384274</v>
@@ -37141,7 +37141,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1268" t="n">
-        <v>16.9762287139893</v>
+        <v>16.9762268066406</v>
       </c>
       <c r="H1268" t="n">
         <v>261190</v>
@@ -37199,7 +37199,7 @@
         <v>19.5</v>
       </c>
       <c r="G1270" t="n">
-        <v>17.0111236572266</v>
+        <v>17.0111217498779</v>
       </c>
       <c r="H1270" t="n">
         <v>344884</v>
@@ -37228,7 +37228,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G1271" t="n">
-        <v>17.6305027008057</v>
+        <v>17.630500793457</v>
       </c>
       <c r="H1271" t="n">
         <v>1005080</v>
@@ -37373,7 +37373,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>18.6686153411865</v>
+        <v>18.6686172485352</v>
       </c>
       <c r="H1276" t="n">
         <v>699182</v>
@@ -37431,7 +37431,7 @@
         <v>21.5699996948242</v>
       </c>
       <c r="G1278" t="n">
-        <v>18.8169193267822</v>
+        <v>18.8169174194336</v>
       </c>
       <c r="H1278" t="n">
         <v>449059</v>
@@ -37518,7 +37518,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G1281" t="n">
-        <v>18.7384033203125</v>
+        <v>18.7384052276611</v>
       </c>
       <c r="H1281" t="n">
         <v>556510</v>
@@ -37547,7 +37547,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G1282" t="n">
-        <v>18.8518142700195</v>
+        <v>18.8518123626709</v>
       </c>
       <c r="H1282" t="n">
         <v>982689</v>
@@ -37634,7 +37634,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1285" t="n">
-        <v>18.1626434326172</v>
+        <v>18.1626453399658</v>
       </c>
       <c r="H1285" t="n">
         <v>782816</v>
@@ -37750,7 +37750,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G1289" t="n">
-        <v>17.9009323120117</v>
+        <v>17.900936126709</v>
       </c>
       <c r="H1289" t="n">
         <v>1145039</v>
@@ -37808,7 +37808,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1291" t="n">
-        <v>18.0974960327148</v>
+        <v>18.0974941253662</v>
       </c>
       <c r="H1291" t="n">
         <v>613539</v>
@@ -37837,7 +37837,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G1292" t="n">
-        <v>18.287712097168</v>
+        <v>18.2877101898193</v>
       </c>
       <c r="H1292" t="n">
         <v>532744</v>
@@ -37866,7 +37866,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1293" t="n">
-        <v>18.4779224395752</v>
+        <v>18.4779243469238</v>
       </c>
       <c r="H1293" t="n">
         <v>788037</v>
@@ -37953,7 +37953,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G1296" t="n">
-        <v>19.3655891418457</v>
+        <v>19.3655910491943</v>
       </c>
       <c r="H1296" t="n">
         <v>1398505</v>
@@ -37982,7 +37982,7 @@
         <v>21.25</v>
       </c>
       <c r="G1297" t="n">
-        <v>19.2478370666504</v>
+        <v>19.247838973999</v>
       </c>
       <c r="H1297" t="n">
         <v>1592446</v>
@@ -38040,7 +38040,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G1299" t="n">
-        <v>18.9942226409912</v>
+        <v>18.9942188262939</v>
       </c>
       <c r="H1299" t="n">
         <v>806371</v>
@@ -38098,7 +38098,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G1301" t="n">
-        <v>19.709789276123</v>
+        <v>19.7097854614258</v>
       </c>
       <c r="H1301" t="n">
         <v>990233</v>
@@ -38214,7 +38214,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G1305" t="n">
-        <v>19.2750110626221</v>
+        <v>19.2750129699707</v>
       </c>
       <c r="H1305" t="n">
         <v>480391</v>
@@ -38243,7 +38243,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G1306" t="n">
-        <v>19.1391429901123</v>
+        <v>19.1391448974609</v>
       </c>
       <c r="H1306" t="n">
         <v>469762</v>
@@ -38272,7 +38272,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>19.0666809082031</v>
+        <v>19.0666828155518</v>
       </c>
       <c r="H1307" t="n">
         <v>460630</v>
@@ -38301,7 +38301,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G1308" t="n">
-        <v>19.2750110626221</v>
+        <v>19.2750129699707</v>
       </c>
       <c r="H1308" t="n">
         <v>517471</v>
@@ -38388,7 +38388,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.2931270599365</v>
+        <v>19.2931289672852</v>
       </c>
       <c r="H1311" t="n">
         <v>561478</v>
@@ -38620,7 +38620,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>20.2894859313965</v>
+        <v>20.2894840240479</v>
       </c>
       <c r="H1319" t="n">
         <v>792099</v>
@@ -38707,7 +38707,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1322" t="n">
-        <v>20.271369934082</v>
+        <v>20.2713680267334</v>
       </c>
       <c r="H1322" t="n">
         <v>620853</v>
@@ -38736,7 +38736,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1323" t="n">
-        <v>20.0358695983887</v>
+        <v>20.03586769104</v>
       </c>
       <c r="H1323" t="n">
         <v>402708</v>
@@ -38881,7 +38881,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.1264476776123</v>
+        <v>20.1264457702637</v>
       </c>
       <c r="H1328" t="n">
         <v>436087</v>
@@ -38910,7 +38910,7 @@
         <v>21.25</v>
       </c>
       <c r="G1329" t="n">
-        <v>19.2478370666504</v>
+        <v>19.247838973999</v>
       </c>
       <c r="H1329" t="n">
         <v>1502553</v>
@@ -38997,7 +38997,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G1332" t="n">
-        <v>19.709789276123</v>
+        <v>19.7097854614258</v>
       </c>
       <c r="H1332" t="n">
         <v>623625</v>
@@ -39055,7 +39055,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1334" t="n">
-        <v>20.1083316802979</v>
+        <v>20.1083297729492</v>
       </c>
       <c r="H1334" t="n">
         <v>626540</v>
@@ -39287,7 +39287,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1342" t="n">
-        <v>20.2532558441162</v>
+        <v>20.2532539367676</v>
       </c>
       <c r="H1342" t="n">
         <v>413098</v>
@@ -39345,7 +39345,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G1344" t="n">
-        <v>20.715202331543</v>
+        <v>20.7152042388916</v>
       </c>
       <c r="H1344" t="n">
         <v>676600</v>
@@ -39374,7 +39374,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G1345" t="n">
-        <v>20.3710079193115</v>
+        <v>20.3710060119629</v>
       </c>
       <c r="H1345" t="n">
         <v>590227</v>
@@ -39461,7 +39461,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1348" t="n">
-        <v>20.0358695983887</v>
+        <v>20.03586769104</v>
       </c>
       <c r="H1348" t="n">
         <v>823799</v>
@@ -39548,7 +39548,7 @@
         <v>22.3899993896484</v>
       </c>
       <c r="G1351" t="n">
-        <v>20.2804279327393</v>
+        <v>20.2804298400879</v>
       </c>
       <c r="H1351" t="n">
         <v>368928</v>
@@ -39577,7 +39577,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G1352" t="n">
-        <v>20.2623157501221</v>
+        <v>20.2623138427734</v>
       </c>
       <c r="H1352" t="n">
         <v>614169</v>
@@ -39635,7 +39635,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1354" t="n">
-        <v>20.2351398468018</v>
+        <v>20.2351379394531</v>
       </c>
       <c r="H1354" t="n">
         <v>422414</v>
@@ -39722,7 +39722,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1357" t="n">
-        <v>20.5612201690674</v>
+        <v>20.5612182617188</v>
       </c>
       <c r="H1357" t="n">
         <v>429985</v>
@@ -39751,7 +39751,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G1358" t="n">
-        <v>20.6336822509766</v>
+        <v>20.6336841583252</v>
       </c>
       <c r="H1358" t="n">
         <v>489631</v>
@@ -39780,7 +39780,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G1359" t="n">
-        <v>21.0775146484375</v>
+        <v>21.0775184631348</v>
       </c>
       <c r="H1359" t="n">
         <v>714149</v>
@@ -39809,7 +39809,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G1360" t="n">
-        <v>20.8239002227783</v>
+        <v>20.8238983154297</v>
       </c>
       <c r="H1360" t="n">
         <v>834255</v>
@@ -39838,7 +39838,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G1361" t="n">
-        <v>20.9325942993164</v>
+        <v>20.9325923919678</v>
       </c>
       <c r="H1361" t="n">
         <v>504609</v>
@@ -39867,7 +39867,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G1362" t="n">
-        <v>20.9144763946533</v>
+        <v>20.9144744873047</v>
       </c>
       <c r="H1362" t="n">
         <v>377753</v>
@@ -39896,7 +39896,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1363" t="n">
-        <v>21.4851188659668</v>
+        <v>21.4851169586182</v>
       </c>
       <c r="H1363" t="n">
         <v>721200</v>
@@ -39954,7 +39954,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G1365" t="n">
-        <v>21.6753311157227</v>
+        <v>21.675329208374</v>
       </c>
       <c r="H1365" t="n">
         <v>678307</v>
@@ -39983,7 +39983,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G1366" t="n">
-        <v>20.9054203033447</v>
+        <v>20.9054183959961</v>
       </c>
       <c r="H1366" t="n">
         <v>877417</v>
@@ -40041,7 +40041,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G1368" t="n">
-        <v>20.9325942993164</v>
+        <v>20.9325923919678</v>
       </c>
       <c r="H1368" t="n">
         <v>734019</v>
@@ -80154,6 +80154,35 @@
         <v>312149</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>39.4700012207031</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>39.8300018310547</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>39.3199996948242</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>39.7799987792969</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>39.7799987792969</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>272155</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>
